--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A84749-E886-4D55-91C4-5221521615B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACEB3E2-7457-4EC2-A34A-A7B5CCF719A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00000_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -203,10 +203,10 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -533,67 +533,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA153E9-5DFB-45B3-8931-84232E27E98E}">
   <dimension ref="A2:P68"/>
-  <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16" width="16.58203125" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.58203125" style="1"/>
+    <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
     </row>
     <row r="3" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6" t="s">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="6"/>
+      <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
@@ -646,49 +646,34 @@
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3">
-        <v>3.2446899999999999</v>
-      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>4.7589399999999999</v>
-      </c>
-      <c r="E5" s="3">
-        <v>3.6804700000000001</v>
-      </c>
+        <v>4.7331500000000002</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3">
-        <v>5.3365200000000002</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3.1818599999999999</v>
-      </c>
+        <v>5.3544900000000002</v>
+      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>4.8102600000000004</v>
-      </c>
-      <c r="I5" s="3">
-        <v>3.1968800000000002</v>
-      </c>
+        <v>4.84016</v>
+      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3">
-        <v>4.6488500000000004</v>
-      </c>
-      <c r="K5" s="3">
-        <v>2.8299699999999999</v>
-      </c>
+        <v>4.6296099999999996</v>
+      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="3">
-        <v>4.2943600000000002</v>
-      </c>
-      <c r="M5" s="3">
-        <v>2.9219900000000001</v>
-      </c>
+        <v>4.3128500000000001</v>
+      </c>
+      <c r="M5" s="3"/>
       <c r="N5" s="3">
-        <v>4.26187</v>
-      </c>
-      <c r="O5" s="3">
-        <f>AVERAGE(C5,E5,G5,I5,K5,M5)</f>
-        <v>3.1759766666666671</v>
-      </c>
+        <v>4.2569699999999999</v>
+      </c>
+      <c r="O5" s="3"/>
       <c r="P5" s="3">
         <f>AVERAGE(D5,F5,H5,J5,L5,N5)</f>
-        <v>4.6851333333333329</v>
+        <v>4.6878716666666671</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -697,19 +682,34 @@
         <v>9</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>4.8913900000000003</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3">
+        <v>5.5302499999999997</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>4.9999799999999999</v>
+      </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>4.8009399999999998</v>
+      </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>4.4855999999999998</v>
+      </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="N6" s="3">
+        <v>4.4412000000000003</v>
+      </c>
       <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <f t="shared" ref="P6:P9" si="0">AVERAGE(D6,F6,H6,J6,L6,N6)</f>
+        <v>4.8582266666666669</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
@@ -717,19 +717,34 @@
         <v>10</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3">
+        <v>4.9870799999999997</v>
+      </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3">
+        <v>5.6116200000000003</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>5.0410199999999996</v>
+      </c>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="3">
+        <v>4.9493400000000003</v>
+      </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>4.5785200000000001</v>
+      </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="N7" s="3">
+        <v>4.5447699999999998</v>
+      </c>
       <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9520583333333335</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
@@ -737,19 +752,34 @@
         <v>11</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3">
+        <v>5.0443600000000002</v>
+      </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3">
+        <v>5.6475499999999998</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>5.0628000000000002</v>
+      </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="J8" s="3">
+        <v>4.9394600000000004</v>
+      </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <v>4.6181299999999998</v>
+      </c>
       <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="N8" s="3">
+        <v>4.5690200000000001</v>
+      </c>
       <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9802200000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
@@ -757,73 +787,88 @@
         <v>12</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>5.0284599999999999</v>
+      </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4">
+        <v>5.6217199999999998</v>
+      </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="H9" s="4">
+        <v>5.1266999999999996</v>
+      </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="J9" s="4">
+        <v>4.96793</v>
+      </c>
       <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+      <c r="L9" s="4">
+        <v>4.63727</v>
+      </c>
       <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4">
+        <v>4.5743200000000002</v>
+      </c>
       <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="P9" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9927333333333328</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6" t="s">
+      <c r="L11" s="5"/>
+      <c r="M11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6" t="s">
+      <c r="N11" s="5"/>
+      <c r="O11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="6"/>
+      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
@@ -876,49 +921,34 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3">
-        <v>2.8740600000000001</v>
-      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="3">
-        <v>4.5374999999999996</v>
-      </c>
-      <c r="E13" s="3">
-        <v>3.3617599999999999</v>
-      </c>
+        <v>4.5132899999999996</v>
+      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3">
-        <v>5.0008600000000003</v>
-      </c>
-      <c r="G13" s="3">
-        <v>3.2083900000000001</v>
-      </c>
+        <v>5.0724900000000002</v>
+      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
-        <v>4.83718</v>
-      </c>
-      <c r="I13" s="3">
-        <v>2.9540700000000002</v>
-      </c>
+        <v>4.8775700000000004</v>
+      </c>
+      <c r="I13" s="3"/>
       <c r="J13" s="3">
-        <v>4.5148099999999998</v>
-      </c>
-      <c r="K13" s="3">
-        <v>2.6569400000000001</v>
-      </c>
+        <v>4.54291</v>
+      </c>
+      <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>4.15707</v>
-      </c>
-      <c r="M13" s="3">
-        <v>2.6871200000000002</v>
-      </c>
+        <v>4.1329700000000003</v>
+      </c>
+      <c r="M13" s="3"/>
       <c r="N13" s="3">
-        <v>4.1199300000000001</v>
-      </c>
-      <c r="O13" s="3">
-        <f>AVERAGE(C13,E13,G13,I13,K13,M13)</f>
-        <v>2.9570566666666664</v>
-      </c>
+        <v>4.1148800000000003</v>
+      </c>
+      <c r="O13" s="3"/>
       <c r="P13" s="3">
         <f>AVERAGE(D13,F13,H13,J13,L13,N13)</f>
-        <v>4.5278916666666671</v>
+        <v>4.5423516666666668</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -927,19 +957,34 @@
         <v>9</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>4.7063600000000001</v>
+      </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3">
+        <v>5.2547600000000001</v>
+      </c>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3">
+        <v>4.8792900000000001</v>
+      </c>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>4.5448399999999998</v>
+      </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>4.2995400000000004</v>
+      </c>
       <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="N14" s="3">
+        <v>4.23569</v>
+      </c>
       <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <f t="shared" ref="P14:P17" si="1">AVERAGE(D14,F14,H14,J14,L14,N14)</f>
+        <v>4.6534133333333338</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
@@ -947,19 +992,34 @@
         <v>10</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>4.7744499999999999</v>
+      </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3">
+        <v>5.24275</v>
+      </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <v>5.0554300000000003</v>
+      </c>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="3">
+        <v>4.7523499999999999</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>4.3680899999999996</v>
+      </c>
       <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="N15" s="3">
+        <v>4.3902099999999997</v>
+      </c>
       <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="1"/>
+        <v>4.7638799999999994</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
@@ -967,19 +1027,34 @@
         <v>11</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>4.8411799999999996</v>
+      </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3">
+        <v>5.2918099999999999</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3">
+        <v>5.1157899999999996</v>
+      </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>4.7609899999999996</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <v>4.4552699999999996</v>
+      </c>
       <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="N16" s="3">
+        <v>4.4038599999999999</v>
+      </c>
       <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <f t="shared" si="1"/>
+        <v>4.8114833333333324</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
@@ -987,75 +1062,90 @@
         <v>12</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>4.8296099999999997</v>
+      </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="F17" s="4">
+        <v>5.3057299999999996</v>
+      </c>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="H17" s="4">
+        <v>5.1624800000000004</v>
+      </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="4">
+        <v>4.81447</v>
+      </c>
       <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="L17" s="4">
+        <v>4.4093200000000001</v>
+      </c>
       <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="N17" s="4">
+        <v>4.4369399999999999</v>
+      </c>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <f t="shared" si="1"/>
+        <v>4.8264250000000004</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6" t="s">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6" t="s">
+      <c r="L20" s="5"/>
+      <c r="M20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6" t="s">
+      <c r="N20" s="5"/>
+      <c r="O20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P20" s="6"/>
+      <c r="P20" s="5"/>
     </row>
     <row r="21" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
@@ -1109,19 +1199,34 @@
         <v>8</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>5.0917300000000001</v>
+      </c>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3">
+        <v>5.7859600000000002</v>
+      </c>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="3">
+        <v>5.2265300000000003</v>
+      </c>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3">
+        <v>4.9669499999999998</v>
+      </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="L22" s="3">
+        <v>4.6795799999999996</v>
+      </c>
       <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="N22" s="3">
+        <v>4.5426299999999999</v>
+      </c>
       <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <f>AVERAGE(D22,F22,H22,J22,L22,N22)</f>
+        <v>5.0488966666666668</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
@@ -1129,19 +1234,34 @@
         <v>9</v>
       </c>
       <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>5.2306299999999997</v>
+      </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3">
+        <v>5.8695700000000004</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="3">
+        <v>5.3025799999999998</v>
+      </c>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
+      <c r="J23" s="3">
+        <v>5.1180300000000001</v>
+      </c>
       <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <v>4.8536200000000003</v>
+      </c>
       <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="N23" s="3">
+        <v>4.7490699999999997</v>
+      </c>
       <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <f>AVERAGE(D23,F23,H23,J23,L23,N23)</f>
+        <v>5.1872499999999997</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
@@ -1149,19 +1269,34 @@
         <v>10</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3">
+        <v>5.3506999999999998</v>
+      </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3">
+        <v>5.9641000000000002</v>
+      </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3">
+        <v>5.3904399999999999</v>
+      </c>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="3">
+        <v>5.20702</v>
+      </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="L24" s="3">
+        <v>4.9446599999999998</v>
+      </c>
       <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="N24" s="3">
+        <v>4.8455500000000002</v>
+      </c>
       <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <f>AVERAGE(D24,F24,H24,J24,L24,N24)</f>
+        <v>5.2837449999999997</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
@@ -1205,57 +1340,57 @@
     </row>
     <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6" t="s">
+      <c r="F28" s="5"/>
+      <c r="G28" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6" t="s">
+      <c r="L28" s="5"/>
+      <c r="M28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6" t="s">
+      <c r="N28" s="5"/>
+      <c r="O28" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P28" s="6"/>
+      <c r="P28" s="5"/>
     </row>
     <row r="29" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
@@ -1309,19 +1444,34 @@
         <v>8</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>4.86165</v>
+      </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3">
+        <v>5.3726500000000001</v>
+      </c>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="3">
+        <v>5.17258</v>
+      </c>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
+      <c r="J30" s="3">
+        <v>4.7725099999999996</v>
+      </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="L30" s="3">
+        <v>4.4440900000000001</v>
+      </c>
       <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+      <c r="N30" s="3">
+        <v>4.4501499999999998</v>
+      </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3">
+        <f>AVERAGE(D30,F30,H30,J30,L30,N30)</f>
+        <v>4.8456049999999999</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
@@ -1329,19 +1479,34 @@
         <v>9</v>
       </c>
       <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>4.9434300000000002</v>
+      </c>
       <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3">
+        <v>5.5869999999999997</v>
+      </c>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="3">
+        <v>5.3209299999999997</v>
+      </c>
       <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="J31" s="3">
+        <v>4.9447700000000001</v>
+      </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
+      <c r="L31" s="3">
+        <v>4.6178600000000003</v>
+      </c>
       <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
+      <c r="N31" s="3">
+        <v>4.5539100000000001</v>
+      </c>
       <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="P31" s="3">
+        <f>AVERAGE(D31,F31,H31,J31,L31,N31)</f>
+        <v>4.99465</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
@@ -1349,19 +1514,34 @@
         <v>10</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>5.0438499999999999</v>
+      </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3">
+        <v>5.6688400000000003</v>
+      </c>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="H32" s="3">
+        <v>5.2460800000000001</v>
+      </c>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3">
+        <v>5.0347400000000002</v>
+      </c>
       <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+      <c r="L32" s="3">
+        <v>4.6789300000000003</v>
+      </c>
       <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
+      <c r="N32" s="3">
+        <v>4.6941699999999997</v>
+      </c>
       <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3">
+        <f>AVERAGE(D32,F32,H32,J32,L32,N32)</f>
+        <v>5.0611016666666666</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
@@ -1407,57 +1587,57 @@
       <c r="A36" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
     </row>
     <row r="37" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="5"/>
+      <c r="E37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="5"/>
+      <c r="G37" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="5"/>
+      <c r="I37" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6" t="s">
+      <c r="J37" s="5"/>
+      <c r="K37" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6" t="s">
+      <c r="L37" s="5"/>
+      <c r="M37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6" t="s">
+      <c r="N37" s="5"/>
+      <c r="O37" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P37" s="6"/>
+      <c r="P37" s="5"/>
     </row>
     <row r="38" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
@@ -1511,19 +1691,34 @@
         <v>8</v>
       </c>
       <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3">
+        <v>4.9199900000000003</v>
+      </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3">
+        <v>5.5874300000000003</v>
+      </c>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="H39" s="3">
+        <v>4.9704800000000002</v>
+      </c>
       <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+      <c r="J39" s="3">
+        <v>4.7198399999999996</v>
+      </c>
       <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+      <c r="L39" s="3">
+        <v>4.49193</v>
+      </c>
       <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
+      <c r="N39" s="3">
+        <v>4.2741699999999998</v>
+      </c>
       <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
+      <c r="P39" s="3">
+        <f>AVERAGE(D39,F39,H39,J39,L39,N39)</f>
+        <v>4.827306666666666</v>
+      </c>
     </row>
     <row r="40" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
@@ -1607,57 +1802,57 @@
     </row>
     <row r="44" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
     </row>
     <row r="45" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6" t="s">
+      <c r="D45" s="5"/>
+      <c r="E45" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6" t="s">
+      <c r="F45" s="5"/>
+      <c r="G45" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="5"/>
+      <c r="I45" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6" t="s">
+      <c r="J45" s="5"/>
+      <c r="K45" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6" t="s">
+      <c r="L45" s="5"/>
+      <c r="M45" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6" t="s">
+      <c r="N45" s="5"/>
+      <c r="O45" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P45" s="6"/>
+      <c r="P45" s="5"/>
     </row>
     <row r="46" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
@@ -1711,19 +1906,34 @@
         <v>8</v>
       </c>
       <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="D47" s="3">
+        <v>4.6547400000000003</v>
+      </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3">
+        <v>5.2228700000000003</v>
+      </c>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="3">
+        <v>4.8950399999999998</v>
+      </c>
       <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
+      <c r="J47" s="3">
+        <v>4.6132999999999997</v>
+      </c>
       <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
+      <c r="L47" s="3">
+        <v>4.28667</v>
+      </c>
       <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
+      <c r="N47" s="3">
+        <v>4.1562599999999996</v>
+      </c>
       <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
+      <c r="P47" s="3">
+        <f>AVERAGE(D47,F47,H47,J47,L47,N47)</f>
+        <v>4.6381466666666666</v>
+      </c>
     </row>
     <row r="48" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
@@ -1809,57 +2019,57 @@
       <c r="A53" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
     </row>
     <row r="54" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6" t="s">
+      <c r="D54" s="5"/>
+      <c r="E54" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6" t="s">
+      <c r="F54" s="5"/>
+      <c r="G54" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6" t="s">
+      <c r="H54" s="5"/>
+      <c r="I54" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6" t="s">
+      <c r="J54" s="5"/>
+      <c r="K54" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6" t="s">
+      <c r="L54" s="5"/>
+      <c r="M54" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6" t="s">
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P54" s="6"/>
+      <c r="P54" s="5"/>
     </row>
     <row r="55" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
@@ -1913,19 +2123,34 @@
         <v>8</v>
       </c>
       <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3">
+        <v>4.7237600000000004</v>
+      </c>
       <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3">
+        <v>5.4169700000000001</v>
+      </c>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
+      <c r="H56" s="3">
+        <v>4.7933399999999997</v>
+      </c>
       <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
+      <c r="J56" s="3">
+        <v>4.5930299999999997</v>
+      </c>
       <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
+      <c r="L56" s="3">
+        <v>4.37033</v>
+      </c>
       <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
+      <c r="N56" s="3">
+        <v>4.1235600000000003</v>
+      </c>
       <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
+      <c r="P56" s="3">
+        <f>AVERAGE(D56,F56,H56,J56,L56,N56)</f>
+        <v>4.6701649999999999</v>
+      </c>
     </row>
     <row r="57" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
@@ -2009,57 +2234,57 @@
     </row>
     <row r="61" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
     </row>
     <row r="62" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6" t="s">
+      <c r="D62" s="5"/>
+      <c r="E62" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6" t="s">
+      <c r="F62" s="5"/>
+      <c r="G62" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6" t="s">
+      <c r="H62" s="5"/>
+      <c r="I62" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6" t="s">
+      <c r="J62" s="5"/>
+      <c r="K62" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6" t="s">
+      <c r="L62" s="5"/>
+      <c r="M62" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6" t="s">
+      <c r="N62" s="5"/>
+      <c r="O62" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P62" s="6"/>
+      <c r="P62" s="5"/>
     </row>
     <row r="63" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
@@ -2113,19 +2338,34 @@
         <v>8</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3">
+        <v>4.5262000000000002</v>
+      </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3">
+        <v>5.1717599999999999</v>
+      </c>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
+      <c r="H64" s="3">
+        <v>4.7594000000000003</v>
+      </c>
       <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
+      <c r="J64" s="3">
+        <v>4.4965999999999999</v>
+      </c>
       <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
+      <c r="L64" s="3">
+        <v>4.0846099999999996</v>
+      </c>
       <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
+      <c r="N64" s="3">
+        <v>4.0165800000000003</v>
+      </c>
       <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
+      <c r="P64" s="3">
+        <f>AVERAGE(D64,F64,H64,J64,L64,N64)</f>
+        <v>4.5091916666666672</v>
+      </c>
     </row>
     <row r="65" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
@@ -2249,8 +2489,6 @@
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="M37:N37"/>
     <mergeCell ref="O37:P37"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
     <mergeCell ref="B27:P27"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:D28"/>
@@ -2260,15 +2498,6 @@
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="O28:P28"/>
-    <mergeCell ref="B19:P19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="O20:P20"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B10:P10"/>
     <mergeCell ref="B11:B12"/>
@@ -2281,10 +2510,21 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="B19:P19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="O20:P20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACEB3E2-7457-4EC2-A34A-A7B5CCF719A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72B9E31-D106-46F2-BB4B-31A94003F986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -102,8 +102,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Large Drafter
-LD</t>
+    <r>
+      <t xml:space="preserve">Large Drafter
+LD
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>not detach</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,13 +147,25 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -212,10 +236,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1304,19 +1328,34 @@
         <v>11</v>
       </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>5.33786</v>
+      </c>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3">
+        <v>5.9935799999999997</v>
+      </c>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="3">
+        <v>5.4206399999999997</v>
+      </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+      <c r="J25" s="3">
+        <v>5.2401299999999997</v>
+      </c>
       <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+      <c r="L25" s="3">
+        <v>4.9555800000000003</v>
+      </c>
       <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="N25" s="3">
+        <v>4.8746600000000004</v>
+      </c>
       <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
+        <v>5.3037416666666672</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
@@ -1324,19 +1363,34 @@
         <v>12</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>5.3412699999999997</v>
+      </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4">
+        <v>5.9933699999999996</v>
+      </c>
       <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="H26" s="4">
+        <v>5.4163199999999998</v>
+      </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="J26" s="4">
+        <v>5.2602200000000003</v>
+      </c>
       <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="L26" s="4">
+        <v>4.9869199999999996</v>
+      </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="N26" s="4">
+        <v>4.91995</v>
+      </c>
       <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
+      <c r="P26" s="4">
+        <f>AVERAGE(D26,F26,H26,J26,L26,N26)</f>
+        <v>5.3196750000000002</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
@@ -1549,19 +1603,34 @@
         <v>11</v>
       </c>
       <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>5.0611499999999996</v>
+      </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3">
+        <v>5.6457899999999999</v>
+      </c>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="3">
+        <v>5.3829700000000003</v>
+      </c>
       <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="3">
+        <v>5.1852099999999997</v>
+      </c>
       <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
+      <c r="L33" s="3">
+        <v>4.7620899999999997</v>
+      </c>
       <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
+      <c r="N33" s="3">
+        <v>4.7435400000000003</v>
+      </c>
       <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
+      <c r="P33" s="3">
+        <f>AVERAGE(D33,F33,H33,J33,L33,N33)</f>
+        <v>5.1301250000000005</v>
+      </c>
     </row>
     <row r="34" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
@@ -1569,19 +1638,34 @@
         <v>12</v>
       </c>
       <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4">
+        <v>5.0952400000000004</v>
+      </c>
       <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+      <c r="F34" s="4">
+        <v>5.5869600000000004</v>
+      </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="H34" s="4">
+        <v>5.3165500000000003</v>
+      </c>
       <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="J34" s="4">
+        <v>5.1437799999999996</v>
+      </c>
       <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
+      <c r="L34" s="4">
+        <v>4.7247700000000004</v>
+      </c>
       <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
+      <c r="N34" s="4">
+        <v>4.7457000000000003</v>
+      </c>
       <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
+      <c r="P34" s="4">
+        <f>AVERAGE(D34,F34,H34,J34,L34,N34)</f>
+        <v>5.1021666666666663</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -2198,19 +2282,34 @@
         <v>11</v>
       </c>
       <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3">
+        <v>5.1421799999999998</v>
+      </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3">
+        <v>5.8545800000000003</v>
+      </c>
       <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
+      <c r="H59" s="3">
+        <v>5.2994899999999996</v>
+      </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
+      <c r="J59" s="3">
+        <v>5.1080399999999999</v>
+      </c>
       <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
+      <c r="L59" s="3">
+        <v>4.7957599999999996</v>
+      </c>
       <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
+      <c r="N59" s="3">
+        <v>4.6078999999999999</v>
+      </c>
       <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
+      <c r="P59" s="3">
+        <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
+        <v>5.1346583333333333</v>
+      </c>
     </row>
     <row r="60" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
@@ -2413,19 +2512,34 @@
         <v>11</v>
       </c>
       <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3">
+        <v>4.9710700000000001</v>
+      </c>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3">
+        <v>5.4894499999999997</v>
+      </c>
       <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
+      <c r="H67" s="3">
+        <v>5.2308899999999996</v>
+      </c>
       <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
+      <c r="J67" s="3">
+        <v>4.8858800000000002</v>
+      </c>
       <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
+      <c r="L67" s="3">
+        <v>4.5251400000000004</v>
+      </c>
       <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
+      <c r="N67" s="3">
+        <v>4.47593</v>
+      </c>
       <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
+      <c r="P67" s="3">
+        <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
+        <v>4.9297266666666664</v>
+      </c>
     </row>
     <row r="68" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3C14E-D598-46F2-8944-F765BD996A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8708106B-F687-45D0-A79D-DCAD449B97EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="llama2-7b" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -214,10 +213,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -547,7 +546,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -569,7 +568,7 @@
       <c r="P2" s="8"/>
     </row>
     <row r="3" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -603,7 +602,7 @@
       <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="9"/>
       <c r="C4" s="2" t="s">
         <v>15</v>
@@ -649,7 +648,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -684,7 +683,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
+      <c r="A6" s="7"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
@@ -719,7 +718,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
@@ -754,7 +753,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
+      <c r="A8" s="7"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -789,7 +788,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -824,7 +823,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
+      <c r="A10" s="7"/>
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
@@ -844,7 +843,7 @@
       <c r="P10" s="8"/>
     </row>
     <row r="11" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
@@ -878,7 +877,7 @@
       <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="9"/>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -924,7 +923,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -959,7 +958,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
@@ -994,7 +993,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,7 +1028,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -1064,7 +1063,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1115,7 +1114,7 @@
       <c r="P18" s="3"/>
     </row>
     <row r="20" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -1137,7 +1136,7 @@
       <c r="P20" s="8"/>
     </row>
     <row r="21" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="5" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1170,7 @@
       <c r="P21" s="5"/>
     </row>
     <row r="22" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="9"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
@@ -1217,7 +1216,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1251,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1287,7 +1286,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1322,7 +1321,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
+      <c r="A26" s="7"/>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -1357,7 +1356,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -1392,7 +1391,7 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
+      <c r="A28" s="7"/>
       <c r="B28" s="8" t="s">
         <v>14</v>
       </c>
@@ -1412,7 +1411,7 @@
       <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
+      <c r="A29" s="7"/>
       <c r="B29" s="5" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1445,7 @@
       <c r="P29" s="5"/>
     </row>
     <row r="30" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
+      <c r="A30" s="7"/>
       <c r="B30" s="9"/>
       <c r="C30" s="2" t="s">
         <v>15</v>
@@ -1492,7 +1491,7 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
+      <c r="A31" s="7"/>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
@@ -1527,7 +1526,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
+      <c r="A32" s="7"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -1562,7 +1561,7 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -1597,7 +1596,7 @@
       </c>
     </row>
     <row r="34" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
+      <c r="A34" s="7"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1632,7 +1631,7 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
+      <c r="A35" s="7"/>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
@@ -1699,7 +1698,7 @@
       <c r="P37" s="3"/>
     </row>
     <row r="38" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1721,7 +1720,7 @@
       <c r="P38" s="8"/>
     </row>
     <row r="39" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="5" t="s">
         <v>0</v>
       </c>
@@ -1755,7 +1754,7 @@
       <c r="P39" s="5"/>
     </row>
     <row r="40" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="9"/>
       <c r="C40" s="2" t="s">
         <v>15</v>
@@ -1801,7 +1800,7 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -1836,7 +1835,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1871,27 +1870,42 @@
       </c>
     </row>
     <row r="43" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>5.3713800000000003</v>
+      </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>6.0097399999999999</v>
+      </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="3">
+        <v>5.4100900000000003</v>
+      </c>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="3">
+        <v>5.2283900000000001</v>
+      </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="L43" s="3">
+        <v>5.0531199999999998</v>
+      </c>
       <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="N43" s="3">
+        <v>4.7590399999999997</v>
+      </c>
       <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
+      <c r="P43" s="3">
+        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
+        <v>5.3052933333333332</v>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -1911,7 +1925,7 @@
       <c r="P44" s="3"/>
     </row>
     <row r="45" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
@@ -1931,7 +1945,7 @@
       <c r="P45" s="4"/>
     </row>
     <row r="46" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
+      <c r="A46" s="7"/>
       <c r="B46" s="8" t="s">
         <v>14</v>
       </c>
@@ -1951,7 +1965,7 @@
       <c r="P46" s="8"/>
     </row>
     <row r="47" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="5" t="s">
         <v>0</v>
       </c>
@@ -1985,7 +1999,7 @@
       <c r="P47" s="5"/>
     </row>
     <row r="48" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
+      <c r="A48" s="7"/>
       <c r="B48" s="9"/>
       <c r="C48" s="2" t="s">
         <v>15</v>
@@ -2031,7 +2045,7 @@
       </c>
     </row>
     <row r="49" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -2066,7 +2080,7 @@
       </c>
     </row>
     <row r="50" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
+      <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
@@ -2101,27 +2115,42 @@
       </c>
     </row>
     <row r="51" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3">
+        <v>5.0986200000000004</v>
+      </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3">
+        <v>5.6387900000000002</v>
+      </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
+      <c r="H51" s="3">
+        <v>5.34267</v>
+      </c>
       <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
+      <c r="J51" s="3">
+        <v>5.0380700000000003</v>
+      </c>
       <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="L51" s="3">
+        <v>4.8503800000000004</v>
+      </c>
       <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+      <c r="N51" s="3">
+        <v>4.5972499999999998</v>
+      </c>
       <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
+      <c r="P51" s="3">
+        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
+        <v>5.0942966666666676</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
+      <c r="A52" s="7"/>
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
@@ -2141,7 +2170,7 @@
       <c r="P52" s="3"/>
     </row>
     <row r="53" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
+      <c r="A53" s="7"/>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2177,7 +2206,7 @@
       <c r="P54" s="3"/>
     </row>
     <row r="56" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -2199,7 +2228,7 @@
       <c r="P56" s="8"/>
     </row>
     <row r="57" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
+      <c r="A57" s="7"/>
       <c r="B57" s="5" t="s">
         <v>0</v>
       </c>
@@ -2233,7 +2262,7 @@
       <c r="P57" s="5"/>
     </row>
     <row r="58" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
+      <c r="A58" s="7"/>
       <c r="B58" s="9"/>
       <c r="C58" s="2" t="s">
         <v>15</v>
@@ -2279,7 +2308,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
+      <c r="A59" s="7"/>
       <c r="B59" s="1" t="s">
         <v>8</v>
       </c>
@@ -2314,7 +2343,7 @@
       </c>
     </row>
     <row r="60" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
+      <c r="A60" s="7"/>
       <c r="B60" s="1" t="s">
         <v>9</v>
       </c>
@@ -2349,27 +2378,42 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
+      <c r="A61" s="7"/>
       <c r="B61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3">
+        <v>5.1006499999999999</v>
+      </c>
       <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3">
+        <v>5.8121</v>
+      </c>
       <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
+      <c r="H61" s="3">
+        <v>5.21882</v>
+      </c>
       <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
+      <c r="J61" s="3">
+        <v>5.0633699999999999</v>
+      </c>
       <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
+      <c r="L61" s="3">
+        <v>4.7288600000000001</v>
+      </c>
       <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
+      <c r="N61" s="3">
+        <v>4.5111400000000001</v>
+      </c>
       <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
+      <c r="P61" s="3">
+        <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
+        <v>5.0724900000000002</v>
+      </c>
     </row>
     <row r="62" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
+      <c r="A62" s="7"/>
       <c r="B62" s="1" t="s">
         <v>11</v>
       </c>
@@ -2404,27 +2448,42 @@
       </c>
     </row>
     <row r="63" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
+      <c r="A63" s="7"/>
       <c r="B63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
+      <c r="D63" s="4">
+        <v>5.18682</v>
+      </c>
       <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+      <c r="F63" s="4">
+        <v>5.8269299999999999</v>
+      </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
+      <c r="H63" s="4">
+        <v>5.3310199999999996</v>
+      </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
+      <c r="J63" s="4">
+        <v>5.1258499999999998</v>
+      </c>
       <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
+      <c r="L63" s="4">
+        <v>4.8208500000000001</v>
+      </c>
       <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
+      <c r="N63" s="4">
+        <v>4.6295500000000001</v>
+      </c>
       <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
+      <c r="P63" s="4">
+        <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
+        <v>5.1535033333333331</v>
+      </c>
     </row>
     <row r="64" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
+      <c r="A64" s="7"/>
       <c r="B64" s="8" t="s">
         <v>14</v>
       </c>
@@ -2444,7 +2503,7 @@
       <c r="P64" s="8"/>
     </row>
     <row r="65" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
+      <c r="A65" s="7"/>
       <c r="B65" s="5" t="s">
         <v>0</v>
       </c>
@@ -2478,7 +2537,7 @@
       <c r="P65" s="5"/>
     </row>
     <row r="66" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
+      <c r="A66" s="7"/>
       <c r="B66" s="9"/>
       <c r="C66" s="2" t="s">
         <v>15</v>
@@ -2524,7 +2583,7 @@
       </c>
     </row>
     <row r="67" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
+      <c r="A67" s="7"/>
       <c r="B67" s="1" t="s">
         <v>8</v>
       </c>
@@ -2559,7 +2618,7 @@
       </c>
     </row>
     <row r="68" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
+      <c r="A68" s="7"/>
       <c r="B68" s="1" t="s">
         <v>9</v>
       </c>
@@ -2594,27 +2653,42 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
+      <c r="A69" s="7"/>
       <c r="B69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3">
+        <v>4.8427899999999999</v>
+      </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3">
+        <v>5.4260799999999998</v>
+      </c>
       <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="H69" s="3">
+        <v>5.3422499999999999</v>
+      </c>
       <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
+      <c r="J69" s="3">
+        <v>4.9078900000000001</v>
+      </c>
       <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
+      <c r="L69" s="3">
+        <v>4.5387500000000003</v>
+      </c>
       <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
+      <c r="N69" s="3">
+        <v>4.3954199999999997</v>
+      </c>
       <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
+      <c r="P69" s="3">
+        <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
+        <v>4.9088633333333336</v>
+      </c>
     </row>
     <row r="70" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
+      <c r="A70" s="7"/>
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
@@ -2649,27 +2723,102 @@
       </c>
     </row>
     <row r="71" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
+      <c r="A71" s="7"/>
       <c r="B71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
+      <c r="D71" s="4">
+        <v>4.9133500000000003</v>
+      </c>
       <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="F71" s="4">
+        <v>5.5378100000000003</v>
+      </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="H71" s="4">
+        <v>5.2631699999999997</v>
+      </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
+      <c r="J71" s="4">
+        <v>4.8795099999999998</v>
+      </c>
       <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
+      <c r="L71" s="4">
+        <v>4.5223500000000003</v>
+      </c>
       <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
+      <c r="N71" s="4">
+        <v>4.4981600000000004</v>
+      </c>
       <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
+      <c r="P71" s="4">
+        <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+        <v>4.9357250000000006</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B64:P64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B10:P10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B20:P20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="M47:N47"/>
     <mergeCell ref="O47:P47"/>
     <mergeCell ref="A38:A53"/>
@@ -2686,66 +2835,6 @@
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B20:P20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B10:P10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="A2:A17"/>
-    <mergeCell ref="A20:A35"/>
-    <mergeCell ref="A56:A71"/>
-    <mergeCell ref="B64:P64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="B56:P56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:D57"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8708106B-F687-45D0-A79D-DCAD449B97EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FF8191-08A4-4D1F-88EE-D73457FD1B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="36">
   <si>
     <t>Data Num.</t>
   </si>
@@ -98,12 +98,90 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Large Drafter
-LD</t>
+    <t>HASS-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HASS-2</t>
+    <t>Large Drafter
+LD5
+100k (epoch=20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/0/0/0/0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/1/1/1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/0/0/1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Large Drafter
+LD
+100k (epoch=40)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/0/0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0/1/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Large Drafter
+LD
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Load Error</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Large Drafter
+LD
+from HASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100k (epoch=10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200k (epoch=8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400k (epoch=7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600k (epoch=6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800k (epoch=5)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,7 +192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +210,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -193,7 +277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,7 +293,10 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -219,6 +306,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -538,72 +628,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA153E9-5DFB-45B3-8931-84232E27E98E}">
-  <dimension ref="A2:P71"/>
-  <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:P117"/>
+  <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
     <col min="17" max="16384" width="7.58203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-    </row>
-    <row r="3" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="5" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="10"/>
+      <c r="K3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="10"/>
+      <c r="M3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
+      <c r="N3" s="10"/>
+      <c r="O3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="9"/>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
@@ -647,8 +737,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
+    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -682,8 +772,8 @@
         <v>4.6878716666666671</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
@@ -717,8 +807,8 @@
         <v>4.8582266666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
@@ -752,8 +842,8 @@
         <v>4.9520583333333335</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
+    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -787,8 +877,8 @@
         <v>4.9802200000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -822,63 +912,63 @@
         <v>4.9927333333333328</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-    </row>
-    <row r="11" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="5" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5" t="s">
+      <c r="J11" s="10"/>
+      <c r="K11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5" t="s">
+      <c r="L11" s="10"/>
+      <c r="M11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5" t="s">
+      <c r="N11" s="10"/>
+      <c r="O11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="9"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
@@ -922,8 +1012,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -957,8 +1047,8 @@
         <v>4.5423516666666668</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
@@ -992,8 +1082,8 @@
         <v>4.6534133333333338</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
+    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,8 +1117,8 @@
         <v>4.7638799999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -1062,8 +1152,8 @@
         <v>4.8114833333333324</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1097,7 +1187,7 @@
         <v>4.8264250000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1113,65 +1203,65 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-    </row>
-    <row r="21" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="5" t="s">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
+      <c r="F21" s="10"/>
+      <c r="G21" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
+      <c r="H21" s="10"/>
+      <c r="I21" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5" t="s">
+      <c r="J21" s="10"/>
+      <c r="K21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5" t="s">
+      <c r="L21" s="10"/>
+      <c r="M21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5" t="s">
+      <c r="N21" s="10"/>
+      <c r="O21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="9"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
@@ -1215,8 +1305,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1250,8 +1340,8 @@
         <v>5.0488966666666668</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1285,8 +1375,8 @@
         <v>5.1872499999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1320,8 +1410,8 @@
         <v>5.2837449999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -1355,8 +1445,8 @@
         <v>5.3037416666666672</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -1390,63 +1480,63 @@
         <v>5.3196750000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8" t="s">
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-    </row>
-    <row r="29" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="5" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+    </row>
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5" t="s">
+      <c r="F29" s="10"/>
+      <c r="G29" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5" t="s">
+      <c r="H29" s="10"/>
+      <c r="I29" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5" t="s">
+      <c r="J29" s="10"/>
+      <c r="K29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5" t="s">
+      <c r="L29" s="10"/>
+      <c r="M29" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5" t="s">
+      <c r="N29" s="10"/>
+      <c r="O29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P29" s="5"/>
-    </row>
-    <row r="30" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="9"/>
+      <c r="P29" s="10"/>
+    </row>
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="2" t="s">
         <v>15</v>
       </c>
@@ -1490,8 +1580,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
+    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
@@ -1525,8 +1615,8 @@
         <v>4.8456049999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
+    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -1560,8 +1650,8 @@
         <v>4.99465</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
+    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="8"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -1595,8 +1685,8 @@
         <v>5.0611016666666666</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
+    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1630,8 +1720,8 @@
         <v>5.1301250000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8"/>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
@@ -1665,7 +1755,7 @@
         <v>5.1021666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1681,7 +1771,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1697,65 +1787,65 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="8" t="s">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-    </row>
-    <row r="39" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
-      <c r="B39" s="5" t="s">
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+    </row>
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="8"/>
+      <c r="B39" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5" t="s">
+      <c r="D39" s="10"/>
+      <c r="E39" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5" t="s">
+      <c r="F39" s="10"/>
+      <c r="G39" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5" t="s">
+      <c r="H39" s="10"/>
+      <c r="I39" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5" t="s">
+      <c r="J39" s="10"/>
+      <c r="K39" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5" t="s">
+      <c r="L39" s="10"/>
+      <c r="M39" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5" t="s">
+      <c r="N39" s="10"/>
+      <c r="O39" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P39" s="5"/>
-    </row>
-    <row r="40" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="9"/>
+      <c r="P39" s="10"/>
+    </row>
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="8"/>
+      <c r="B40" s="11"/>
       <c r="C40" s="2" t="s">
         <v>15</v>
       </c>
@@ -1799,8 +1889,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="8"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -1834,8 +1924,8 @@
         <v>4.8278233333333338</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="8"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1869,8 +1959,8 @@
         <v>5.113105</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7"/>
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -1904,103 +1994,133 @@
         <v>5.3052933333333332</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7"/>
+    <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3">
+        <v>5.45756</v>
+      </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3">
+        <v>6.0939899999999998</v>
+      </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
+      <c r="H44" s="3">
+        <v>5.5139899999999997</v>
+      </c>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
+      <c r="J44" s="3">
+        <v>5.2473900000000002</v>
+      </c>
       <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="L44" s="3">
+        <v>5.1256199999999996</v>
+      </c>
       <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
+      <c r="N44" s="3">
+        <v>4.9132999999999996</v>
+      </c>
       <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="7"/>
+      <c r="P44" s="3">
+        <f>AVERAGE(D44,F44,H44,J44,L44,N44)</f>
+        <v>5.3919749999999995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="4">
+        <v>5.4647899999999998</v>
+      </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="F45" s="4">
+        <v>6.1206399999999999</v>
+      </c>
       <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="H45" s="4">
+        <v>5.5117900000000004</v>
+      </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
+      <c r="J45" s="4">
+        <v>5.2759</v>
+      </c>
       <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
+      <c r="L45" s="4">
+        <v>5.1492000000000004</v>
+      </c>
       <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
+      <c r="N45" s="4">
+        <v>4.9018199999999998</v>
+      </c>
       <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-    </row>
-    <row r="46" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7"/>
-      <c r="B46" s="8" t="s">
+      <c r="P45" s="4">
+        <f>AVERAGE(D45,F45,H45,J45,L45,N45)</f>
+        <v>5.4040233333333338</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-    </row>
-    <row r="47" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7"/>
-      <c r="B47" s="5" t="s">
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+    </row>
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5" t="s">
+      <c r="D47" s="10"/>
+      <c r="E47" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5" t="s">
+      <c r="F47" s="10"/>
+      <c r="G47" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5" t="s">
+      <c r="H47" s="10"/>
+      <c r="I47" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5" t="s">
+      <c r="J47" s="10"/>
+      <c r="K47" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5" t="s">
+      <c r="L47" s="10"/>
+      <c r="M47" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5" t="s">
+      <c r="N47" s="10"/>
+      <c r="O47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P47" s="5"/>
-    </row>
-    <row r="48" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="9"/>
+      <c r="P47" s="10"/>
+    </row>
+    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="11"/>
       <c r="C48" s="2" t="s">
         <v>15</v>
       </c>
@@ -2044,8 +2164,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -2079,8 +2199,8 @@
         <v>4.6474716666666662</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="8"/>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
@@ -2114,8 +2234,8 @@
         <v>4.9287549999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7"/>
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="8"/>
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
@@ -2149,47 +2269,77 @@
         <v>5.0942966666666676</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7"/>
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3">
+        <v>5.2426599999999999</v>
+      </c>
       <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3">
+        <v>5.7818800000000001</v>
+      </c>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
+      <c r="H52" s="3">
+        <v>5.4486800000000004</v>
+      </c>
       <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
+      <c r="J52" s="3">
+        <v>5.1177400000000004</v>
+      </c>
       <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
+      <c r="L52" s="3">
+        <v>4.8524399999999996</v>
+      </c>
       <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
+      <c r="N52" s="3">
+        <v>4.7699400000000001</v>
+      </c>
       <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7"/>
+      <c r="P52" s="3">
+        <f>AVERAGE(D52,F52,H52,J52,L52,N52)</f>
+        <v>5.2022233333333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="D53" s="4">
+        <v>5.2222999999999997</v>
+      </c>
       <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="F53" s="4">
+        <v>5.7977800000000004</v>
+      </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
+      <c r="H53" s="4">
+        <v>5.4139999999999997</v>
+      </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
+      <c r="J53" s="4">
+        <v>5.0881499999999997</v>
+      </c>
       <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
+      <c r="L53" s="4">
+        <v>4.8854499999999996</v>
+      </c>
       <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
+      <c r="N53" s="4">
+        <v>4.7302400000000002</v>
+      </c>
       <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-    </row>
-    <row r="54" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P53" s="4">
+        <f>AVERAGE(D53,F53,H53,J53,L53,N53)</f>
+        <v>5.1896533333333332</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -2205,65 +2355,65 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
     </row>
-    <row r="56" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="8" t="s">
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-    </row>
-    <row r="57" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="7"/>
-      <c r="B57" s="5" t="s">
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+    </row>
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8"/>
+      <c r="B57" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5" t="s">
+      <c r="D57" s="10"/>
+      <c r="E57" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5" t="s">
+      <c r="F57" s="10"/>
+      <c r="G57" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5" t="s">
+      <c r="H57" s="10"/>
+      <c r="I57" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5" t="s">
+      <c r="J57" s="10"/>
+      <c r="K57" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5" t="s">
+      <c r="L57" s="10"/>
+      <c r="M57" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5" t="s">
+      <c r="N57" s="10"/>
+      <c r="O57" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P57" s="5"/>
-    </row>
-    <row r="58" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7"/>
-      <c r="B58" s="9"/>
+      <c r="P57" s="10"/>
+    </row>
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="11"/>
       <c r="C58" s="2" t="s">
         <v>15</v>
       </c>
@@ -2307,238 +2457,238 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7"/>
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="8"/>
       <c r="B59" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
-        <v>4.7237600000000004</v>
+        <v>5.2073999999999998</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3">
-        <v>5.4169700000000001</v>
+        <v>5.8605600000000004</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3">
-        <v>4.7933399999999997</v>
+        <v>5.31914</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3">
-        <v>4.5930299999999997</v>
+        <v>5.0819999999999999</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3">
-        <v>4.37033</v>
+        <v>4.8082599999999998</v>
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3">
-        <v>4.1235600000000003</v>
+        <v>4.6433400000000002</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3">
         <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
-        <v>4.6701649999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7"/>
+        <v>5.1534500000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
       <c r="B60" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
-        <v>4.9773500000000004</v>
+        <v>5.3815099999999996</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3">
-        <v>5.6767399999999997</v>
+        <v>6.0031100000000004</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3">
-        <v>5.0666599999999997</v>
+        <v>5.4532499999999997</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3">
-        <v>4.8805199999999997</v>
+        <v>5.3174299999999999</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3">
-        <v>4.6018600000000003</v>
+        <v>4.9750399999999999</v>
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3">
-        <v>4.3956900000000001</v>
+        <v>4.8680300000000001</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3">
         <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
-        <v>4.9331366666666669</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="7"/>
+        <v>5.3330616666666666</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="8"/>
       <c r="B61" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3">
-        <v>5.1006499999999999</v>
+        <v>5.5081300000000004</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3">
-        <v>5.8121</v>
+        <v>6.0905899999999997</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3">
-        <v>5.21882</v>
+        <v>5.5952700000000002</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3">
-        <v>5.0633699999999999</v>
+        <v>5.4570299999999996</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3">
-        <v>4.7288600000000001</v>
+        <v>5.1396499999999996</v>
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3">
-        <v>4.5111400000000001</v>
+        <v>5.0198400000000003</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3">
         <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
-        <v>5.0724900000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="7"/>
+        <v>5.4684183333333332</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
       <c r="B62" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
-        <v>5.1421799999999998</v>
+        <v>5.5651700000000002</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3">
-        <v>5.8545800000000003</v>
+        <v>6.1571400000000001</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3">
-        <v>5.2994899999999996</v>
+        <v>5.5857700000000001</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3">
-        <v>5.1080399999999999</v>
+        <v>5.5197099999999999</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3">
-        <v>4.7957599999999996</v>
+        <v>5.2210999999999999</v>
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="3">
-        <v>4.6078999999999999</v>
+        <v>5.1161700000000003</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3">
         <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
-        <v>5.1346583333333333</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="7"/>
+        <v>5.5275099999999995</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
       <c r="B63" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="4">
-        <v>5.18682</v>
+        <v>5.5830399999999996</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4">
-        <v>5.8269299999999999</v>
+        <v>6.1738900000000001</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4">
-        <v>5.3310199999999996</v>
+        <v>5.6955600000000004</v>
       </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4">
-        <v>5.1258499999999998</v>
+        <v>5.5742200000000004</v>
       </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4">
-        <v>4.8208500000000001</v>
+        <v>5.2870999999999997</v>
       </c>
       <c r="M63" s="4"/>
       <c r="N63" s="4">
-        <v>4.6295500000000001</v>
+        <v>5.2011099999999999</v>
       </c>
       <c r="O63" s="4"/>
       <c r="P63" s="4">
         <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
-        <v>5.1535033333333331</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8" t="s">
+        <v>5.5858200000000009</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-    </row>
-    <row r="65" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="7"/>
-      <c r="B65" s="5" t="s">
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5" t="s">
+      <c r="D65" s="10"/>
+      <c r="E65" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5" t="s">
+      <c r="F65" s="10"/>
+      <c r="G65" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5" t="s">
+      <c r="H65" s="10"/>
+      <c r="I65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5" t="s">
+      <c r="J65" s="10"/>
+      <c r="K65" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5" t="s">
+      <c r="L65" s="10"/>
+      <c r="M65" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5" t="s">
+      <c r="N65" s="10"/>
+      <c r="O65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P65" s="5"/>
-    </row>
-    <row r="66" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7"/>
-      <c r="B66" s="9"/>
+      <c r="P65" s="10"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="11"/>
       <c r="C66" s="2" t="s">
         <v>15</v>
       </c>
@@ -2582,187 +2732,1569 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7"/>
+    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="8"/>
       <c r="B67" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3">
-        <v>4.5262000000000002</v>
+        <v>4.9480500000000003</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3">
-        <v>5.1717599999999999</v>
+        <v>5.4515700000000002</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3">
-        <v>4.7594000000000003</v>
+        <v>5.2034700000000003</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3">
-        <v>4.4965999999999999</v>
+        <v>4.9538700000000002</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>4.0846099999999996</v>
+        <v>4.6159699999999999</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3">
-        <v>4.0165800000000003</v>
+        <v>4.49674</v>
       </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3">
         <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
-        <v>4.5091916666666672</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7"/>
+        <v>4.9449450000000006</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="8"/>
       <c r="B68" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3">
-        <v>4.8009000000000004</v>
+        <v>5.1192900000000003</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3">
-        <v>5.3028599999999999</v>
+        <v>5.7098199999999997</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3">
-        <v>5.0737100000000002</v>
+        <v>5.4138599999999997</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3">
-        <v>4.7705099999999998</v>
+        <v>5.0689299999999999</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3">
-        <v>4.3765799999999997</v>
+        <v>4.76905</v>
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3">
-        <v>4.1800800000000002</v>
+        <v>4.7179200000000003</v>
       </c>
       <c r="O68" s="3"/>
       <c r="P68" s="3">
         <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
-        <v>4.750773333333334</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="7"/>
+        <v>5.1331449999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
       <c r="B69" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3">
-        <v>4.8427899999999999</v>
+        <v>5.2209700000000003</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3">
-        <v>5.4260799999999998</v>
+        <v>5.8197700000000001</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3">
-        <v>5.3422499999999999</v>
+        <v>5.5050100000000004</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3">
-        <v>4.9078900000000001</v>
+        <v>5.3612900000000003</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3">
-        <v>4.5387500000000003</v>
+        <v>4.9223499999999998</v>
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3">
-        <v>4.3954199999999997</v>
+        <v>4.8206100000000003</v>
       </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3">
         <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
-        <v>4.9088633333333336</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7"/>
+        <v>5.2749999999999995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="8"/>
       <c r="B70" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3">
-        <v>4.9710700000000001</v>
+        <v>5.2853000000000003</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3">
-        <v>5.4894499999999997</v>
+        <v>5.78003</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3">
-        <v>5.2308899999999996</v>
+        <v>5.5651999999999999</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3">
-        <v>4.8858800000000002</v>
+        <v>5.2809499999999998</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="3">
-        <v>4.5251400000000004</v>
+        <v>4.9378000000000002</v>
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3">
-        <v>4.47593</v>
+        <v>4.8616700000000002</v>
       </c>
       <c r="O70" s="3"/>
       <c r="P70" s="3">
         <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
-        <v>4.9297266666666664</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="7"/>
+        <v>5.2851583333333334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
       <c r="B71" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4">
-        <v>4.9133500000000003</v>
+        <v>5.3318000000000003</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4">
-        <v>5.5378100000000003</v>
+        <v>5.8621400000000001</v>
       </c>
       <c r="G71" s="4"/>
       <c r="H71" s="4">
-        <v>5.2631699999999997</v>
+        <v>5.5247900000000003</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4">
-        <v>4.8795099999999998</v>
+        <v>5.3355199999999998</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4">
-        <v>4.5223500000000003</v>
+        <v>4.9871299999999996</v>
       </c>
       <c r="M71" s="4"/>
       <c r="N71" s="4">
-        <v>4.4981600000000004</v>
+        <v>5.0164600000000004</v>
       </c>
       <c r="O71" s="4"/>
       <c r="P71" s="4">
         <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+        <v>5.3429733333333331</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
+      <c r="N74" s="9"/>
+      <c r="O74" s="9"/>
+      <c r="P74" s="9"/>
+    </row>
+    <row r="75" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="8"/>
+      <c r="B75" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="10"/>
+      <c r="G75" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="10"/>
+    </row>
+    <row r="76" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="8"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="8"/>
+      <c r="B77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>4.7237600000000004</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3">
+        <v>5.4169700000000001</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3">
+        <v>4.7933399999999997</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3">
+        <v>4.5930299999999997</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>4.37033</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>4.1235600000000003</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3">
+        <f>AVERAGE(D77,F77,H77,J77,L77,N77)</f>
+        <v>4.6701649999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="8"/>
+      <c r="B78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>4.9773500000000004</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <v>5.6767399999999997</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
+        <v>5.0666599999999997</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3">
+        <v>4.8805199999999997</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>4.6018600000000003</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3">
+        <v>4.3956900000000001</v>
+      </c>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3">
+        <f>AVERAGE(D78,F78,H78,J78,L78,N78)</f>
+        <v>4.9331366666666669</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="8"/>
+      <c r="B79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3">
+        <v>5.1006499999999999</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
+        <v>5.8121</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3">
+        <v>5.21882</v>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3">
+        <v>5.0633699999999999</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3">
+        <v>4.7288600000000001</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>4.5111400000000001</v>
+      </c>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3">
+        <f>AVERAGE(D79,F79,H79,J79,L79,N79)</f>
+        <v>5.0724900000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="8"/>
+      <c r="B80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3">
+        <v>5.1421799999999998</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3">
+        <v>5.8545800000000003</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3">
+        <v>5.2994899999999996</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3">
+        <v>5.1080399999999999</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3">
+        <v>4.7957599999999996</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3">
+        <v>4.6078999999999999</v>
+      </c>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3">
+        <f>AVERAGE(D80,F80,H80,J80,L80,N80)</f>
+        <v>5.1346583333333333</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="8"/>
+      <c r="B81" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4">
+        <v>5.18682</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4">
+        <v>5.8269299999999999</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4">
+        <v>5.3310199999999996</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4">
+        <v>5.1258499999999998</v>
+      </c>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4">
+        <v>4.8208500000000001</v>
+      </c>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4">
+        <v>4.6295500000000001</v>
+      </c>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4">
+        <f>AVERAGE(D81,F81,H81,J81,L81,N81)</f>
+        <v>5.1535033333333331</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="9"/>
+      <c r="N82" s="9"/>
+      <c r="O82" s="9"/>
+      <c r="P82" s="9"/>
+    </row>
+    <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8"/>
+      <c r="B83" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="10"/>
+      <c r="K83" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N83" s="10"/>
+      <c r="O83" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P83" s="10"/>
+    </row>
+    <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="8"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8"/>
+      <c r="B85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3">
+        <v>4.5262000000000002</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3">
+        <v>5.1717599999999999</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3">
+        <v>4.7594000000000003</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3">
+        <v>4.4965999999999999</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3">
+        <v>4.0846099999999996</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3">
+        <v>4.0165800000000003</v>
+      </c>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3">
+        <f>AVERAGE(D85,F85,H85,J85,L85,N85)</f>
+        <v>4.5091916666666672</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="8"/>
+      <c r="B86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3">
+        <v>4.8009000000000004</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3">
+        <v>5.3028599999999999</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3">
+        <v>5.0737100000000002</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3">
+        <v>4.7705099999999998</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3">
+        <v>4.3765799999999997</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3">
+        <v>4.1800800000000002</v>
+      </c>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3">
+        <f>AVERAGE(D86,F86,H86,J86,L86,N86)</f>
+        <v>4.750773333333334</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3">
+        <v>4.8427899999999999</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3">
+        <v>5.4260799999999998</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3">
+        <v>5.3422499999999999</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3">
+        <v>4.9078900000000001</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3">
+        <v>4.5387500000000003</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3">
+        <v>4.3954199999999997</v>
+      </c>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3">
+        <f>AVERAGE(D87,F87,H87,J87,L87,N87)</f>
+        <v>4.9088633333333336</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="8"/>
+      <c r="B88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>4.9710700000000001</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3">
+        <v>5.4894499999999997</v>
+      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3">
+        <v>5.2308899999999996</v>
+      </c>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3">
+        <v>4.8858800000000002</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3">
+        <v>4.5251400000000004</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3">
+        <v>4.47593</v>
+      </c>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3">
+        <f>AVERAGE(D88,F88,H88,J88,L88,N88)</f>
+        <v>4.9297266666666664</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="8"/>
+      <c r="B89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4">
+        <v>4.9133500000000003</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4">
+        <v>5.5378100000000003</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4">
+        <v>5.2631699999999997</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4">
+        <v>4.8795099999999998</v>
+      </c>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4">
+        <v>4.5223500000000003</v>
+      </c>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4">
+        <v>4.4981600000000004</v>
+      </c>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4">
+        <f>AVERAGE(D89,F89,H89,J89,L89,N89)</f>
         <v>4.9357250000000006</v>
       </c>
     </row>
+    <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="N92" s="9"/>
+      <c r="O92" s="9"/>
+      <c r="P92" s="9"/>
+    </row>
+    <row r="93" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="8"/>
+      <c r="B93" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J93" s="10"/>
+      <c r="K93" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L93" s="10"/>
+      <c r="M93" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N93" s="10"/>
+      <c r="O93" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P93" s="10"/>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="8"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="8"/>
+      <c r="B95" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3">
+        <v>4.8117299999999998</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3">
+        <v>5.4849600000000001</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3">
+        <v>4.9283900000000003</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3">
+        <v>4.6700100000000004</v>
+      </c>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3">
+        <v>4.40869</v>
+      </c>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3">
+        <v>4.2693899999999996</v>
+      </c>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3">
+        <f>AVERAGE(D95,F95,H95,J95,L95,N95)</f>
+        <v>4.7621949999999993</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+      <c r="B96" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3">
+        <v>4.7237600000000004</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3">
+        <v>5.4169700000000001</v>
+      </c>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3">
+        <v>4.7933399999999997</v>
+      </c>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3">
+        <v>4.5930299999999997</v>
+      </c>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3">
+        <v>4.37033</v>
+      </c>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3">
+        <v>4.1235600000000003</v>
+      </c>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3">
+        <f>AVERAGE(D96,F96,H96,J96,L96,N96)</f>
+        <v>4.6701649999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="8"/>
+      <c r="B97" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3">
+        <v>3.02467</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3">
+        <v>3.1975899999999999</v>
+      </c>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3">
+        <v>3.04508</v>
+      </c>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3">
+        <v>3.0737199999999998</v>
+      </c>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3">
+        <v>2.8365</v>
+      </c>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3">
+        <v>2.9474800000000001</v>
+      </c>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3">
+        <f>AVERAGE(D97,F97,H97,J97,L97,N97)</f>
+        <v>3.0208399999999997</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="8"/>
+      <c r="B98" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+    </row>
+    <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L99" s="10"/>
+      <c r="M99" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N99" s="10"/>
+      <c r="O99" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P99" s="10"/>
+    </row>
+    <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8"/>
+      <c r="B101" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3">
+        <v>4.5697099999999997</v>
+      </c>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3">
+        <v>5.1458199999999996</v>
+      </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3">
+        <v>4.9436099999999996</v>
+      </c>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3">
+        <v>4.5331599999999996</v>
+      </c>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3">
+        <v>4.25556</v>
+      </c>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3">
+        <v>4.1576599999999999</v>
+      </c>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3">
+        <f>AVERAGE(D101,F101,H101,J101,L101,N101)</f>
+        <v>4.6009199999999995</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3">
+        <v>4.5262000000000002</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3">
+        <v>5.1717599999999999</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3">
+        <v>4.7594000000000003</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3">
+        <v>4.4965999999999999</v>
+      </c>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3">
+        <v>4.0846099999999996</v>
+      </c>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3">
+        <v>4.0165800000000003</v>
+      </c>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3">
+        <f>AVERAGE(D102,F102,H102,J102,L102,N102)</f>
+        <v>4.5091916666666672</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4">
+        <v>2.9611100000000001</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4">
+        <v>3.1002999999999998</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4">
+        <v>3.0455999999999999</v>
+      </c>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4">
+        <v>3.0547200000000001</v>
+      </c>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4">
+        <v>2.79765</v>
+      </c>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4">
+        <v>2.9202699999999999</v>
+      </c>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4">
+        <f>AVERAGE(D103,F103,H103,J103,L103,N103)</f>
+        <v>2.9799416666666665</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9"/>
+      <c r="O106" s="9"/>
+      <c r="P106" s="9"/>
+    </row>
+    <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8"/>
+      <c r="B107" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F107" s="10"/>
+      <c r="G107" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L107" s="10"/>
+      <c r="M107" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N107" s="10"/>
+      <c r="O107" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P107" s="10"/>
+    </row>
+    <row r="108" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="8"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8"/>
+      <c r="B109" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3">
+        <v>5.09335</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3">
+        <v>5.8246799999999999</v>
+      </c>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3">
+        <v>5.1640100000000002</v>
+      </c>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3">
+        <v>4.8891099999999996</v>
+      </c>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3">
+        <v>4.7041199999999996</v>
+      </c>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3">
+        <v>4.5401699999999998</v>
+      </c>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3">
+        <f>AVERAGE(D109,F109,H109,J109,L109,N109)</f>
+        <v>5.0359066666666665</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="8"/>
+      <c r="B110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3">
+        <v>4.7492799999999997</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3">
+        <v>5.5074500000000004</v>
+      </c>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3">
+        <v>4.83683</v>
+      </c>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3">
+        <v>4.5345500000000003</v>
+      </c>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3">
+        <v>4.3890599999999997</v>
+      </c>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3">
+        <v>4.0718500000000004</v>
+      </c>
+      <c r="O110" s="3"/>
+      <c r="P110" s="3">
+        <f>AVERAGE(D110,F110,H110,J110,L110,N110)</f>
+        <v>4.6815033333333336</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="8"/>
+      <c r="B111" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3">
+        <v>4.3005399999999998</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3">
+        <v>4.6823100000000002</v>
+      </c>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3">
+        <v>4.4440400000000002</v>
+      </c>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3">
+        <v>4.3711799999999998</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3">
+        <v>4.0388099999999998</v>
+      </c>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3">
+        <v>4.0564200000000001</v>
+      </c>
+      <c r="O111" s="3"/>
+      <c r="P111" s="3">
+        <f>AVERAGE(D111,F111,H111,J111,L111,N111)</f>
+        <v>4.31555</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="8"/>
+      <c r="B112" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+    </row>
+    <row r="113" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="8"/>
+      <c r="B113" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F113" s="10"/>
+      <c r="G113" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H113" s="10"/>
+      <c r="I113" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J113" s="10"/>
+      <c r="K113" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L113" s="10"/>
+      <c r="M113" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="N113" s="10"/>
+      <c r="O113" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P113" s="10"/>
+    </row>
+    <row r="114" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="8"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="8"/>
+      <c r="B115" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3">
+        <v>4.8830299999999998</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3">
+        <v>5.4337900000000001</v>
+      </c>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3">
+        <v>5.15395</v>
+      </c>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3">
+        <v>4.66831</v>
+      </c>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3">
+        <v>4.4721200000000003</v>
+      </c>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3">
+        <v>4.3131700000000004</v>
+      </c>
+      <c r="O115" s="3"/>
+      <c r="P115" s="3">
+        <f>AVERAGE(D115,F115,H115,J115,L115,N115)</f>
+        <v>4.8207283333333333</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="8"/>
+      <c r="B116" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3">
+        <v>4.5984499999999997</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3">
+        <v>5.0827600000000004</v>
+      </c>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3">
+        <v>4.8210600000000001</v>
+      </c>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3">
+        <v>4.5414899999999996</v>
+      </c>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3">
+        <v>4.1288200000000002</v>
+      </c>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3">
+        <v>4.0509300000000001</v>
+      </c>
+      <c r="O116" s="3"/>
+      <c r="P116" s="3">
+        <f>AVERAGE(D116,F116,H116,J116,L116,N116)</f>
+        <v>4.5372516666666671</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="8"/>
+      <c r="B117" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4">
+        <v>4.1373300000000004</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4">
+        <v>4.50509</v>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4">
+        <v>4.4094199999999999</v>
+      </c>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4">
+        <v>4.2390699999999999</v>
+      </c>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4">
+        <v>3.9544199999999998</v>
+      </c>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4">
+        <v>3.9953799999999999</v>
+      </c>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4">
+        <f>AVERAGE(D117,F117,H117,J117,L117,N117)</f>
+        <v>4.2067850000000009</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="A2:A17"/>
-    <mergeCell ref="A20:A35"/>
+  <mergeCells count="133">
     <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
     <mergeCell ref="B64:P64"/>
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="C65:D65"/>
@@ -2772,55 +4304,46 @@
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="M65:N65"/>
     <mergeCell ref="O65:P65"/>
-    <mergeCell ref="B56:P56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B10:P10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="O113:P113"/>
+    <mergeCell ref="A106:A117"/>
+    <mergeCell ref="B106:P106"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="B112:P112"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="A92:A103"/>
+    <mergeCell ref="B92:P92"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="O93:P93"/>
+    <mergeCell ref="B98:P98"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="O99:P99"/>
     <mergeCell ref="B20:P20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="O47:P47"/>
     <mergeCell ref="A38:A53"/>
     <mergeCell ref="B38:P38"/>
     <mergeCell ref="B39:B40"/>
@@ -2835,8 +4358,69 @@
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B10:P10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A74:A89"/>
+    <mergeCell ref="B82:P82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="B74:P74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43FF8191-08A4-4D1F-88EE-D73457FD1B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F304A2-2891-4E03-87A7-8FFF723E6508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
   <sheets>
     <sheet name="llama2-7b" sheetId="1" r:id="rId1"/>
+    <sheet name="llama3-8b-5" sheetId="3" r:id="rId2"/>
+    <sheet name="llama3-8b-7" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="45">
   <si>
     <t>Data Num.</t>
   </si>
@@ -184,6 +186,46 @@
     <t>800k (epoch=5)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>total-token=60
+depth=5
+top-k=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>total-token=60
+depth=7
+top-k=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eagle3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100k (epoch=8)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200k (epoch=6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400k (epoch=5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600k (epoch=4)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800k (epoch=3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -277,7 +319,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -299,6 +341,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -312,6 +357,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -636,64 +687,64 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
+      <c r="H3" s="11"/>
+      <c r="I3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10" t="s">
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10" t="s">
+      <c r="L3" s="11"/>
+      <c r="M3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10" t="s">
+      <c r="N3" s="11"/>
+      <c r="O3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="10"/>
+      <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
@@ -738,7 +789,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -773,7 +824,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
@@ -808,7 +859,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
@@ -843,7 +894,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
@@ -878,7 +929,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="9"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -913,62 +964,62 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10" t="s">
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10" t="s">
+      <c r="L11" s="11"/>
+      <c r="M11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10" t="s">
+      <c r="N11" s="11"/>
+      <c r="O11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P11" s="10"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
@@ -1013,7 +1064,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="9"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1048,7 +1099,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="9"/>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,7 +1134,7 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="9"/>
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1118,7 +1169,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="9"/>
       <c r="B16" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,7 +1204,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="9"/>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1204,64 +1255,64 @@
       <c r="P18" s="3"/>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="10" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10" t="s">
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10" t="s">
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10" t="s">
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10" t="s">
+      <c r="J21" s="11"/>
+      <c r="K21" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10" t="s">
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10" t="s">
+      <c r="N21" s="11"/>
+      <c r="O21" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P21" s="10"/>
+      <c r="P21" s="11"/>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
@@ -1306,7 +1357,7 @@
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="9"/>
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +1392,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="9"/>
       <c r="B24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1376,7 +1427,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="9"/>
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1411,7 +1462,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
+      <c r="A26" s="9"/>
       <c r="B26" s="1" t="s">
         <v>11</v>
       </c>
@@ -1446,7 +1497,7 @@
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
+      <c r="A27" s="9"/>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
@@ -1481,62 +1532,62 @@
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="10" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10" t="s">
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10" t="s">
+      <c r="F29" s="11"/>
+      <c r="G29" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10" t="s">
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10" t="s">
+      <c r="J29" s="11"/>
+      <c r="K29" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10" t="s">
+      <c r="L29" s="11"/>
+      <c r="M29" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10" t="s">
+      <c r="N29" s="11"/>
+      <c r="O29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P29" s="10"/>
+      <c r="P29" s="11"/>
     </row>
     <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="12"/>
       <c r="C30" s="2" t="s">
         <v>15</v>
       </c>
@@ -1581,7 +1632,7 @@
       </c>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
+      <c r="A31" s="9"/>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
@@ -1616,7 +1667,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
+      <c r="A32" s="9"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -1651,7 +1702,7 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
+      <c r="A33" s="9"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +1737,7 @@
       </c>
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
+      <c r="A34" s="9"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1721,7 +1772,7 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
+      <c r="A35" s="9"/>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
@@ -1788,64 +1839,64 @@
       <c r="P37" s="3"/>
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
     </row>
     <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="10" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10" t="s">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10" t="s">
+      <c r="F39" s="11"/>
+      <c r="G39" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10" t="s">
+      <c r="H39" s="11"/>
+      <c r="I39" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10" t="s">
+      <c r="J39" s="11"/>
+      <c r="K39" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10" t="s">
+      <c r="L39" s="11"/>
+      <c r="M39" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10" t="s">
+      <c r="N39" s="11"/>
+      <c r="O39" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P39" s="10"/>
+      <c r="P39" s="11"/>
     </row>
     <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="12"/>
       <c r="C40" s="2" t="s">
         <v>15</v>
       </c>
@@ -1890,7 +1941,7 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
+      <c r="A41" s="9"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
@@ -1925,7 +1976,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
+      <c r="A42" s="9"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1960,7 +2011,7 @@
       </c>
     </row>
     <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
+      <c r="A43" s="9"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -1995,7 +2046,7 @@
       </c>
     </row>
     <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
+      <c r="A44" s="9"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -2030,7 +2081,7 @@
       </c>
     </row>
     <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
+      <c r="A45" s="9"/>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2065,62 +2116,62 @@
       </c>
     </row>
     <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
     </row>
     <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="10" t="s">
+      <c r="A47" s="9"/>
+      <c r="B47" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10" t="s">
+      <c r="D47" s="11"/>
+      <c r="E47" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10" t="s">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10" t="s">
+      <c r="H47" s="11"/>
+      <c r="I47" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10" t="s">
+      <c r="J47" s="11"/>
+      <c r="K47" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10" t="s">
+      <c r="L47" s="11"/>
+      <c r="M47" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10" t="s">
+      <c r="N47" s="11"/>
+      <c r="O47" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P47" s="10"/>
+      <c r="P47" s="11"/>
     </row>
     <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="12"/>
       <c r="C48" s="2" t="s">
         <v>15</v>
       </c>
@@ -2165,7 +2216,7 @@
       </c>
     </row>
     <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
+      <c r="A49" s="9"/>
       <c r="B49" s="1" t="s">
         <v>8</v>
       </c>
@@ -2200,7 +2251,7 @@
       </c>
     </row>
     <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
+      <c r="A50" s="9"/>
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
@@ -2235,7 +2286,7 @@
       </c>
     </row>
     <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
+      <c r="A51" s="9"/>
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
@@ -2270,7 +2321,7 @@
       </c>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
+      <c r="A52" s="9"/>
       <c r="B52" s="1" t="s">
         <v>11</v>
       </c>
@@ -2305,7 +2356,7 @@
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
+      <c r="A53" s="9"/>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2356,64 +2407,64 @@
       <c r="P54" s="3"/>
     </row>
     <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="10" t="s">
+      <c r="A57" s="9"/>
+      <c r="B57" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10" t="s">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10" t="s">
+      <c r="F57" s="11"/>
+      <c r="G57" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10" t="s">
+      <c r="H57" s="11"/>
+      <c r="I57" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10" t="s">
+      <c r="J57" s="11"/>
+      <c r="K57" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10" t="s">
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10" t="s">
+      <c r="N57" s="11"/>
+      <c r="O57" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P57" s="10"/>
+      <c r="P57" s="11"/>
     </row>
     <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="12"/>
       <c r="C58" s="2" t="s">
         <v>15</v>
       </c>
@@ -2458,7 +2509,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
+      <c r="A59" s="9"/>
       <c r="B59" s="1" t="s">
         <v>31</v>
       </c>
@@ -2493,7 +2544,7 @@
       </c>
     </row>
     <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
+      <c r="A60" s="9"/>
       <c r="B60" s="1" t="s">
         <v>32</v>
       </c>
@@ -2528,7 +2579,7 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
+      <c r="A61" s="9"/>
       <c r="B61" s="1" t="s">
         <v>33</v>
       </c>
@@ -2563,7 +2614,7 @@
       </c>
     </row>
     <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
+      <c r="A62" s="9"/>
       <c r="B62" s="1" t="s">
         <v>34</v>
       </c>
@@ -2598,7 +2649,7 @@
       </c>
     </row>
     <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
+      <c r="A63" s="9"/>
       <c r="B63" s="2" t="s">
         <v>35</v>
       </c>
@@ -2633,62 +2684,62 @@
       </c>
     </row>
     <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9" t="s">
+      <c r="A64" s="9"/>
+      <c r="B64" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
     </row>
     <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="10" t="s">
+      <c r="A65" s="9"/>
+      <c r="B65" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10" t="s">
+      <c r="D65" s="11"/>
+      <c r="E65" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10" t="s">
+      <c r="F65" s="11"/>
+      <c r="G65" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10" t="s">
+      <c r="H65" s="11"/>
+      <c r="I65" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10" t="s">
+      <c r="J65" s="11"/>
+      <c r="K65" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10" t="s">
+      <c r="L65" s="11"/>
+      <c r="M65" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10" t="s">
+      <c r="N65" s="11"/>
+      <c r="O65" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P65" s="10"/>
+      <c r="P65" s="11"/>
     </row>
     <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="12"/>
       <c r="C66" s="2" t="s">
         <v>15</v>
       </c>
@@ -2733,7 +2784,7 @@
       </c>
     </row>
     <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
+      <c r="A67" s="9"/>
       <c r="B67" s="1" t="s">
         <v>31</v>
       </c>
@@ -2768,7 +2819,7 @@
       </c>
     </row>
     <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
+      <c r="A68" s="9"/>
       <c r="B68" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,7 +2854,7 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
+      <c r="A69" s="9"/>
       <c r="B69" s="1" t="s">
         <v>33</v>
       </c>
@@ -2838,7 +2889,7 @@
       </c>
     </row>
     <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
+      <c r="A70" s="9"/>
       <c r="B70" s="1" t="s">
         <v>34</v>
       </c>
@@ -2873,7 +2924,7 @@
       </c>
     </row>
     <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
+      <c r="A71" s="9"/>
       <c r="B71" s="2" t="s">
         <v>35</v>
       </c>
@@ -2908,64 +2959,64 @@
       </c>
     </row>
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
-      <c r="M74" s="9"/>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
     </row>
     <row r="75" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="10" t="s">
+      <c r="A75" s="9"/>
+      <c r="B75" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10" t="s">
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10" t="s">
+      <c r="F75" s="11"/>
+      <c r="G75" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10" t="s">
+      <c r="H75" s="11"/>
+      <c r="I75" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10" t="s">
+      <c r="J75" s="11"/>
+      <c r="K75" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10" t="s">
+      <c r="L75" s="11"/>
+      <c r="M75" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N75" s="10"/>
-      <c r="O75" s="10" t="s">
+      <c r="N75" s="11"/>
+      <c r="O75" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P75" s="10"/>
+      <c r="P75" s="11"/>
     </row>
     <row r="76" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="11"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="12"/>
       <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
@@ -3010,7 +3061,7 @@
       </c>
     </row>
     <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
+      <c r="A77" s="9"/>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
@@ -3045,7 +3096,7 @@
       </c>
     </row>
     <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
+      <c r="A78" s="9"/>
       <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
@@ -3080,7 +3131,7 @@
       </c>
     </row>
     <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
+      <c r="A79" s="9"/>
       <c r="B79" s="1" t="s">
         <v>10</v>
       </c>
@@ -3115,7 +3166,7 @@
       </c>
     </row>
     <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
+      <c r="A80" s="9"/>
       <c r="B80" s="1" t="s">
         <v>11</v>
       </c>
@@ -3150,7 +3201,7 @@
       </c>
     </row>
     <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
+      <c r="A81" s="9"/>
       <c r="B81" s="2" t="s">
         <v>12</v>
       </c>
@@ -3185,62 +3236,62 @@
       </c>
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9" t="s">
+      <c r="A82" s="9"/>
+      <c r="B82" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="9"/>
-      <c r="K82" s="9"/>
-      <c r="L82" s="9"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
     </row>
     <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="10" t="s">
+      <c r="A83" s="9"/>
+      <c r="B83" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10" t="s">
+      <c r="D83" s="11"/>
+      <c r="E83" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10" t="s">
+      <c r="F83" s="11"/>
+      <c r="G83" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10" t="s">
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10" t="s">
+      <c r="J83" s="11"/>
+      <c r="K83" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="10"/>
-      <c r="M83" s="10" t="s">
+      <c r="L83" s="11"/>
+      <c r="M83" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N83" s="10"/>
-      <c r="O83" s="10" t="s">
+      <c r="N83" s="11"/>
+      <c r="O83" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P83" s="10"/>
+      <c r="P83" s="11"/>
     </row>
     <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="8"/>
-      <c r="B84" s="11"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="12"/>
       <c r="C84" s="2" t="s">
         <v>15</v>
       </c>
@@ -3285,7 +3336,7 @@
       </c>
     </row>
     <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
+      <c r="A85" s="9"/>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
@@ -3320,7 +3371,7 @@
       </c>
     </row>
     <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
+      <c r="A86" s="9"/>
       <c r="B86" s="1" t="s">
         <v>9</v>
       </c>
@@ -3355,7 +3406,7 @@
       </c>
     </row>
     <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
+      <c r="A87" s="9"/>
       <c r="B87" s="1" t="s">
         <v>10</v>
       </c>
@@ -3390,7 +3441,7 @@
       </c>
     </row>
     <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
+      <c r="A88" s="9"/>
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
@@ -3425,7 +3476,7 @@
       </c>
     </row>
     <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
+      <c r="A89" s="9"/>
       <c r="B89" s="2" t="s">
         <v>12</v>
       </c>
@@ -3460,64 +3511,64 @@
       </c>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
-      <c r="N92" s="9"/>
-      <c r="O92" s="9"/>
-      <c r="P92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
     </row>
     <row r="93" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="8"/>
-      <c r="B93" s="10" t="s">
+      <c r="A93" s="9"/>
+      <c r="B93" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10" t="s">
+      <c r="D93" s="11"/>
+      <c r="E93" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10" t="s">
+      <c r="F93" s="11"/>
+      <c r="G93" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10" t="s">
+      <c r="H93" s="11"/>
+      <c r="I93" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10" t="s">
+      <c r="J93" s="11"/>
+      <c r="K93" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10" t="s">
+      <c r="L93" s="11"/>
+      <c r="M93" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N93" s="10"/>
-      <c r="O93" s="10" t="s">
+      <c r="N93" s="11"/>
+      <c r="O93" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P93" s="10"/>
+      <c r="P93" s="11"/>
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="8"/>
-      <c r="B94" s="11"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="12"/>
       <c r="C94" s="2" t="s">
         <v>15</v>
       </c>
@@ -3562,7 +3613,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="8"/>
+      <c r="A95" s="9"/>
       <c r="B95" s="5" t="s">
         <v>25</v>
       </c>
@@ -3597,7 +3648,7 @@
       </c>
     </row>
     <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="8"/>
+      <c r="A96" s="9"/>
       <c r="B96" s="5" t="s">
         <v>26</v>
       </c>
@@ -3632,7 +3683,7 @@
       </c>
     </row>
     <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
+      <c r="A97" s="9"/>
       <c r="B97" s="5" t="s">
         <v>27</v>
       </c>
@@ -3667,62 +3718,62 @@
       </c>
     </row>
     <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9" t="s">
+      <c r="A98" s="9"/>
+      <c r="B98" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-      <c r="M98" s="9"/>
-      <c r="N98" s="9"/>
-      <c r="O98" s="9"/>
-      <c r="P98" s="9"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="10"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="10"/>
+      <c r="M98" s="10"/>
+      <c r="N98" s="10"/>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
     </row>
     <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="8"/>
-      <c r="B99" s="10" t="s">
+      <c r="A99" s="9"/>
+      <c r="B99" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10" t="s">
+      <c r="D99" s="11"/>
+      <c r="E99" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10" t="s">
+      <c r="F99" s="11"/>
+      <c r="G99" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10" t="s">
+      <c r="H99" s="11"/>
+      <c r="I99" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10" t="s">
+      <c r="J99" s="11"/>
+      <c r="K99" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L99" s="10"/>
-      <c r="M99" s="10" t="s">
+      <c r="L99" s="11"/>
+      <c r="M99" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N99" s="10"/>
-      <c r="O99" s="10" t="s">
+      <c r="N99" s="11"/>
+      <c r="O99" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P99" s="10"/>
+      <c r="P99" s="11"/>
     </row>
     <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
-      <c r="B100" s="11"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="12"/>
       <c r="C100" s="2" t="s">
         <v>15</v>
       </c>
@@ -3767,7 +3818,7 @@
       </c>
     </row>
     <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
+      <c r="A101" s="9"/>
       <c r="B101" s="5" t="s">
         <v>25</v>
       </c>
@@ -3802,7 +3853,7 @@
       </c>
     </row>
     <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="8"/>
+      <c r="A102" s="9"/>
       <c r="B102" s="5" t="s">
         <v>26</v>
       </c>
@@ -3837,7 +3888,7 @@
       </c>
     </row>
     <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="8"/>
+      <c r="A103" s="9"/>
       <c r="B103" s="6" t="s">
         <v>27</v>
       </c>
@@ -3872,64 +3923,64 @@
       </c>
     </row>
     <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="9"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="9"/>
-      <c r="M106" s="9"/>
-      <c r="N106" s="9"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="10"/>
+      <c r="H106" s="10"/>
+      <c r="I106" s="10"/>
+      <c r="J106" s="10"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
     </row>
     <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="8"/>
-      <c r="B107" s="10" t="s">
+      <c r="A107" s="9"/>
+      <c r="B107" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10" t="s">
+      <c r="D107" s="11"/>
+      <c r="E107" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10" t="s">
+      <c r="F107" s="11"/>
+      <c r="G107" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10" t="s">
+      <c r="H107" s="11"/>
+      <c r="I107" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10" t="s">
+      <c r="J107" s="11"/>
+      <c r="K107" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10" t="s">
+      <c r="L107" s="11"/>
+      <c r="M107" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N107" s="10"/>
-      <c r="O107" s="10" t="s">
+      <c r="N107" s="11"/>
+      <c r="O107" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P107" s="10"/>
+      <c r="P107" s="11"/>
     </row>
     <row r="108" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="8"/>
-      <c r="B108" s="11"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="12"/>
       <c r="C108" s="2" t="s">
         <v>15</v>
       </c>
@@ -3974,7 +4025,7 @@
       </c>
     </row>
     <row r="109" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="8"/>
+      <c r="A109" s="9"/>
       <c r="B109" s="1" t="s">
         <v>21</v>
       </c>
@@ -4009,7 +4060,7 @@
       </c>
     </row>
     <row r="110" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
+      <c r="A110" s="9"/>
       <c r="B110" s="1" t="s">
         <v>22</v>
       </c>
@@ -4044,7 +4095,7 @@
       </c>
     </row>
     <row r="111" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
+      <c r="A111" s="9"/>
       <c r="B111" s="1" t="s">
         <v>23</v>
       </c>
@@ -4079,62 +4130,62 @@
       </c>
     </row>
     <row r="112" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="8"/>
-      <c r="B112" s="9" t="s">
+      <c r="A112" s="9"/>
+      <c r="B112" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="9"/>
-      <c r="L112" s="9"/>
-      <c r="M112" s="9"/>
-      <c r="N112" s="9"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="10"/>
+      <c r="F112" s="10"/>
+      <c r="G112" s="10"/>
+      <c r="H112" s="10"/>
+      <c r="I112" s="10"/>
+      <c r="J112" s="10"/>
+      <c r="K112" s="10"/>
+      <c r="L112" s="10"/>
+      <c r="M112" s="10"/>
+      <c r="N112" s="10"/>
+      <c r="O112" s="10"/>
+      <c r="P112" s="10"/>
     </row>
     <row r="113" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="8"/>
-      <c r="B113" s="10" t="s">
+      <c r="A113" s="9"/>
+      <c r="B113" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C113" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D113" s="10"/>
-      <c r="E113" s="10" t="s">
+      <c r="D113" s="11"/>
+      <c r="E113" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F113" s="10"/>
-      <c r="G113" s="10" t="s">
+      <c r="F113" s="11"/>
+      <c r="G113" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10" t="s">
+      <c r="H113" s="11"/>
+      <c r="I113" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J113" s="10"/>
-      <c r="K113" s="10" t="s">
+      <c r="J113" s="11"/>
+      <c r="K113" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L113" s="10"/>
-      <c r="M113" s="10" t="s">
+      <c r="L113" s="11"/>
+      <c r="M113" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N113" s="10"/>
-      <c r="O113" s="10" t="s">
+      <c r="N113" s="11"/>
+      <c r="O113" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P113" s="10"/>
+      <c r="P113" s="11"/>
     </row>
     <row r="114" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="8"/>
-      <c r="B114" s="11"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="12"/>
       <c r="C114" s="2" t="s">
         <v>15</v>
       </c>
@@ -4179,7 +4230,7 @@
       </c>
     </row>
     <row r="115" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="8"/>
+      <c r="A115" s="9"/>
       <c r="B115" s="1" t="s">
         <v>21</v>
       </c>
@@ -4214,7 +4265,7 @@
       </c>
     </row>
     <row r="116" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="8"/>
+      <c r="A116" s="9"/>
       <c r="B116" s="1" t="s">
         <v>22</v>
       </c>
@@ -4249,7 +4300,7 @@
       </c>
     </row>
     <row r="117" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="8"/>
+      <c r="A117" s="9"/>
       <c r="B117" s="2" t="s">
         <v>23</v>
       </c>
@@ -4285,96 +4336,25 @@
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="A56:A71"/>
-    <mergeCell ref="B56:P56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="B64:P64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="M113:N113"/>
-    <mergeCell ref="O113:P113"/>
-    <mergeCell ref="A106:A117"/>
-    <mergeCell ref="B106:P106"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="G107:H107"/>
-    <mergeCell ref="I107:J107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="M107:N107"/>
-    <mergeCell ref="O107:P107"/>
-    <mergeCell ref="B112:P112"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="A92:A103"/>
-    <mergeCell ref="B92:P92"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="M93:N93"/>
-    <mergeCell ref="O93:P93"/>
-    <mergeCell ref="B98:P98"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="B20:P20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A38:A53"/>
-    <mergeCell ref="B38:P38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B46:P46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A74:A89"/>
+    <mergeCell ref="B82:P82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="B74:P74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="A20:A35"/>
     <mergeCell ref="I3:J3"/>
@@ -4399,25 +4379,5158 @@
     <mergeCell ref="B10:P10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A74:A89"/>
-    <mergeCell ref="B82:P82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="M83:N83"/>
-    <mergeCell ref="O83:P83"/>
-    <mergeCell ref="B74:P74"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="O75:P75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B20:P20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A38:A53"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A92:A103"/>
+    <mergeCell ref="B92:P92"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="O93:P93"/>
+    <mergeCell ref="B98:P98"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="O113:P113"/>
+    <mergeCell ref="A106:A117"/>
+    <mergeCell ref="B106:P106"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="B112:P112"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="B64:P64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D606126C-3FE1-428A-BDA2-93CD7E4A00CB}">
+  <dimension ref="A2:T71"/>
+  <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.58203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="R2" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="11"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>4.3087400000000002</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>5.0599699999999999</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>4.8281400000000003</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
+        <v>4.3653899999999997</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>3.9928699999999999</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
+        <v>3.6211099999999998</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3">
+        <f>AVERAGE(D5,F5,H5,J5,L5,N5)</f>
+        <v>4.3627033333333332</v>
+      </c>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>4.4191500000000001</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
+        <v>5.18363</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>4.8700599999999996</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
+        <v>4.5928199999999997</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>4.1554900000000004</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
+        <v>3.7521599999999999</v>
+      </c>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
+        <f>AVERAGE(D6,F6,H6,J6,L6,N6)</f>
+        <v>4.4955516666666666</v>
+      </c>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>4.5416499999999997</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>5.3048500000000001</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>5.0471199999999996</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
+        <v>4.6762499999999996</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>4.2282599999999997</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
+        <v>3.8422999999999998</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
+        <f>AVERAGE(D7,F7,H7,J7,L7,N7)</f>
+        <v>4.6067383333333325</v>
+      </c>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>4.5712900000000003</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>5.3359399999999999</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>5.0900999999999996</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
+        <v>4.7393400000000003</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>4.3044399999999996</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
+        <v>3.8893800000000001</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3">
+        <f>AVERAGE(D8,F8,H8,J8,L8,N8)</f>
+        <v>4.6550816666666668</v>
+      </c>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>4.6014499999999998</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <v>5.3707099999999999</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
+        <v>5.1400800000000002</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>4.6508000000000003</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4">
+        <v>4.2111900000000002</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
+        <v>3.8771599999999999</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="3">
+        <f>AVERAGE(D9,F9,H9,J9,L9,N9)</f>
+        <v>4.6418983333333328</v>
+      </c>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+    </row>
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3">
+        <v>3.9427500000000002</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
+        <v>4.7552599999999998</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>4.6803999999999997</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>4.1638500000000001</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>3.7195</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>3.3722400000000001</v>
+      </c>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3">
+        <f>AVERAGE(D13,F13,H13,J13,L13,N13)</f>
+        <v>4.105666666666667</v>
+      </c>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+    </row>
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>4.1139799999999997</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>5.0107999999999997</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
+        <v>4.7341800000000003</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>4.3601700000000001</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>3.8696199999999998</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <v>3.5631699999999999</v>
+      </c>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3">
+        <f>AVERAGE(D14,F14,H14,J14,L14,N14)</f>
+        <v>4.2753199999999998</v>
+      </c>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
+        <v>4.1571100000000003</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>5.0759100000000004</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3">
+        <v>4.8683899999999998</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>4.4054799999999998</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>3.93289</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>3.6810200000000002</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3">
+        <f>AVERAGE(D15,F15,H15,J15,L15,N15)</f>
+        <v>4.3534666666666668</v>
+      </c>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3">
+        <v>4.1813900000000004</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3">
+        <v>5.1694000000000004</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
+        <v>4.8948799999999997</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>4.4668000000000001</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>4.00122</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
+        <v>3.68866</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3">
+        <f>AVERAGE(D16,F16,H16,J16,L16,N16)</f>
+        <v>4.4003916666666667</v>
+      </c>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+    </row>
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4">
+        <v>4.2530000000000001</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4">
+        <v>5.1594899999999999</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
+        <v>4.8507300000000004</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>4.3982200000000002</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4">
+        <v>3.9194499999999999</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4">
+        <v>3.67726</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4">
+        <f>AVERAGE(D17,F17,H17,J17,L17,N17)</f>
+        <v>4.3763583333333331</v>
+      </c>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+    </row>
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+    </row>
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3">
+        <v>4.6584000000000003</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
+        <v>5.6210599999999999</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>5.3454499999999996</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3">
+        <v>4.8077899999999998</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>4.3698199999999998</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
+        <v>3.8694600000000001</v>
+      </c>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3">
+        <f>AVERAGE(D23,F23,H23,J23,L23,N23)</f>
+        <v>4.7786633333333333</v>
+      </c>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+    </row>
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>4.78146</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
+        <v>5.7847400000000002</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>5.4347500000000002</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3">
+        <v>4.9870799999999997</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>4.5327999999999999</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
+        <v>4.0762299999999998</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3">
+        <f>AVERAGE(D24,F24,H24,J24,L24,N24)</f>
+        <v>4.9328433333333326</v>
+      </c>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+    </row>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3">
+        <v>4.8853299999999997</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3">
+        <v>5.8437299999999999</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
+        <v>5.5219699999999996</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3">
+        <v>5.1352500000000001</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3">
+        <v>4.6790099999999999</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3">
+        <v>4.1275500000000003</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3">
+        <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
+        <v>5.0321399999999992</v>
+      </c>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+    </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3">
+        <v>4.9222400000000004</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
+        <v>5.90184</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>5.5779500000000004</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3">
+        <v>5.0900800000000004</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3">
+        <v>4.6751199999999997</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3">
+        <v>4.1644899999999998</v>
+      </c>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3">
+        <f>AVERAGE(D26,F26,H26,J26,L26,N26)</f>
+        <v>5.0552866666666665</v>
+      </c>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+    </row>
+    <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4">
+        <v>4.94916</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <v>5.8987600000000002</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4">
+        <v>5.6253900000000003</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4">
+        <v>5.0972999999999997</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4">
+        <v>4.6465399999999999</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4">
+        <v>4.12784</v>
+      </c>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4">
+        <f>AVERAGE(D27,F27,H27,J27,L27,N27)</f>
+        <v>5.0574983333333341</v>
+      </c>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+    </row>
+    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+    </row>
+    <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P29" s="11"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+    </row>
+    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+    </row>
+    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
+        <v>4.3267899999999999</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3">
+        <v>5.3582799999999997</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3">
+        <v>5.1484899999999998</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3">
+        <v>4.4641099999999998</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3">
+        <v>4.0290900000000001</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3">
+        <v>3.6514700000000002</v>
+      </c>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3">
+        <f>AVERAGE(D31,F31,H31,J31,L31,N31)</f>
+        <v>4.4963716666666658</v>
+      </c>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+    </row>
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
+        <v>4.3927500000000004</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3">
+        <v>5.4578699999999998</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>5.2147800000000002</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
+        <v>4.7100200000000001</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3">
+        <v>4.21652</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3">
+        <v>3.6653899999999999</v>
+      </c>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3">
+        <f>AVERAGE(D32,F32,H32,J32,L32,N32)</f>
+        <v>4.6095549999999994</v>
+      </c>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+    </row>
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3">
+        <v>4.4714900000000002</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3">
+        <v>5.59145</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
+        <v>5.3195899999999998</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
+        <v>4.7229700000000001</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3">
+        <v>4.2790800000000004</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3">
+        <v>3.86571</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3">
+        <f>AVERAGE(D33,F33,H33,J33,L33,N33)</f>
+        <v>4.7083816666666669</v>
+      </c>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+    </row>
+    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3">
+        <v>4.5896400000000002</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
+        <v>5.5566399999999998</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3">
+        <v>5.3896800000000002</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3">
+        <v>4.8712099999999996</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3">
+        <v>4.3392299999999997</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3">
+        <v>3.87656</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3">
+        <f>AVERAGE(D34,F34,H34,J34,L34,N34)</f>
+        <v>4.7704933333333335</v>
+      </c>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+    </row>
+    <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <v>4.5360699999999996</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4">
+        <v>5.5996199999999998</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4">
+        <v>5.4069700000000003</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4">
+        <v>4.7460399999999998</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4">
+        <v>4.26335</v>
+      </c>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4">
+        <v>3.8490899999999999</v>
+      </c>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4">
+        <f>AVERAGE(D35,F35,H35,J35,L35,N35)</f>
+        <v>4.7335233333333333</v>
+      </c>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+    </row>
+    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+    </row>
+    <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+    </row>
+    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
+    </row>
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P39" s="11"/>
+      <c r="R39" s="14"/>
+      <c r="S39" s="14"/>
+      <c r="T39" s="14"/>
+    </row>
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+    </row>
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3">
+        <v>4.8613999999999997</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
+        <v>5.88361</v>
+      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3">
+        <v>5.5696399999999997</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3">
+        <v>5.0985699999999996</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>4.5044000000000004</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3">
+        <v>4.0416400000000001</v>
+      </c>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3">
+        <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
+        <v>4.9932100000000004</v>
+      </c>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
+    </row>
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3">
+        <v>5.0363800000000003</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <v>6.0898700000000003</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3">
+        <v>5.7049899999999996</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3">
+        <v>5.3215500000000002</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>4.7849199999999996</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3">
+        <v>4.2842399999999996</v>
+      </c>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3">
+        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
+        <v>5.2036583333333342</v>
+      </c>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+    </row>
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3">
+        <v>5.1776600000000004</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
+        <v>6.1842800000000002</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3">
+        <v>5.8865100000000004</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3">
+        <v>5.48346</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>4.9375</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3">
+        <v>4.3942699999999997</v>
+      </c>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3">
+        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
+        <v>5.3439466666666675</v>
+      </c>
+      <c r="R43" s="14"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="14"/>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
+        <v>5.2876300000000001</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
+        <v>6.2506199999999996</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3">
+        <v>5.9457700000000004</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3">
+        <v>5.5481100000000003</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3">
+        <v>5.0165199999999999</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3">
+        <v>4.5465</v>
+      </c>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3">
+        <f>AVERAGE(D44,F44,H44,J44,L44,N44)</f>
+        <v>5.4325250000000009</v>
+      </c>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+    </row>
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4">
+        <v>5.2888599999999997</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4">
+        <v>6.2779600000000002</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4">
+        <v>6.0451699999999997</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4">
+        <v>5.5814599999999999</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4">
+        <v>5.0148900000000003</v>
+      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4">
+        <v>4.53064</v>
+      </c>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4">
+        <f>AVERAGE(D45,F45,H45,J45,L45,N45)</f>
+        <v>5.4564966666666663</v>
+      </c>
+      <c r="R45" s="14"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
+    </row>
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
+    </row>
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P47" s="11"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+    </row>
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R48" s="14"/>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
+    </row>
+    <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3">
+        <v>4.39011</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
+        <v>5.6082400000000003</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3">
+        <v>5.3261500000000002</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3">
+        <v>4.6698899999999997</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3">
+        <v>4.1432399999999996</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3">
+        <v>3.7595499999999999</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3">
+        <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
+        <v>4.6495299999999995</v>
+      </c>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
+    </row>
+    <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3">
+        <v>4.5535100000000002</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
+        <v>5.7491000000000003</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3">
+        <v>5.4894600000000002</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3">
+        <v>4.9547800000000004</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3">
+        <v>4.3115500000000004</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3">
+        <v>4.0073100000000004</v>
+      </c>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3">
+        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
+        <v>4.8442850000000002</v>
+      </c>
+      <c r="R50" s="14"/>
+      <c r="S50" s="14"/>
+      <c r="T50" s="14"/>
+    </row>
+    <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3">
+        <v>4.7401799999999996</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
+        <v>5.87758</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3">
+        <v>5.6888500000000004</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3">
+        <v>5.1455900000000003</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3">
+        <v>4.44956</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3">
+        <v>4.04033</v>
+      </c>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3">
+        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
+        <v>4.9903483333333325</v>
+      </c>
+      <c r="R51" s="14"/>
+      <c r="S51" s="14"/>
+      <c r="T51" s="14"/>
+    </row>
+    <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3">
+        <v>4.8115199999999998</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
+        <v>5.9385199999999996</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
+        <v>5.6940099999999996</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3">
+        <v>5.04535</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3">
+        <v>4.57951</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3">
+        <v>4.1412100000000001</v>
+      </c>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3">
+        <f>AVERAGE(D52,F52,H52,J52,L52,N52)</f>
+        <v>5.0350199999999994</v>
+      </c>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
+      <c r="T52" s="14"/>
+    </row>
+    <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4">
+        <v>4.7477600000000004</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4">
+        <v>6.0426799999999998</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4">
+        <v>5.7625099999999998</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4">
+        <v>5.2044899999999998</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4">
+        <v>4.6174200000000001</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4">
+        <v>4.1296299999999997</v>
+      </c>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4">
+        <f>AVERAGE(D53,F53,H53,J53,L53,N53)</f>
+        <v>5.0840816666666662</v>
+      </c>
+      <c r="R53" s="14"/>
+      <c r="S53" s="14"/>
+      <c r="T53" s="14"/>
+    </row>
+    <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+    </row>
+    <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P57" s="11"/>
+    </row>
+    <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3">
+        <v>4.8350999999999997</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3">
+        <v>5.8418599999999996</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3">
+        <v>5.3804100000000004</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3">
+        <v>5.1307099999999997</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3">
+        <v>4.2869599999999997</v>
+      </c>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3">
+        <v>3.9249200000000002</v>
+      </c>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3">
+        <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
+        <v>4.8999933333333336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9"/>
+      <c r="B60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3">
+        <v>5.0928699999999996</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3">
+        <v>5.9963899999999999</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3">
+        <v>5.7409499999999998</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3">
+        <v>5.3913000000000002</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3">
+        <v>4.4194800000000001</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3">
+        <v>4.1529199999999999</v>
+      </c>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3">
+        <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
+        <v>5.132318333333334</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3">
+        <v>5.3201000000000001</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3">
+        <v>6.1637899999999997</v>
+      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3">
+        <v>5.9080199999999996</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3">
+        <v>5.5360100000000001</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3">
+        <v>4.71347</v>
+      </c>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3">
+        <v>4.3147200000000003</v>
+      </c>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3">
+        <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
+        <v>5.3260183333333337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
+        <v>5.36137</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <v>6.2123900000000001</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3">
+        <v>6.0613599999999996</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3">
+        <v>5.5939699999999997</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3">
+        <v>4.8575299999999997</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3">
+        <v>4.4312899999999997</v>
+      </c>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3">
+        <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
+        <v>5.4196516666666668</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+      <c r="B63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4">
+        <v>5.4131900000000002</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4">
+        <v>6.2545000000000002</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4">
+        <v>6.0812799999999996</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4">
+        <v>5.6418999999999997</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4">
+        <v>4.8334400000000004</v>
+      </c>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4">
+        <v>4.4951999999999996</v>
+      </c>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4">
+        <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
+        <v>5.4532516666666666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9"/>
+      <c r="B64" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9"/>
+      <c r="B65" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P65" s="11"/>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9"/>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3">
+        <v>4.4249700000000001</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3">
+        <v>5.5333399999999999</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3">
+        <v>5.1902999999999997</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3">
+        <v>4.8660300000000003</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3">
+        <v>3.8866299999999998</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3">
+        <v>3.6355400000000002</v>
+      </c>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3">
+        <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
+        <v>4.5894683333333335</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9"/>
+      <c r="B68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3">
+        <v>4.66181</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3">
+        <v>5.6358699999999997</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3">
+        <v>5.5303500000000003</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3">
+        <v>4.9067100000000003</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3">
+        <v>4.1264799999999999</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3">
+        <v>3.8291499999999998</v>
+      </c>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3">
+        <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
+        <v>4.7817283333333336</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+      <c r="B69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3">
+        <v>4.8665000000000003</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3">
+        <v>5.8399900000000002</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3">
+        <v>5.65158</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3">
+        <v>5.07212</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3">
+        <v>4.3304900000000002</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3">
+        <v>3.9704700000000002</v>
+      </c>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3">
+        <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
+        <v>4.9551916666666669</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9"/>
+      <c r="B70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3">
+        <v>4.9245000000000001</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3">
+        <v>5.9912099999999997</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3">
+        <v>5.8172800000000002</v>
+      </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3">
+        <v>5.1707700000000001</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3">
+        <v>4.4135600000000004</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3">
+        <v>4.1507300000000003</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3">
+        <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
+        <v>5.0780083333333339</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9"/>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4">
+        <v>4.8952299999999997</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4">
+        <v>6.0022099999999998</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4">
+        <v>5.8484299999999996</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4">
+        <v>5.3302800000000001</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4">
+        <v>4.4426100000000002</v>
+      </c>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4">
+        <v>4.1807600000000003</v>
+      </c>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4">
+        <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+        <v>5.1165866666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="A38:A53"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="B64:P64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="B20:P20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="R2:T53"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B10:P10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E601461E-E0CB-471A-BB17-97A9D65353CC}">
+  <dimension ref="A2:T73"/>
+  <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="7.58203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="R2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="11"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
+        <v>4.3631000000000002</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
+        <v>5.2723599999999999</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>4.9640399999999998</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
+        <v>4.4830199999999998</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <v>4.02501</v>
+      </c>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
+        <v>3.6421700000000001</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3">
+        <f>AVERAGE(D5,F5,H5,J5,L5,N5)</f>
+        <v>4.4582833333333332</v>
+      </c>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>4.5181899999999997</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
+        <v>5.4440900000000001</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>5.0273000000000003</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3">
+        <v>4.7429500000000004</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <v>4.1732399999999998</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
+        <v>3.7964799999999999</v>
+      </c>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
+        <f>AVERAGE(D6,F6,H6,J6,L6,N6)</f>
+        <v>4.6170416666666663</v>
+      </c>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>4.6383900000000002</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
+        <v>5.6491400000000001</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
+        <v>5.1610399999999998</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3">
+        <v>4.8702199999999998</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>4.30246</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
+        <v>3.8928099999999999</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
+        <f>AVERAGE(D7,F7,H7,J7,L7,N7)</f>
+        <v>4.7523433333333331</v>
+      </c>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>4.7031200000000002</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
+        <v>5.6686100000000001</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>5.2423500000000001</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3">
+        <v>4.8738200000000003</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <v>4.3827100000000003</v>
+      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
+        <v>3.9784999999999999</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3">
+        <f>AVERAGE(D8,F8,H8,J8,L8,N8)</f>
+        <v>4.8081849999999999</v>
+      </c>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>4.7287100000000004</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <v>5.7062900000000001</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4">
+        <v>5.3048700000000002</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>4.9085299999999998</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4">
+        <v>4.2626999999999997</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4">
+        <v>3.9096099999999998</v>
+      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="3">
+        <f>AVERAGE(D9,F9,H9,J9,L9,N9)</f>
+        <v>4.8034516666666667</v>
+      </c>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+    </row>
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="11"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+    </row>
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3">
+        <v>3.9840499999999999</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
+        <v>5.0627300000000002</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3">
+        <v>4.6909099999999997</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>4.3232900000000001</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>3.6934200000000001</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>3.4621200000000001</v>
+      </c>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3">
+        <f>AVERAGE(D13,F13,H13,J13,L13,N13)</f>
+        <v>4.2027533333333329</v>
+      </c>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+    </row>
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3">
+        <v>4.1424500000000002</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3">
+        <v>5.1456499999999998</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3">
+        <v>4.81839</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>4.3048999999999999</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <v>3.92584</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <v>3.5759300000000001</v>
+      </c>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3">
+        <f>AVERAGE(D14,F14,H14,J14,L14,N14)</f>
+        <v>4.3188599999999999</v>
+      </c>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3">
+        <v>4.2482499999999996</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
+        <v>5.3839800000000002</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3">
+        <v>4.8995899999999999</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>4.58439</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>4.0186200000000003</v>
+      </c>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>3.6019199999999998</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3">
+        <f>AVERAGE(D15,F15,H15,J15,L15,N15)</f>
+        <v>4.4561250000000001</v>
+      </c>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+    </row>
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3">
+        <v>4.2962100000000003</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3">
+        <v>5.4276900000000001</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3">
+        <v>4.9443099999999998</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>4.5353500000000002</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>4.0282400000000003</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
+        <v>3.7635200000000002</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3">
+        <f>AVERAGE(D16,F16,H16,J16,L16,N16)</f>
+        <v>4.4992200000000002</v>
+      </c>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="13"/>
+    </row>
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4">
+        <v>4.2996499999999997</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4">
+        <v>5.44726</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
+        <v>5.0716599999999996</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>4.4807499999999996</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4">
+        <v>4.0464500000000001</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4">
+        <v>3.6364399999999999</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4">
+        <f>AVERAGE(D17,F17,H17,J17,L17,N17)</f>
+        <v>4.4970349999999994</v>
+      </c>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="13"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+    </row>
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+    </row>
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+    </row>
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P21" s="11"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+    </row>
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="13"/>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3">
+        <v>4.9093900000000001</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
+        <v>6.16669</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>5.7668799999999996</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3">
+        <v>5.1024500000000002</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>4.5156099999999997</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
+        <v>3.95038</v>
+      </c>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3">
+        <f>AVERAGE(D23,F23,H23,J23,L23,N23)</f>
+        <v>5.0685666666666664</v>
+      </c>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="13"/>
+    </row>
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
+        <v>5.03796</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
+        <v>6.3759199999999998</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>5.8883799999999997</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3">
+        <v>5.2884599999999997</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>4.7176299999999998</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
+        <v>4.1200200000000002</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3">
+        <f>AVERAGE(D24,F24,H24,J24,L24,N24)</f>
+        <v>5.2380616666666659</v>
+      </c>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="13"/>
+    </row>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3">
+        <v>5.2032499999999997</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3">
+        <v>6.4965200000000003</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
+        <v>6.1082200000000002</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3">
+        <v>5.42326</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3">
+        <v>4.86639</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3">
+        <v>4.1759399999999998</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3">
+        <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
+        <v>5.3789299999999995</v>
+      </c>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+    </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3">
+        <v>5.2596400000000001</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
+        <v>6.5412800000000004</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>6.1145399999999999</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3">
+        <v>5.5060799999999999</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3">
+        <v>4.8705400000000001</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3">
+        <v>4.2789700000000002</v>
+      </c>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3">
+        <f>AVERAGE(D26,F26,H26,J26,L26,N26)</f>
+        <v>5.4285083333333342</v>
+      </c>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
+    </row>
+    <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4">
+        <v>5.2412799999999997</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4">
+        <v>6.5973699999999997</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4">
+        <v>6.2436499999999997</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4">
+        <v>5.4269499999999997</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4">
+        <v>4.85501</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4">
+        <v>4.2236799999999999</v>
+      </c>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4">
+        <f>AVERAGE(D27,F27,H27,J27,L27,N27)</f>
+        <v>5.4313233333333342</v>
+      </c>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+    </row>
+    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="13"/>
+    </row>
+    <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P29" s="11"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+    </row>
+    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+    </row>
+    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3">
+        <v>4.4171199999999997</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3">
+        <v>5.9098699999999997</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3">
+        <v>5.47966</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3">
+        <v>4.7360600000000002</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3">
+        <v>4.1972500000000004</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3">
+        <v>3.7159399999999998</v>
+      </c>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3">
+        <f>AVERAGE(D31,F31,H31,J31,L31,N31)</f>
+        <v>4.7426500000000003</v>
+      </c>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+    </row>
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3">
+        <v>4.58711</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3">
+        <v>6.08108</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3">
+        <v>5.6364999999999998</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3">
+        <v>4.9332500000000001</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3">
+        <v>4.3310000000000004</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3">
+        <v>3.8146800000000001</v>
+      </c>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3">
+        <f>AVERAGE(D32,F32,H32,J32,L32,N32)</f>
+        <v>4.8972699999999998</v>
+      </c>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+    </row>
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3">
+        <v>4.6610100000000001</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3">
+        <v>6.1149399999999998</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3">
+        <v>5.7544300000000002</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3">
+        <v>5.0990099999999998</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3">
+        <v>4.4406999999999996</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3">
+        <v>3.9679899999999999</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3">
+        <f>AVERAGE(D33,F33,H33,J33,L33,N33)</f>
+        <v>5.0063466666666665</v>
+      </c>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+    </row>
+    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3">
+        <v>4.7348999999999997</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
+        <v>6.2387899999999998</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3">
+        <v>5.7909199999999998</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3">
+        <v>5.0852700000000004</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3">
+        <v>4.5058999999999996</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3">
+        <v>3.9577800000000001</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3">
+        <f>AVERAGE(D34,F34,H34,J34,L34,N34)</f>
+        <v>5.0522599999999995</v>
+      </c>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+    </row>
+    <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4">
+        <v>4.7842799999999999</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4">
+        <v>6.2119400000000002</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4">
+        <v>5.8964100000000004</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4">
+        <v>5.08866</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4">
+        <v>4.4506100000000002</v>
+      </c>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4">
+        <v>3.8703599999999998</v>
+      </c>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4">
+        <f>AVERAGE(D35,F35,H35,J35,L35,N35)</f>
+        <v>5.0503766666666676</v>
+      </c>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+    </row>
+    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+    </row>
+    <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+    </row>
+    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="13"/>
+    </row>
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P39" s="11"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+    </row>
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+    </row>
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3">
+        <v>5.1281100000000004</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
+        <v>6.5967399999999996</v>
+      </c>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3">
+        <v>6.0303000000000004</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3">
+        <v>5.3832500000000003</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>4.6546099999999999</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3">
+        <v>4.1087600000000002</v>
+      </c>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3">
+        <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
+        <v>5.3169616666666668</v>
+      </c>
+      <c r="R41" s="13"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="13"/>
+    </row>
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3">
+        <v>5.3770699999999998</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <v>6.8782699999999997</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3">
+        <v>6.2976999999999999</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3">
+        <v>5.7444899999999999</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>5.0132099999999999</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3">
+        <v>4.3860799999999998</v>
+      </c>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3">
+        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
+        <v>5.6161366666666668</v>
+      </c>
+      <c r="R42" s="13"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="13"/>
+    </row>
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3">
+        <v>5.5884400000000003</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
+        <v>7.08704</v>
+      </c>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3">
+        <v>6.5990099999999998</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3">
+        <v>5.9165700000000001</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3">
+        <v>5.1949899999999998</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3">
+        <v>4.5554399999999999</v>
+      </c>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3">
+        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
+        <v>5.8235816666666667</v>
+      </c>
+      <c r="R43" s="13"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="13"/>
+    </row>
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3">
+        <v>5.7150499999999997</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
+        <v>7.2029199999999998</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3">
+        <v>6.7062799999999996</v>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3">
+        <v>6.0313600000000003</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3">
+        <v>5.2746899999999997</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3">
+        <v>4.6651199999999999</v>
+      </c>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3">
+        <f>AVERAGE(D44,F44,H44,J44,L44,N44)</f>
+        <v>5.9325699999999992</v>
+      </c>
+      <c r="R44" s="13"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="13"/>
+    </row>
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4">
+        <v>5.7586199999999996</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4">
+        <v>7.1936299999999997</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4">
+        <v>6.8118600000000002</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4">
+        <v>6.0483900000000004</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4">
+        <v>5.2916400000000001</v>
+      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4">
+        <v>4.6908899999999996</v>
+      </c>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4">
+        <f>AVERAGE(D45,F45,H45,J45,L45,N45)</f>
+        <v>5.9658383333333331</v>
+      </c>
+      <c r="R45" s="13"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="13"/>
+    </row>
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="R46" s="13"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="13"/>
+    </row>
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N47" s="11"/>
+      <c r="O47" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P47" s="11"/>
+      <c r="R47" s="13"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="13"/>
+    </row>
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R48" s="13"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="13"/>
+    </row>
+    <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3">
+        <v>4.6195399999999998</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
+        <v>6.1778500000000003</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3">
+        <v>5.6644199999999998</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3">
+        <v>4.9727899999999998</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3">
+        <v>4.2516499999999997</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3">
+        <v>3.8186</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3">
+        <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
+        <v>4.9174750000000005</v>
+      </c>
+      <c r="R49" s="13"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="13"/>
+    </row>
+    <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3">
+        <v>4.80246</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
+        <v>6.5113200000000004</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3">
+        <v>5.9667000000000003</v>
+      </c>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3">
+        <v>5.2817999999999996</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3">
+        <v>4.5609599999999997</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3">
+        <v>3.9993099999999999</v>
+      </c>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3">
+        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
+        <v>5.1870916666666673</v>
+      </c>
+      <c r="R50" s="13"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="13"/>
+    </row>
+    <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3">
+        <v>5.0526200000000001</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3">
+        <v>6.4544100000000002</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3">
+        <v>6.3133100000000004</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3">
+        <v>5.4720500000000003</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3">
+        <v>4.6336500000000003</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3">
+        <v>4.2481499999999999</v>
+      </c>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3">
+        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
+        <v>5.3623650000000005</v>
+      </c>
+      <c r="R51" s="13"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="13"/>
+    </row>
+    <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3">
+        <v>5.1760700000000002</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
+        <v>6.7060399999999998</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
+        <v>6.4015500000000003</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3">
+        <v>5.5596500000000004</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3">
+        <v>4.7579900000000004</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3">
+        <v>4.33087</v>
+      </c>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3">
+        <f>AVERAGE(D52,F52,H52,J52,L52,N52)</f>
+        <v>5.4886949999999999</v>
+      </c>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+    </row>
+    <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4">
+        <v>5.2329600000000003</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4">
+        <v>6.6994300000000004</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4">
+        <v>6.5334000000000003</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4">
+        <v>5.6490499999999999</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4">
+        <v>4.7836100000000004</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4">
+        <v>4.18377</v>
+      </c>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4">
+        <f>AVERAGE(D53,F53,H53,J53,L53,N53)</f>
+        <v>5.513703333333333</v>
+      </c>
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="13"/>
+    </row>
+    <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="13"/>
+    </row>
+    <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="13"/>
+    </row>
+    <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="R56" s="13"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="13"/>
+    </row>
+    <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P57" s="11"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="13"/>
+    </row>
+    <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R58" s="13"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="13"/>
+    </row>
+    <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+      <c r="B59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3">
+        <v>5.2170199999999998</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3">
+        <v>6.7058</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3">
+        <v>5.8960900000000001</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3">
+        <v>5.51302</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3">
+        <v>4.4889099999999997</v>
+      </c>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3">
+        <v>3.9875500000000001</v>
+      </c>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3">
+        <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
+        <v>5.3013983333333332</v>
+      </c>
+      <c r="R59" s="13"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="13"/>
+    </row>
+    <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9"/>
+      <c r="B60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3">
+        <v>5.5326500000000003</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3">
+        <v>6.9372800000000003</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3">
+        <v>6.4316899999999997</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3">
+        <v>5.9229700000000003</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3">
+        <v>4.6546399999999997</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3">
+        <v>4.2896900000000002</v>
+      </c>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3">
+        <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
+        <v>5.6281533333333336</v>
+      </c>
+      <c r="R60" s="13"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="13"/>
+    </row>
+    <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3">
+        <v>5.8452999999999999</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3">
+        <v>7.30708</v>
+      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3">
+        <v>6.8287000000000004</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3">
+        <v>6.1655600000000002</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3">
+        <v>5.0092600000000003</v>
+      </c>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3">
+        <v>4.5428699999999997</v>
+      </c>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3">
+        <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
+        <v>5.9497950000000008</v>
+      </c>
+      <c r="R61" s="13"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="13"/>
+    </row>
+    <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
+        <v>5.9729999999999999</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <v>7.3642000000000003</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3">
+        <v>7.0712900000000003</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3">
+        <v>6.2563599999999999</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3">
+        <v>5.2250699999999997</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3">
+        <v>4.7006600000000001</v>
+      </c>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3">
+        <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
+        <v>6.0984300000000005</v>
+      </c>
+      <c r="R62" s="13"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="13"/>
+    </row>
+    <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+      <c r="B63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4">
+        <v>6.0232900000000003</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4">
+        <v>7.4203700000000001</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4">
+        <v>7.0931699999999998</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4">
+        <v>6.30504</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4">
+        <v>5.1756000000000002</v>
+      </c>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4">
+        <v>4.7927299999999997</v>
+      </c>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4">
+        <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
+        <v>6.1350333333333333</v>
+      </c>
+      <c r="R63" s="13"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="13"/>
+    </row>
+    <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9"/>
+      <c r="B64" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="R64" s="13"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="13"/>
+    </row>
+    <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9"/>
+      <c r="B65" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P65" s="11"/>
+      <c r="R65" s="13"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="13"/>
+    </row>
+    <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+    </row>
+    <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9"/>
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3">
+        <v>4.6100399999999997</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3">
+        <v>6.26553</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3">
+        <v>5.6264399999999997</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3">
+        <v>5.0568900000000001</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3">
+        <v>4.0156999999999998</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3">
+        <v>3.6715399999999998</v>
+      </c>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3">
+        <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
+        <v>4.8743566666666664</v>
+      </c>
+      <c r="R67" s="13"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="13"/>
+    </row>
+    <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9"/>
+      <c r="B68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3">
+        <v>4.9540199999999999</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3">
+        <v>6.5081300000000004</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3">
+        <v>5.9816200000000004</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3">
+        <v>5.2504499999999998</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3">
+        <v>3.9525700000000001</v>
+      </c>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3">
+        <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
+        <v>5.1494650000000002</v>
+      </c>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="13"/>
+    </row>
+    <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9"/>
+      <c r="B69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3">
+        <v>5.1785199999999998</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3">
+        <v>6.7186700000000004</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3">
+        <v>6.3500199999999998</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3">
+        <v>5.5468599999999997</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3">
+        <v>4.5016999999999996</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3">
+        <v>4.2653400000000001</v>
+      </c>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3">
+        <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
+        <v>5.4268516666666669</v>
+      </c>
+      <c r="R69" s="13"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="13"/>
+    </row>
+    <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="9"/>
+      <c r="B70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3">
+        <v>5.2362000000000002</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3">
+        <v>6.9116600000000004</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3">
+        <v>6.6836399999999996</v>
+      </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3">
+        <v>5.7034900000000004</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3">
+        <v>4.6085099999999999</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3">
+        <v>4.1947000000000001</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3">
+        <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
+        <v>5.5563666666666665</v>
+      </c>
+      <c r="R70" s="13"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="13"/>
+    </row>
+    <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="9"/>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4">
+        <v>5.3973599999999999</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4">
+        <v>7.0010300000000001</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4">
+        <v>6.7210599999999996</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4">
+        <v>5.7859999999999996</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4">
+        <v>4.6787099999999997</v>
+      </c>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4">
+        <v>4.3733199999999997</v>
+      </c>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4">
+        <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+        <v>5.6595800000000009</v>
+      </c>
+      <c r="R71" s="13"/>
+      <c r="S71" s="13"/>
+      <c r="T71" s="13"/>
+    </row>
+    <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R72" s="7"/>
+      <c r="S72" s="7"/>
+      <c r="T72" s="7"/>
+    </row>
+    <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="B64:P64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="A38:A53"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="A20:A35"/>
+    <mergeCell ref="B20:P20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="B10:P10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="R2:T71"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F304A2-2891-4E03-87A7-8FFF723E6508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A0C25A-CFE1-4E10-8991-4EF4CB468DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="47">
   <si>
     <t>Data Num.</t>
   </si>
@@ -226,6 +226,15 @@
     <t>800k (epoch=3)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>HASS-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HASS-1
+Align-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -319,7 +328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -363,6 +372,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4478,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D606126C-3FE1-428A-BDA2-93CD7E4A00CB}">
-  <dimension ref="A2:T71"/>
+  <dimension ref="A2:T107"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -5731,13 +5749,27 @@
       <c r="T36" s="14"/>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
       <c r="R37" s="14"/>
       <c r="S37" s="14"/>
       <c r="T37" s="14"/>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>30</v>
+      <c r="A38" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>13</v>
@@ -5849,36 +5881,36 @@
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3">
-        <v>4.8613999999999997</v>
+        <v>4.5689299999999999</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3">
-        <v>5.88361</v>
+        <v>5.5732100000000004</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3">
-        <v>5.5696399999999997</v>
+        <v>5.1474900000000003</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3">
-        <v>5.0985699999999996</v>
+        <v>4.7865599999999997</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3">
-        <v>4.5044000000000004</v>
+        <v>4.1556199999999999</v>
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3">
-        <v>4.0416400000000001</v>
+        <v>3.6334300000000002</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3">
         <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
-        <v>4.9932100000000004</v>
+        <v>4.6442066666666673</v>
       </c>
       <c r="R41" s="14"/>
       <c r="S41" s="14"/>
@@ -5887,37 +5919,22 @@
     <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>5.0363800000000003</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>6.0898700000000003</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3">
-        <v>5.7049899999999996</v>
-      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3">
-        <v>5.3215500000000002</v>
-      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>4.7849199999999996</v>
-      </c>
+      <c r="L42" s="3"/>
       <c r="M42" s="3"/>
-      <c r="N42" s="3">
-        <v>4.2842399999999996</v>
-      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="3">
-        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
-        <v>5.2036583333333342</v>
-      </c>
+      <c r="P42" s="3"/>
       <c r="R42" s="14"/>
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
@@ -5925,37 +5942,22 @@
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3">
-        <v>5.1776600000000004</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>6.1842800000000002</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3">
-        <v>5.8865100000000004</v>
-      </c>
+      <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3">
-        <v>5.48346</v>
-      </c>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>4.9375</v>
-      </c>
+      <c r="L43" s="3"/>
       <c r="M43" s="3"/>
-      <c r="N43" s="3">
-        <v>4.3942699999999997</v>
-      </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="3">
-        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
-        <v>5.3439466666666675</v>
-      </c>
+      <c r="P43" s="3"/>
       <c r="R43" s="14"/>
       <c r="S43" s="14"/>
       <c r="T43" s="14"/>
@@ -5963,37 +5965,22 @@
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C44" s="3"/>
-      <c r="D44" s="3">
-        <v>5.2876300000000001</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="3">
-        <v>6.2506199999999996</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3">
-        <v>5.9457700000000004</v>
-      </c>
+      <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3">
-        <v>5.5481100000000003</v>
-      </c>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
-      <c r="L44" s="3">
-        <v>5.0165199999999999</v>
-      </c>
+      <c r="L44" s="3"/>
       <c r="M44" s="3"/>
-      <c r="N44" s="3">
-        <v>4.5465</v>
-      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3"/>
-      <c r="P44" s="3">
-        <f>AVERAGE(D44,F44,H44,J44,L44,N44)</f>
-        <v>5.4325250000000009</v>
-      </c>
+      <c r="P44" s="3"/>
       <c r="R44" s="14"/>
       <c r="S44" s="14"/>
       <c r="T44" s="14"/>
@@ -6001,37 +5988,22 @@
     <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="4">
-        <v>5.2888599999999997</v>
-      </c>
+      <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="4">
-        <v>6.2779600000000002</v>
-      </c>
+      <c r="F45" s="4"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="4">
-        <v>6.0451699999999997</v>
-      </c>
+      <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="4">
-        <v>5.5814599999999999</v>
-      </c>
+      <c r="J45" s="4"/>
       <c r="K45" s="4"/>
-      <c r="L45" s="4">
-        <v>5.0148900000000003</v>
-      </c>
+      <c r="L45" s="4"/>
       <c r="M45" s="4"/>
-      <c r="N45" s="4">
-        <v>4.53064</v>
-      </c>
+      <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="4">
-        <f>AVERAGE(D45,F45,H45,J45,L45,N45)</f>
-        <v>5.4564966666666663</v>
-      </c>
+      <c r="P45" s="4"/>
       <c r="R45" s="14"/>
       <c r="S45" s="14"/>
       <c r="T45" s="14"/>
@@ -6148,36 +6120,36 @@
     <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3">
-        <v>4.39011</v>
+        <v>4.1356999999999999</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3">
-        <v>5.6082400000000003</v>
+        <v>5.3262299999999998</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3">
-        <v>5.3261500000000002</v>
+        <v>4.8702199999999998</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3">
-        <v>4.6698899999999997</v>
+        <v>4.4009</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3">
-        <v>4.1432399999999996</v>
+        <v>3.8662399999999999</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3">
-        <v>3.7595499999999999</v>
+        <v>3.46048</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3">
         <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
-        <v>4.6495299999999995</v>
+        <v>4.3432950000000003</v>
       </c>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
@@ -6186,37 +6158,22 @@
     <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="3">
-        <v>4.5535100000000002</v>
-      </c>
+      <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3">
-        <v>5.7491000000000003</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3">
-        <v>5.4894600000000002</v>
-      </c>
+      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3">
-        <v>4.9547800000000004</v>
-      </c>
+      <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-      <c r="L50" s="3">
-        <v>4.3115500000000004</v>
-      </c>
+      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
-      <c r="N50" s="3">
-        <v>4.0073100000000004</v>
-      </c>
+      <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="3">
-        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
-        <v>4.8442850000000002</v>
-      </c>
+      <c r="P50" s="3"/>
       <c r="R50" s="14"/>
       <c r="S50" s="14"/>
       <c r="T50" s="14"/>
@@ -6224,37 +6181,22 @@
     <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3">
-        <v>4.7401799999999996</v>
-      </c>
+      <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="3">
-        <v>5.87758</v>
-      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3">
-        <v>5.6888500000000004</v>
-      </c>
+      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3">
-        <v>5.1455900000000003</v>
-      </c>
+      <c r="J51" s="3"/>
       <c r="K51" s="3"/>
-      <c r="L51" s="3">
-        <v>4.44956</v>
-      </c>
+      <c r="L51" s="3"/>
       <c r="M51" s="3"/>
-      <c r="N51" s="3">
-        <v>4.04033</v>
-      </c>
+      <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="3">
-        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
-        <v>4.9903483333333325</v>
-      </c>
+      <c r="P51" s="3"/>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
@@ -6262,37 +6204,22 @@
     <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C52" s="3"/>
-      <c r="D52" s="3">
-        <v>4.8115199999999998</v>
-      </c>
+      <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="3">
-        <v>5.9385199999999996</v>
-      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3">
-        <v>5.6940099999999996</v>
-      </c>
+      <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="3">
-        <v>5.04535</v>
-      </c>
+      <c r="J52" s="3"/>
       <c r="K52" s="3"/>
-      <c r="L52" s="3">
-        <v>4.57951</v>
-      </c>
+      <c r="L52" s="3"/>
       <c r="M52" s="3"/>
-      <c r="N52" s="3">
-        <v>4.1412100000000001</v>
-      </c>
+      <c r="N52" s="3"/>
       <c r="O52" s="3"/>
-      <c r="P52" s="3">
-        <f>AVERAGE(D52,F52,H52,J52,L52,N52)</f>
-        <v>5.0350199999999994</v>
-      </c>
+      <c r="P52" s="3"/>
       <c r="R52" s="14"/>
       <c r="S52" s="14"/>
       <c r="T52" s="14"/>
@@ -6300,44 +6227,67 @@
     <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C53" s="4"/>
-      <c r="D53" s="4">
-        <v>4.7477600000000004</v>
-      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="4">
-        <v>6.0426799999999998</v>
-      </c>
+      <c r="F53" s="4"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="4">
-        <v>5.7625099999999998</v>
-      </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="4">
-        <v>5.2044899999999998</v>
-      </c>
+      <c r="J53" s="4"/>
       <c r="K53" s="4"/>
-      <c r="L53" s="4">
-        <v>4.6174200000000001</v>
-      </c>
+      <c r="L53" s="4"/>
       <c r="M53" s="4"/>
-      <c r="N53" s="4">
-        <v>4.1296299999999997</v>
-      </c>
+      <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="4">
-        <f>AVERAGE(D53,F53,H53,J53,L53,N53)</f>
-        <v>5.0840816666666662</v>
-      </c>
+      <c r="P53" s="4"/>
       <c r="R53" s="14"/>
       <c r="S53" s="14"/>
       <c r="T53" s="14"/>
     </row>
+    <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
+    </row>
+    <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="R55" s="14"/>
+      <c r="S55" s="14"/>
+      <c r="T55" s="14"/>
+    </row>
     <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>13</v>
@@ -6356,6 +6306,9 @@
       <c r="N56" s="10"/>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
     </row>
     <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
@@ -6390,6 +6343,9 @@
         <v>7</v>
       </c>
       <c r="P57" s="11"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
     </row>
     <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
@@ -6436,6 +6392,9 @@
       <c r="P58" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R58" s="14"/>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
     </row>
     <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
@@ -6444,33 +6403,36 @@
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
-        <v>4.8350999999999997</v>
+        <v>4.6461800000000002</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3">
-        <v>5.8418599999999996</v>
+        <v>5.7082499999999996</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3">
-        <v>5.3804100000000004</v>
+        <v>5.4791999999999996</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3">
-        <v>5.1307099999999997</v>
+        <v>4.8402599999999998</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3">
-        <v>4.2869599999999997</v>
+        <v>4.3976300000000004</v>
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3">
-        <v>3.9249200000000002</v>
+        <v>3.82822</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3">
         <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
-        <v>4.8999933333333336</v>
-      </c>
+        <v>4.8166233333333333</v>
+      </c>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
     </row>
     <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
@@ -6478,34 +6440,22 @@
         <v>9</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="3">
-        <v>5.0928699999999996</v>
-      </c>
+      <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="3">
-        <v>5.9963899999999999</v>
-      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="3">
-        <v>5.7409499999999998</v>
-      </c>
+      <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="3">
-        <v>5.3913000000000002</v>
-      </c>
+      <c r="J60" s="3"/>
       <c r="K60" s="3"/>
-      <c r="L60" s="3">
-        <v>4.4194800000000001</v>
-      </c>
+      <c r="L60" s="3"/>
       <c r="M60" s="3"/>
-      <c r="N60" s="3">
-        <v>4.1529199999999999</v>
-      </c>
+      <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="3">
-        <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
-        <v>5.132318333333334</v>
-      </c>
+      <c r="P60" s="3"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
     </row>
     <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
@@ -6513,34 +6463,22 @@
         <v>10</v>
       </c>
       <c r="C61" s="3"/>
-      <c r="D61" s="3">
-        <v>5.3201000000000001</v>
-      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="3">
-        <v>6.1637899999999997</v>
-      </c>
+      <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="3">
-        <v>5.9080199999999996</v>
-      </c>
+      <c r="H61" s="3"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="3">
-        <v>5.5360100000000001</v>
-      </c>
+      <c r="J61" s="3"/>
       <c r="K61" s="3"/>
-      <c r="L61" s="3">
-        <v>4.71347</v>
-      </c>
+      <c r="L61" s="3"/>
       <c r="M61" s="3"/>
-      <c r="N61" s="3">
-        <v>4.3147200000000003</v>
-      </c>
+      <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="3">
-        <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
-        <v>5.3260183333333337</v>
-      </c>
+      <c r="P61" s="3"/>
+      <c r="R61" s="14"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
@@ -6548,34 +6486,22 @@
         <v>11</v>
       </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="3">
-        <v>5.36137</v>
-      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="3">
-        <v>6.2123900000000001</v>
-      </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3">
-        <v>6.0613599999999996</v>
-      </c>
+      <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="3">
-        <v>5.5939699999999997</v>
-      </c>
+      <c r="J62" s="3"/>
       <c r="K62" s="3"/>
-      <c r="L62" s="3">
-        <v>4.8575299999999997</v>
-      </c>
+      <c r="L62" s="3"/>
       <c r="M62" s="3"/>
-      <c r="N62" s="3">
-        <v>4.4312899999999997</v>
-      </c>
+      <c r="N62" s="3"/>
       <c r="O62" s="3"/>
-      <c r="P62" s="3">
-        <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
-        <v>5.4196516666666668</v>
-      </c>
+      <c r="P62" s="3"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
     </row>
     <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
@@ -6583,34 +6509,22 @@
         <v>12</v>
       </c>
       <c r="C63" s="4"/>
-      <c r="D63" s="4">
-        <v>5.4131900000000002</v>
-      </c>
+      <c r="D63" s="4"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="4">
-        <v>6.2545000000000002</v>
-      </c>
+      <c r="F63" s="4"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="4">
-        <v>6.0812799999999996</v>
-      </c>
+      <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="4">
-        <v>5.6418999999999997</v>
-      </c>
+      <c r="J63" s="4"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="4">
-        <v>4.8334400000000004</v>
-      </c>
+      <c r="L63" s="4"/>
       <c r="M63" s="4"/>
-      <c r="N63" s="4">
-        <v>4.4951999999999996</v>
-      </c>
+      <c r="N63" s="4"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="4">
-        <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
-        <v>5.4532516666666666</v>
-      </c>
+      <c r="P63" s="4"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
     </row>
     <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
@@ -6631,8 +6545,11 @@
       <c r="N64" s="10"/>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
-    </row>
-    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+    </row>
+    <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
       <c r="B65" s="11" t="s">
         <v>0</v>
@@ -6665,8 +6582,11 @@
         <v>7</v>
       </c>
       <c r="P65" s="11"/>
-    </row>
-    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R65" s="14"/>
+      <c r="S65" s="14"/>
+      <c r="T65" s="14"/>
+    </row>
+    <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="12"/>
       <c r="C66" s="2" t="s">
@@ -6711,211 +6631,1324 @@
       <c r="P66" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R66" s="14"/>
+      <c r="S66" s="14"/>
+      <c r="T66" s="14"/>
+    </row>
+    <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3">
-        <v>4.4249700000000001</v>
+        <v>4.2968700000000002</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3">
-        <v>5.5333399999999999</v>
+        <v>5.4696899999999999</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3">
-        <v>5.1902999999999997</v>
+        <v>5.2728200000000003</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3">
-        <v>4.8660300000000003</v>
+        <v>4.5333500000000004</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3">
-        <v>3.8866299999999998</v>
+        <v>4.0951500000000003</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3">
-        <v>3.6355400000000002</v>
+        <v>3.5975899999999998</v>
       </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3">
         <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
-        <v>4.5894683333333335</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.5442450000000001</v>
+      </c>
+      <c r="R67" s="14"/>
+      <c r="S67" s="14"/>
+      <c r="T67" s="14"/>
+    </row>
+    <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
       <c r="B68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3">
-        <v>4.66181</v>
-      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="3">
-        <v>5.6358699999999997</v>
-      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3">
-        <v>5.5303500000000003</v>
-      </c>
+      <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-      <c r="J68" s="3">
-        <v>4.9067100000000003</v>
-      </c>
+      <c r="J68" s="3"/>
       <c r="K68" s="3"/>
-      <c r="L68" s="3">
-        <v>4.1264799999999999</v>
-      </c>
+      <c r="L68" s="3"/>
       <c r="M68" s="3"/>
-      <c r="N68" s="3">
-        <v>3.8291499999999998</v>
-      </c>
+      <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="3">
-        <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
-        <v>4.7817283333333336</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P68" s="3"/>
+      <c r="R68" s="14"/>
+      <c r="S68" s="14"/>
+      <c r="T68" s="14"/>
+    </row>
+    <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
       <c r="B69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="3"/>
-      <c r="D69" s="3">
-        <v>4.8665000000000003</v>
-      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="3">
-        <v>5.8399900000000002</v>
-      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="3">
-        <v>5.65158</v>
-      </c>
+      <c r="H69" s="3"/>
       <c r="I69" s="3"/>
-      <c r="J69" s="3">
-        <v>5.07212</v>
-      </c>
+      <c r="J69" s="3"/>
       <c r="K69" s="3"/>
-      <c r="L69" s="3">
-        <v>4.3304900000000002</v>
-      </c>
+      <c r="L69" s="3"/>
       <c r="M69" s="3"/>
-      <c r="N69" s="3">
-        <v>3.9704700000000002</v>
-      </c>
+      <c r="N69" s="3"/>
       <c r="O69" s="3"/>
-      <c r="P69" s="3">
-        <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
-        <v>4.9551916666666669</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P69" s="3"/>
+      <c r="R69" s="14"/>
+      <c r="S69" s="14"/>
+      <c r="T69" s="14"/>
+    </row>
+    <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
       <c r="B70" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="3">
-        <v>4.9245000000000001</v>
-      </c>
+      <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="3">
-        <v>5.9912099999999997</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3">
-        <v>5.8172800000000002</v>
-      </c>
+      <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-      <c r="J70" s="3">
-        <v>5.1707700000000001</v>
-      </c>
+      <c r="J70" s="3"/>
       <c r="K70" s="3"/>
-      <c r="L70" s="3">
-        <v>4.4135600000000004</v>
-      </c>
+      <c r="L70" s="3"/>
       <c r="M70" s="3"/>
-      <c r="N70" s="3">
-        <v>4.1507300000000003</v>
-      </c>
+      <c r="N70" s="3"/>
       <c r="O70" s="3"/>
-      <c r="P70" s="3">
-        <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
-        <v>5.0780083333333339</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P70" s="3"/>
+      <c r="R70" s="14"/>
+      <c r="S70" s="14"/>
+      <c r="T70" s="14"/>
+    </row>
+    <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
       <c r="B71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="4"/>
-      <c r="D71" s="4">
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="R71" s="14"/>
+      <c r="S71" s="14"/>
+      <c r="T71" s="14"/>
+    </row>
+    <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="17"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+      <c r="N72" s="16"/>
+      <c r="O72" s="16"/>
+      <c r="P72" s="16"/>
+      <c r="R72" s="14"/>
+      <c r="S72" s="14"/>
+      <c r="T72" s="14"/>
+    </row>
+    <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="17"/>
+      <c r="R73" s="14"/>
+      <c r="S73" s="14"/>
+      <c r="T73" s="14"/>
+    </row>
+    <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="R74" s="14"/>
+      <c r="S74" s="14"/>
+      <c r="T74" s="14"/>
+    </row>
+    <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9"/>
+      <c r="B75" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="11"/>
+      <c r="R75" s="14"/>
+      <c r="S75" s="14"/>
+      <c r="T75" s="14"/>
+    </row>
+    <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R76" s="14"/>
+      <c r="S76" s="14"/>
+      <c r="T76" s="14"/>
+    </row>
+    <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9"/>
+      <c r="B77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>4.8613999999999997</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3">
+        <v>5.88361</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3">
+        <v>5.5696399999999997</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3">
+        <v>5.0985699999999996</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>4.5044000000000004</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>4.0416400000000001</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3">
+        <f>AVERAGE(D77,F77,H77,J77,L77,N77)</f>
+        <v>4.9932100000000004</v>
+      </c>
+      <c r="R77" s="14"/>
+      <c r="S77" s="14"/>
+      <c r="T77" s="14"/>
+    </row>
+    <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="9"/>
+      <c r="B78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>5.0363800000000003</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <v>6.0898700000000003</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
+        <v>5.7049899999999996</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3">
+        <v>5.3215500000000002</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>4.7849199999999996</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3">
+        <v>4.2842399999999996</v>
+      </c>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3">
+        <f>AVERAGE(D78,F78,H78,J78,L78,N78)</f>
+        <v>5.2036583333333342</v>
+      </c>
+      <c r="R78" s="14"/>
+      <c r="S78" s="14"/>
+      <c r="T78" s="14"/>
+    </row>
+    <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9"/>
+      <c r="B79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3">
+        <v>5.1776600000000004</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
+        <v>6.1842800000000002</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3">
+        <v>5.8865100000000004</v>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3">
+        <v>5.48346</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3">
+        <v>4.9375</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>4.3942699999999997</v>
+      </c>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3">
+        <f>AVERAGE(D79,F79,H79,J79,L79,N79)</f>
+        <v>5.3439466666666675</v>
+      </c>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14"/>
+      <c r="T79" s="14"/>
+    </row>
+    <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3">
+        <v>5.2876300000000001</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3">
+        <v>6.2506199999999996</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3">
+        <v>5.9457700000000004</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3">
+        <v>5.5481100000000003</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3">
+        <v>5.0165199999999999</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3">
+        <v>4.5465</v>
+      </c>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3">
+        <f>AVERAGE(D80,F80,H80,J80,L80,N80)</f>
+        <v>5.4325250000000009</v>
+      </c>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14"/>
+      <c r="T80" s="14"/>
+    </row>
+    <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9"/>
+      <c r="B81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4">
+        <v>5.2888599999999997</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4">
+        <v>6.2779600000000002</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4">
+        <v>6.0451699999999997</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4">
+        <v>5.5814599999999999</v>
+      </c>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4">
+        <v>5.0148900000000003</v>
+      </c>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4">
+        <v>4.53064</v>
+      </c>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4">
+        <f>AVERAGE(D81,F81,H81,J81,L81,N81)</f>
+        <v>5.4564966666666663</v>
+      </c>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
+      <c r="T81" s="14"/>
+    </row>
+    <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
+      <c r="B82" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
+    </row>
+    <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9"/>
+      <c r="B83" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P83" s="11"/>
+      <c r="R83" s="14"/>
+      <c r="S83" s="14"/>
+      <c r="T83" s="14"/>
+    </row>
+    <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R84" s="14"/>
+      <c r="S84" s="14"/>
+      <c r="T84" s="14"/>
+    </row>
+    <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9"/>
+      <c r="B85" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3">
+        <v>4.39011</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3">
+        <v>5.6082400000000003</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3">
+        <v>5.3261500000000002</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3">
+        <v>4.6698899999999997</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3">
+        <v>4.1432399999999996</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3">
+        <v>3.7595499999999999</v>
+      </c>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3">
+        <f>AVERAGE(D85,F85,H85,J85,L85,N85)</f>
+        <v>4.6495299999999995</v>
+      </c>
+      <c r="R85" s="14"/>
+      <c r="S85" s="14"/>
+      <c r="T85" s="14"/>
+    </row>
+    <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9"/>
+      <c r="B86" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3">
+        <v>4.5535100000000002</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3">
+        <v>5.7491000000000003</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3">
+        <v>5.4894600000000002</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3">
+        <v>4.9547800000000004</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3">
+        <v>4.3115500000000004</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3">
+        <v>4.0073100000000004</v>
+      </c>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3">
+        <f>AVERAGE(D86,F86,H86,J86,L86,N86)</f>
+        <v>4.8442850000000002</v>
+      </c>
+      <c r="R86" s="14"/>
+      <c r="S86" s="14"/>
+      <c r="T86" s="14"/>
+    </row>
+    <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9"/>
+      <c r="B87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3">
+        <v>4.7401799999999996</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3">
+        <v>5.87758</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3">
+        <v>5.6888500000000004</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3">
+        <v>5.1455900000000003</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3">
+        <v>4.44956</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3">
+        <v>4.04033</v>
+      </c>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3">
+        <f>AVERAGE(D87,F87,H87,J87,L87,N87)</f>
+        <v>4.9903483333333325</v>
+      </c>
+      <c r="R87" s="14"/>
+      <c r="S87" s="14"/>
+      <c r="T87" s="14"/>
+    </row>
+    <row r="88" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9"/>
+      <c r="B88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>4.8115199999999998</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3">
+        <v>5.9385199999999996</v>
+      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3">
+        <v>5.6940099999999996</v>
+      </c>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3">
+        <v>5.04535</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3">
+        <v>4.57951</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3">
+        <v>4.1412100000000001</v>
+      </c>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3">
+        <f>AVERAGE(D88,F88,H88,J88,L88,N88)</f>
+        <v>5.0350199999999994</v>
+      </c>
+      <c r="R88" s="14"/>
+      <c r="S88" s="14"/>
+      <c r="T88" s="14"/>
+    </row>
+    <row r="89" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9"/>
+      <c r="B89" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4">
+        <v>4.7477600000000004</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4">
+        <v>6.0426799999999998</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4">
+        <v>5.7625099999999998</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4">
+        <v>5.2044899999999998</v>
+      </c>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4">
+        <v>4.6174200000000001</v>
+      </c>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4">
+        <v>4.1296299999999997</v>
+      </c>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4">
+        <f>AVERAGE(D89,F89,H89,J89,L89,N89)</f>
+        <v>5.0840816666666662</v>
+      </c>
+      <c r="R89" s="14"/>
+      <c r="S89" s="14"/>
+      <c r="T89" s="14"/>
+    </row>
+    <row r="92" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
+    </row>
+    <row r="93" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="9"/>
+      <c r="B93" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J93" s="11"/>
+      <c r="K93" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L93" s="11"/>
+      <c r="M93" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N93" s="11"/>
+      <c r="O93" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P93" s="11"/>
+    </row>
+    <row r="94" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="9"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="9"/>
+      <c r="B95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3">
+        <v>4.8350999999999997</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3">
+        <v>5.8418599999999996</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3">
+        <v>5.3804100000000004</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3">
+        <v>5.1307099999999997</v>
+      </c>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3">
+        <v>4.2869599999999997</v>
+      </c>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3">
+        <v>3.9249200000000002</v>
+      </c>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3">
+        <f>AVERAGE(D95,F95,H95,J95,L95,N95)</f>
+        <v>4.8999933333333336</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="9"/>
+      <c r="B96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3">
+        <v>5.0928699999999996</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3">
+        <v>5.9963899999999999</v>
+      </c>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3">
+        <v>5.7409499999999998</v>
+      </c>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3">
+        <v>5.3913000000000002</v>
+      </c>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3">
+        <v>4.4194800000000001</v>
+      </c>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3">
+        <v>4.1529199999999999</v>
+      </c>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3">
+        <f>AVERAGE(D96,F96,H96,J96,L96,N96)</f>
+        <v>5.132318333333334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="9"/>
+      <c r="B97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3">
+        <v>5.3201000000000001</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3">
+        <v>6.1637899999999997</v>
+      </c>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3">
+        <v>5.9080199999999996</v>
+      </c>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3">
+        <v>5.5360100000000001</v>
+      </c>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3">
+        <v>4.71347</v>
+      </c>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3">
+        <v>4.3147200000000003</v>
+      </c>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3">
+        <f>AVERAGE(D97,F97,H97,J97,L97,N97)</f>
+        <v>5.3260183333333337</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="9"/>
+      <c r="B98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3">
+        <v>5.36137</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3">
+        <v>6.2123900000000001</v>
+      </c>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3">
+        <v>6.0613599999999996</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3">
+        <v>5.5939699999999997</v>
+      </c>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3">
+        <v>4.8575299999999997</v>
+      </c>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3">
+        <v>4.4312899999999997</v>
+      </c>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3">
+        <f>AVERAGE(D98,F98,H98,J98,L98,N98)</f>
+        <v>5.4196516666666668</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="9"/>
+      <c r="B99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4">
+        <v>5.4131900000000002</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4">
+        <v>6.2545000000000002</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4">
+        <v>6.0812799999999996</v>
+      </c>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4">
+        <v>5.6418999999999997</v>
+      </c>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4">
+        <v>4.8334400000000004</v>
+      </c>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4">
+        <v>4.4951999999999996</v>
+      </c>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4">
+        <f>AVERAGE(D99,F99,H99,J99,L99,N99)</f>
+        <v>5.4532516666666666</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="9"/>
+      <c r="B100" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10"/>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10"/>
+      <c r="O100" s="10"/>
+      <c r="P100" s="10"/>
+    </row>
+    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="9"/>
+      <c r="B101" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="11"/>
+      <c r="K101" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="11"/>
+      <c r="M101" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N101" s="11"/>
+      <c r="O101" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P101" s="11"/>
+    </row>
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="9"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="9"/>
+      <c r="B103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3">
+        <v>4.4249700000000001</v>
+      </c>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3">
+        <v>5.5333399999999999</v>
+      </c>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3">
+        <v>5.1902999999999997</v>
+      </c>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3">
+        <v>4.8660300000000003</v>
+      </c>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3">
+        <v>3.8866299999999998</v>
+      </c>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3">
+        <v>3.6355400000000002</v>
+      </c>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3">
+        <f>AVERAGE(D103,F103,H103,J103,L103,N103)</f>
+        <v>4.5894683333333335</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="9"/>
+      <c r="B104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3">
+        <v>4.66181</v>
+      </c>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3">
+        <v>5.6358699999999997</v>
+      </c>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3">
+        <v>5.5303500000000003</v>
+      </c>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3">
+        <v>4.9067100000000003</v>
+      </c>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3">
+        <v>4.1264799999999999</v>
+      </c>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3">
+        <v>3.8291499999999998</v>
+      </c>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3">
+        <f>AVERAGE(D104,F104,H104,J104,L104,N104)</f>
+        <v>4.7817283333333336</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="9"/>
+      <c r="B105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3">
+        <v>4.8665000000000003</v>
+      </c>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3">
+        <v>5.8399900000000002</v>
+      </c>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3">
+        <v>5.65158</v>
+      </c>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3">
+        <v>5.07212</v>
+      </c>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3">
+        <v>4.3304900000000002</v>
+      </c>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3">
+        <v>3.9704700000000002</v>
+      </c>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3">
+        <f>AVERAGE(D105,F105,H105,J105,L105,N105)</f>
+        <v>4.9551916666666669</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="9"/>
+      <c r="B106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3">
+        <v>4.9245000000000001</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3">
+        <v>5.9912099999999997</v>
+      </c>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3">
+        <v>5.8172800000000002</v>
+      </c>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3">
+        <v>5.1707700000000001</v>
+      </c>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3">
+        <v>4.4135600000000004</v>
+      </c>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3">
+        <v>4.1507300000000003</v>
+      </c>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3">
+        <f>AVERAGE(D106,F106,H106,J106,L106,N106)</f>
+        <v>5.0780083333333339</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="9"/>
+      <c r="B107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4">
         <v>4.8952299999999997</v>
       </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4">
+      <c r="E107" s="4"/>
+      <c r="F107" s="4">
         <v>6.0022099999999998</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4">
+      <c r="G107" s="4"/>
+      <c r="H107" s="4">
         <v>5.8484299999999996</v>
       </c>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4">
+      <c r="I107" s="4"/>
+      <c r="J107" s="4">
         <v>5.3302800000000001</v>
       </c>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4">
+      <c r="K107" s="4"/>
+      <c r="L107" s="4">
         <v>4.4426100000000002</v>
       </c>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4">
+      <c r="M107" s="4"/>
+      <c r="N107" s="4">
         <v>4.1807600000000003</v>
       </c>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4">
-        <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4">
+        <f>AVERAGE(D107,F107,H107,J107,L107,N107)</f>
         <v>5.1165866666666666</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
+  <mergeCells count="115">
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="M65:N65"/>
     <mergeCell ref="O65:P65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="A38:A53"/>
-    <mergeCell ref="B38:P38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B46:P46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O47:P47"/>
     <mergeCell ref="A56:A71"/>
     <mergeCell ref="B56:P56"/>
     <mergeCell ref="B57:B58"/>
@@ -6929,13 +7962,52 @@
     <mergeCell ref="B64:P64"/>
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="B82:P82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="A92:A107"/>
+    <mergeCell ref="B92:P92"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="O93:P93"/>
+    <mergeCell ref="B100:P100"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A74:A89"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="O11:P11"/>
     <mergeCell ref="A20:A35"/>
@@ -6950,7 +8022,17 @@
     <mergeCell ref="O21:P21"/>
     <mergeCell ref="B28:P28"/>
     <mergeCell ref="B29:B30"/>
-    <mergeCell ref="R2:T53"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="R2:T89"/>
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:B4"/>
@@ -6963,9 +8045,22 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="B10:P10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A38:A53"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D47"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A0C25A-CFE1-4E10-8991-4EF4CB468DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124EE7BD-FF67-4EF7-9123-7612D11DA046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="47">
   <si>
     <t>Data Num.</t>
   </si>
@@ -328,7 +328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -372,15 +372,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4496,7 +4487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D606126C-3FE1-428A-BDA2-93CD7E4A00CB}">
-  <dimension ref="A2:T107"/>
+  <dimension ref="A2:T103"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -5922,19 +5913,34 @@
         <v>9</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>4.9636199999999997</v>
+      </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3">
+        <v>5.8313199999999998</v>
+      </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="3">
+        <v>5.6455599999999997</v>
+      </c>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+      <c r="J42" s="3">
+        <v>5.1763000000000003</v>
+      </c>
       <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="L42" s="3">
+        <v>4.6677099999999996</v>
+      </c>
       <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="N42" s="3">
+        <v>4.0916800000000002</v>
+      </c>
       <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
+      <c r="P42" s="3">
+        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
+        <v>5.0626983333333335</v>
+      </c>
       <c r="R42" s="14"/>
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
@@ -5945,19 +5951,34 @@
         <v>10</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>5.1536600000000004</v>
+      </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3">
+        <v>6.0681799999999999</v>
+      </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="3">
+        <v>5.8374499999999996</v>
+      </c>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="3">
+        <v>5.4357300000000004</v>
+      </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="L43" s="3">
+        <v>4.9444400000000002</v>
+      </c>
       <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="N43" s="3">
+        <v>4.3256100000000002</v>
+      </c>
       <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
+      <c r="P43" s="3">
+        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
+        <v>5.2941783333333339</v>
+      </c>
       <c r="R43" s="14"/>
       <c r="S43" s="14"/>
       <c r="T43" s="14"/>
@@ -6161,19 +6182,34 @@
         <v>9</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3">
+        <v>4.47675</v>
+      </c>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3">
+        <v>5.66073</v>
+      </c>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
+      <c r="H50" s="3">
+        <v>5.4292499999999997</v>
+      </c>
       <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
+      <c r="J50" s="3">
+        <v>4.84232</v>
+      </c>
       <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
+      <c r="L50" s="3">
+        <v>4.2573600000000003</v>
+      </c>
       <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
+      <c r="N50" s="3">
+        <v>3.7513200000000002</v>
+      </c>
       <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
+      <c r="P50" s="3">
+        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
+        <v>4.7362883333333334</v>
+      </c>
       <c r="R50" s="14"/>
       <c r="S50" s="14"/>
       <c r="T50" s="14"/>
@@ -6184,19 +6220,34 @@
         <v>10</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3">
+        <v>4.6834899999999999</v>
+      </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3">
+        <v>5.8116199999999996</v>
+      </c>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
+      <c r="H51" s="3">
+        <v>5.6635</v>
+      </c>
       <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
+      <c r="J51" s="3">
+        <v>5.0595999999999997</v>
+      </c>
       <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="L51" s="3">
+        <v>4.5441099999999999</v>
+      </c>
       <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+      <c r="N51" s="3">
+        <v>4.0245899999999999</v>
+      </c>
       <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
+      <c r="P51" s="3">
+        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
+        <v>4.9644849999999998</v>
+      </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
@@ -6437,199 +6488,259 @@
     <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3">
+        <v>4.8698699999999997</v>
+      </c>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3">
+        <v>5.9710700000000001</v>
+      </c>
       <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
+      <c r="H60" s="3">
+        <v>5.6823300000000003</v>
+      </c>
       <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
+      <c r="J60" s="3">
+        <v>5.1452799999999996</v>
+      </c>
       <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
+      <c r="L60" s="3">
+        <v>4.7675299999999998</v>
+      </c>
       <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
+      <c r="N60" s="3">
+        <v>4.1111500000000003</v>
+      </c>
       <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
+      <c r="P60" s="3">
+        <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
+        <v>5.0912049999999995</v>
+      </c>
       <c r="R60" s="14"/>
       <c r="S60" s="14"/>
       <c r="T60" s="14"/>
     </row>
     <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
-      <c r="B61" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
+      <c r="B61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4">
+        <v>4.9489000000000001</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4">
+        <v>6.0358900000000002</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4">
+        <v>5.8227900000000004</v>
+      </c>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4">
+        <v>5.1799600000000003</v>
+      </c>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4">
+        <v>4.76105</v>
+      </c>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4">
+        <v>4.1094099999999996</v>
+      </c>
+      <c r="O61" s="4"/>
+      <c r="P61" s="3">
+        <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
+        <v>5.1430000000000007</v>
+      </c>
       <c r="R61" s="14"/>
       <c r="S61" s="14"/>
       <c r="T61" s="14"/>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
-      <c r="B62" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
+      <c r="B62" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
       <c r="R62" s="14"/>
       <c r="S62" s="14"/>
       <c r="T62" s="14"/>
     </row>
     <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
-      <c r="B63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
+      <c r="B63" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J63" s="11"/>
+      <c r="K63" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N63" s="11"/>
+      <c r="O63" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P63" s="11"/>
       <c r="R63" s="14"/>
       <c r="S63" s="14"/>
       <c r="T63" s="14"/>
     </row>
     <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
-      <c r="B64" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="R64" s="14"/>
       <c r="S64" s="14"/>
       <c r="T64" s="14"/>
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
-      <c r="B65" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P65" s="11"/>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3">
+        <v>4.2968700000000002</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3">
+        <v>5.4696899999999999</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3">
+        <v>5.2728200000000003</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3">
+        <v>4.5333500000000004</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3">
+        <v>4.0951500000000003</v>
+      </c>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3">
+        <v>3.5975899999999998</v>
+      </c>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3">
+        <f>AVERAGE(D65,F65,H65,J65,L65,N65)</f>
+        <v>4.5442450000000001</v>
+      </c>
       <c r="R65" s="14"/>
       <c r="S65" s="14"/>
       <c r="T65" s="14"/>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>16</v>
+      <c r="B66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3">
+        <v>4.4737999999999998</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3">
+        <v>5.60236</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3">
+        <v>5.5017800000000001</v>
+      </c>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3">
+        <v>4.8213200000000001</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3">
+        <v>4.4157700000000002</v>
+      </c>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3">
+        <v>3.8286199999999999</v>
+      </c>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3">
+        <f>AVERAGE(D66,F66,H66,J66,L66,N66)</f>
+        <v>4.7739416666666665</v>
       </c>
       <c r="R66" s="14"/>
       <c r="S66" s="14"/>
@@ -6637,47 +6748,43 @@
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
-      <c r="B67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3">
-        <v>4.2968700000000002</v>
-      </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3">
-        <v>5.4696899999999999</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3">
-        <v>5.2728200000000003</v>
-      </c>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3">
-        <v>4.5333500000000004</v>
-      </c>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3">
-        <v>4.0951500000000003</v>
-      </c>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3">
-        <v>3.5975899999999998</v>
-      </c>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3">
+      <c r="B67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4">
+        <v>4.5378999999999996</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4">
+        <v>5.7141900000000003</v>
+      </c>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4">
+        <v>5.5835900000000001</v>
+      </c>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4">
+        <v>4.79148</v>
+      </c>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4">
+        <v>4.3329700000000004</v>
+      </c>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4">
+        <v>3.7964500000000001</v>
+      </c>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4">
         <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
-        <v>4.5442450000000001</v>
+        <v>4.7927633333333333</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="14"/>
       <c r="T67" s="14"/>
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
-      <c r="B68" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6697,207 +6804,268 @@
       <c r="T68" s="14"/>
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
-      <c r="B69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
       <c r="R69" s="14"/>
       <c r="S69" s="14"/>
       <c r="T69" s="14"/>
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9"/>
-      <c r="B70" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
+      <c r="A70" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
       <c r="R70" s="14"/>
       <c r="S70" s="14"/>
       <c r="T70" s="14"/>
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
-      <c r="B71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
+      <c r="B71" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N71" s="11"/>
+      <c r="O71" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P71" s="11"/>
       <c r="R71" s="14"/>
       <c r="S71" s="14"/>
       <c r="T71" s="14"/>
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="17"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="16"/>
-      <c r="O72" s="16"/>
-      <c r="P72" s="16"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="R72" s="14"/>
       <c r="S72" s="14"/>
       <c r="T72" s="14"/>
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="17"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3">
+        <v>4.8613999999999997</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3">
+        <v>5.88361</v>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3">
+        <v>5.5696399999999997</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3">
+        <v>5.0985699999999996</v>
+      </c>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3">
+        <v>4.5044000000000004</v>
+      </c>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3">
+        <v>4.0416400000000001</v>
+      </c>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3">
+        <f>AVERAGE(D73,F73,H73,J73,L73,N73)</f>
+        <v>4.9932100000000004</v>
+      </c>
       <c r="R73" s="14"/>
       <c r="S73" s="14"/>
       <c r="T73" s="14"/>
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="10"/>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3">
+        <v>5.0363800000000003</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3">
+        <v>6.0898700000000003</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3">
+        <v>5.7049899999999996</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3">
+        <v>5.3215500000000002</v>
+      </c>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3">
+        <v>4.7849199999999996</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3">
+        <v>4.2842399999999996</v>
+      </c>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3">
+        <f>AVERAGE(D74,F74,H74,J74,L74,N74)</f>
+        <v>5.2036583333333342</v>
+      </c>
       <c r="R74" s="14"/>
       <c r="S74" s="14"/>
       <c r="T74" s="14"/>
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
-      <c r="B75" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J75" s="11"/>
-      <c r="K75" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P75" s="11"/>
+      <c r="B75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3">
+        <v>5.1776600000000004</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3">
+        <v>6.1842800000000002</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3">
+        <v>5.8865100000000004</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3">
+        <v>5.48346</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3">
+        <v>4.9375</v>
+      </c>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3">
+        <v>4.3942699999999997</v>
+      </c>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3">
+        <f>AVERAGE(D75,F75,H75,J75,L75,N75)</f>
+        <v>5.3439466666666675</v>
+      </c>
       <c r="R75" s="14"/>
       <c r="S75" s="14"/>
       <c r="T75" s="14"/>
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>16</v>
+      <c r="B76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3">
+        <v>5.2876300000000001</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3">
+        <v>6.2506199999999996</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3">
+        <v>5.9457700000000004</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3">
+        <v>5.5481100000000003</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3">
+        <v>5.0165199999999999</v>
+      </c>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3">
+        <v>4.5465</v>
+      </c>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3">
+        <f>AVERAGE(D76,F76,H76,J76,L76,N76)</f>
+        <v>5.4325250000000009</v>
       </c>
       <c r="R76" s="14"/>
       <c r="S76" s="14"/>
@@ -6905,37 +7073,37 @@
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
-      <c r="B77" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3">
-        <v>4.8613999999999997</v>
-      </c>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3">
-        <v>5.88361</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3">
-        <v>5.5696399999999997</v>
-      </c>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3">
-        <v>5.0985699999999996</v>
-      </c>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3">
-        <v>4.5044000000000004</v>
-      </c>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3">
-        <v>4.0416400000000001</v>
-      </c>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3">
+      <c r="B77" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4">
+        <v>5.2888599999999997</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4">
+        <v>6.2779600000000002</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4">
+        <v>6.0451699999999997</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4">
+        <v>5.5814599999999999</v>
+      </c>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4">
+        <v>5.0148900000000003</v>
+      </c>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4">
+        <v>4.53064</v>
+      </c>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4">
         <f>AVERAGE(D77,F77,H77,J77,L77,N77)</f>
-        <v>4.9932100000000004</v>
+        <v>5.4564966666666663</v>
       </c>
       <c r="R77" s="14"/>
       <c r="S77" s="14"/>
@@ -6943,113 +7111,108 @@
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
-      <c r="B78" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3">
-        <v>5.0363800000000003</v>
-      </c>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3">
-        <v>6.0898700000000003</v>
-      </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3">
-        <v>5.7049899999999996</v>
-      </c>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3">
-        <v>5.3215500000000002</v>
-      </c>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3">
-        <v>4.7849199999999996</v>
-      </c>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3">
-        <v>4.2842399999999996</v>
-      </c>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3">
-        <f>AVERAGE(D78,F78,H78,J78,L78,N78)</f>
-        <v>5.2036583333333342</v>
-      </c>
+      <c r="B78" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="10"/>
+      <c r="I78" s="10"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
       <c r="R78" s="14"/>
       <c r="S78" s="14"/>
       <c r="T78" s="14"/>
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
-      <c r="B79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3">
-        <v>5.1776600000000004</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3">
-        <v>6.1842800000000002</v>
-      </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3">
-        <v>5.8865100000000004</v>
-      </c>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3">
-        <v>5.48346</v>
-      </c>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3">
-        <v>4.9375</v>
-      </c>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3">
-        <v>4.3942699999999997</v>
-      </c>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3">
-        <f>AVERAGE(D79,F79,H79,J79,L79,N79)</f>
-        <v>5.3439466666666675</v>
-      </c>
+      <c r="B79" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N79" s="11"/>
+      <c r="O79" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P79" s="11"/>
       <c r="R79" s="14"/>
       <c r="S79" s="14"/>
       <c r="T79" s="14"/>
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
-      <c r="B80" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3">
-        <v>5.2876300000000001</v>
-      </c>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3">
-        <v>6.2506199999999996</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3">
-        <v>5.9457700000000004</v>
-      </c>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3">
-        <v>5.5481100000000003</v>
-      </c>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3">
-        <v>5.0165199999999999</v>
-      </c>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3">
-        <v>4.5465</v>
-      </c>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3">
-        <f>AVERAGE(D80,F80,H80,J80,L80,N80)</f>
-        <v>5.4325250000000009</v>
+      <c r="B80" s="12"/>
+      <c r="C80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="R80" s="14"/>
       <c r="S80" s="14"/>
@@ -7057,37 +7220,37 @@
     </row>
     <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
-      <c r="B81" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4">
-        <v>5.2888599999999997</v>
-      </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4">
-        <v>6.2779600000000002</v>
-      </c>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4">
-        <v>6.0451699999999997</v>
-      </c>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4">
-        <v>5.5814599999999999</v>
-      </c>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4">
-        <v>5.0148900000000003</v>
-      </c>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4">
-        <v>4.53064</v>
-      </c>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4">
+      <c r="B81" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3">
+        <v>4.39011</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3">
+        <v>5.6082400000000003</v>
+      </c>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3">
+        <v>5.3261500000000002</v>
+      </c>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3">
+        <v>4.6698899999999997</v>
+      </c>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3">
+        <v>4.1432399999999996</v>
+      </c>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3">
+        <v>3.7595499999999999</v>
+      </c>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3">
         <f>AVERAGE(D81,F81,H81,J81,L81,N81)</f>
-        <v>5.4564966666666663</v>
+        <v>4.6495299999999995</v>
       </c>
       <c r="R81" s="14"/>
       <c r="S81" s="14"/>
@@ -7095,108 +7258,113 @@
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
-      <c r="B82" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="10"/>
-      <c r="M82" s="10"/>
-      <c r="N82" s="10"/>
-      <c r="O82" s="10"/>
-      <c r="P82" s="10"/>
+      <c r="B82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3">
+        <v>4.5535100000000002</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3">
+        <v>5.7491000000000003</v>
+      </c>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3">
+        <v>5.4894600000000002</v>
+      </c>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3">
+        <v>4.9547800000000004</v>
+      </c>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3">
+        <v>4.3115500000000004</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3">
+        <v>4.0073100000000004</v>
+      </c>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3">
+        <f>AVERAGE(D82,F82,H82,J82,L82,N82)</f>
+        <v>4.8442850000000002</v>
+      </c>
       <c r="R82" s="14"/>
       <c r="S82" s="14"/>
       <c r="T82" s="14"/>
     </row>
     <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
-      <c r="B83" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="11"/>
-      <c r="K83" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N83" s="11"/>
-      <c r="O83" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P83" s="11"/>
+      <c r="B83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3">
+        <v>4.7401799999999996</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3">
+        <v>5.87758</v>
+      </c>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3">
+        <v>5.6888500000000004</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3">
+        <v>5.1455900000000003</v>
+      </c>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3">
+        <v>4.44956</v>
+      </c>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3">
+        <v>4.04033</v>
+      </c>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3">
+        <f>AVERAGE(D83,F83,H83,J83,L83,N83)</f>
+        <v>4.9903483333333325</v>
+      </c>
       <c r="R83" s="14"/>
       <c r="S83" s="14"/>
       <c r="T83" s="14"/>
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P84" s="2" t="s">
-        <v>16</v>
+      <c r="B84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3">
+        <v>4.8115199999999998</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3">
+        <v>5.9385199999999996</v>
+      </c>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3">
+        <v>5.6940099999999996</v>
+      </c>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3">
+        <v>5.04535</v>
+      </c>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3">
+        <v>4.57951</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3">
+        <v>4.1412100000000001</v>
+      </c>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3">
+        <f>AVERAGE(D84,F84,H84,J84,L84,N84)</f>
+        <v>5.0350199999999994</v>
       </c>
       <c r="R84" s="14"/>
       <c r="S84" s="14"/>
@@ -7204,752 +7372,600 @@
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
-      <c r="B85" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3">
-        <v>4.39011</v>
-      </c>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3">
-        <v>5.6082400000000003</v>
-      </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3">
-        <v>5.3261500000000002</v>
-      </c>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3">
-        <v>4.6698899999999997</v>
-      </c>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3">
-        <v>4.1432399999999996</v>
-      </c>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3">
-        <v>3.7595499999999999</v>
-      </c>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3">
+      <c r="B85" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4">
+        <v>4.7477600000000004</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4">
+        <v>6.0426799999999998</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4">
+        <v>5.7625099999999998</v>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4">
+        <v>5.2044899999999998</v>
+      </c>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4">
+        <v>4.6174200000000001</v>
+      </c>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4">
+        <v>4.1296299999999997</v>
+      </c>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4">
         <f>AVERAGE(D85,F85,H85,J85,L85,N85)</f>
-        <v>4.6495299999999995</v>
+        <v>5.0840816666666662</v>
       </c>
       <c r="R85" s="14"/>
       <c r="S85" s="14"/>
       <c r="T85" s="14"/>
     </row>
-    <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9"/>
-      <c r="B86" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3">
-        <v>4.5535100000000002</v>
-      </c>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3">
-        <v>5.7491000000000003</v>
-      </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3">
-        <v>5.4894600000000002</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3">
-        <v>4.9547800000000004</v>
-      </c>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3">
-        <v>4.3115500000000004</v>
-      </c>
-      <c r="M86" s="3"/>
-      <c r="N86" s="3">
-        <v>4.0073100000000004</v>
-      </c>
-      <c r="O86" s="3"/>
-      <c r="P86" s="3">
-        <f>AVERAGE(D86,F86,H86,J86,L86,N86)</f>
-        <v>4.8442850000000002</v>
-      </c>
-      <c r="R86" s="14"/>
-      <c r="S86" s="14"/>
-      <c r="T86" s="14"/>
-    </row>
-    <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="9"/>
-      <c r="B87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3">
-        <v>4.7401799999999996</v>
-      </c>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3">
-        <v>5.87758</v>
-      </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3">
-        <v>5.6888500000000004</v>
-      </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3">
-        <v>5.1455900000000003</v>
-      </c>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3">
-        <v>4.44956</v>
-      </c>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3">
-        <v>4.04033</v>
-      </c>
-      <c r="O87" s="3"/>
-      <c r="P87" s="3">
-        <f>AVERAGE(D87,F87,H87,J87,L87,N87)</f>
-        <v>4.9903483333333325</v>
-      </c>
-      <c r="R87" s="14"/>
-      <c r="S87" s="14"/>
-      <c r="T87" s="14"/>
-    </row>
     <row r="88" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="9"/>
-      <c r="B88" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3">
-        <v>4.8115199999999998</v>
-      </c>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3">
-        <v>5.9385199999999996</v>
-      </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3">
-        <v>5.6940099999999996</v>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3">
-        <v>5.04535</v>
-      </c>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3">
-        <v>4.57951</v>
-      </c>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3">
-        <v>4.1412100000000001</v>
-      </c>
-      <c r="O88" s="3"/>
-      <c r="P88" s="3">
-        <f>AVERAGE(D88,F88,H88,J88,L88,N88)</f>
-        <v>5.0350199999999994</v>
-      </c>
-      <c r="R88" s="14"/>
-      <c r="S88" s="14"/>
-      <c r="T88" s="14"/>
+      <c r="A88" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="10"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
-      <c r="B89" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4">
-        <v>4.7477600000000004</v>
-      </c>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4">
-        <v>6.0426799999999998</v>
-      </c>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4">
-        <v>5.7625099999999998</v>
-      </c>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4">
-        <v>5.2044899999999998</v>
-      </c>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4">
-        <v>4.6174200000000001</v>
-      </c>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4">
-        <v>4.1296299999999997</v>
-      </c>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4">
-        <f>AVERAGE(D89,F89,H89,J89,L89,N89)</f>
-        <v>5.0840816666666662</v>
-      </c>
-      <c r="R89" s="14"/>
-      <c r="S89" s="14"/>
-      <c r="T89" s="14"/>
+      <c r="B89" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="11"/>
+      <c r="M89" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N89" s="11"/>
+      <c r="O89" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P89" s="11"/>
+    </row>
+    <row r="90" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="9"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="9"/>
+      <c r="B91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3">
+        <v>4.8350999999999997</v>
+      </c>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3">
+        <v>5.8418599999999996</v>
+      </c>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3">
+        <v>5.3804100000000004</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3">
+        <v>5.1307099999999997</v>
+      </c>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3">
+        <v>4.2869599999999997</v>
+      </c>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3">
+        <v>3.9249200000000002</v>
+      </c>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3">
+        <f>AVERAGE(D91,F91,H91,J91,L91,N91)</f>
+        <v>4.8999933333333336</v>
+      </c>
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
-      <c r="N92" s="10"/>
-      <c r="O92" s="10"/>
-      <c r="P92" s="10"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3">
+        <v>5.0928699999999996</v>
+      </c>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3">
+        <v>5.9963899999999999</v>
+      </c>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3">
+        <v>5.7409499999999998</v>
+      </c>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3">
+        <v>5.3913000000000002</v>
+      </c>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3">
+        <v>4.4194800000000001</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3">
+        <v>4.1529199999999999</v>
+      </c>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3">
+        <f>AVERAGE(D92,F92,H92,J92,L92,N92)</f>
+        <v>5.132318333333334</v>
+      </c>
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9"/>
-      <c r="B93" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H93" s="11"/>
-      <c r="I93" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N93" s="11"/>
-      <c r="O93" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P93" s="11"/>
+      <c r="B93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3">
+        <v>5.3201000000000001</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3">
+        <v>6.1637899999999997</v>
+      </c>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3">
+        <v>5.9080199999999996</v>
+      </c>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3">
+        <v>5.5360100000000001</v>
+      </c>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3">
+        <v>4.71347</v>
+      </c>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3">
+        <v>4.3147200000000003</v>
+      </c>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3">
+        <f>AVERAGE(D93,F93,H93,J93,L93,N93)</f>
+        <v>5.3260183333333337</v>
+      </c>
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P94" s="2" t="s">
-        <v>16</v>
+      <c r="B94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3">
+        <v>5.36137</v>
+      </c>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3">
+        <v>6.2123900000000001</v>
+      </c>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3">
+        <v>6.0613599999999996</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3">
+        <v>5.5939699999999997</v>
+      </c>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3">
+        <v>4.8575299999999997</v>
+      </c>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3">
+        <v>4.4312899999999997</v>
+      </c>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3">
+        <f>AVERAGE(D94,F94,H94,J94,L94,N94)</f>
+        <v>5.4196516666666668</v>
       </c>
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
-      <c r="B95" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3">
-        <v>4.8350999999999997</v>
-      </c>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3">
-        <v>5.8418599999999996</v>
-      </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3">
-        <v>5.3804100000000004</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3">
-        <v>5.1307099999999997</v>
-      </c>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3">
-        <v>4.2869599999999997</v>
-      </c>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3">
-        <v>3.9249200000000002</v>
-      </c>
-      <c r="O95" s="3"/>
-      <c r="P95" s="3">
+      <c r="B95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4">
+        <v>5.4131900000000002</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4">
+        <v>6.2545000000000002</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4">
+        <v>6.0812799999999996</v>
+      </c>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4">
+        <v>5.6418999999999997</v>
+      </c>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4">
+        <v>4.8334400000000004</v>
+      </c>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4">
+        <v>4.4951999999999996</v>
+      </c>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4">
         <f>AVERAGE(D95,F95,H95,J95,L95,N95)</f>
-        <v>4.8999933333333336</v>
+        <v>5.4532516666666666</v>
       </c>
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9"/>
-      <c r="B96" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3">
-        <v>5.0928699999999996</v>
-      </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3">
-        <v>5.9963899999999999</v>
-      </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3">
-        <v>5.7409499999999998</v>
-      </c>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3">
-        <v>5.3913000000000002</v>
-      </c>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3">
-        <v>4.4194800000000001</v>
-      </c>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3">
-        <v>4.1529199999999999</v>
-      </c>
-      <c r="O96" s="3"/>
-      <c r="P96" s="3">
-        <f>AVERAGE(D96,F96,H96,J96,L96,N96)</f>
-        <v>5.132318333333334</v>
-      </c>
+      <c r="B96" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
     </row>
     <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9"/>
-      <c r="B97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3">
-        <v>5.3201000000000001</v>
-      </c>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3">
-        <v>6.1637899999999997</v>
-      </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3">
-        <v>5.9080199999999996</v>
-      </c>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3">
-        <v>5.5360100000000001</v>
-      </c>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3">
-        <v>4.71347</v>
-      </c>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3">
-        <v>4.3147200000000003</v>
-      </c>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3">
-        <f>AVERAGE(D97,F97,H97,J97,L97,N97)</f>
-        <v>5.3260183333333337</v>
-      </c>
+      <c r="B97" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J97" s="11"/>
+      <c r="K97" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L97" s="11"/>
+      <c r="M97" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N97" s="11"/>
+      <c r="O97" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P97" s="11"/>
     </row>
     <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9"/>
-      <c r="B98" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3">
-        <v>5.36137</v>
-      </c>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3">
-        <v>6.2123900000000001</v>
-      </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3">
-        <v>6.0613599999999996</v>
-      </c>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3">
-        <v>5.5939699999999997</v>
-      </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3">
-        <v>4.8575299999999997</v>
-      </c>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3">
-        <v>4.4312899999999997</v>
-      </c>
-      <c r="O98" s="3"/>
-      <c r="P98" s="3">
-        <f>AVERAGE(D98,F98,H98,J98,L98,N98)</f>
-        <v>5.4196516666666668</v>
+      <c r="B98" s="12"/>
+      <c r="C98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
-      <c r="B99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4">
-        <v>5.4131900000000002</v>
-      </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4">
-        <v>6.2545000000000002</v>
-      </c>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4">
-        <v>6.0812799999999996</v>
-      </c>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4">
-        <v>5.6418999999999997</v>
-      </c>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4">
-        <v>4.8334400000000004</v>
-      </c>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4">
-        <v>4.4951999999999996</v>
-      </c>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4">
+      <c r="B99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3">
+        <v>4.4249700000000001</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3">
+        <v>5.5333399999999999</v>
+      </c>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3">
+        <v>5.1902999999999997</v>
+      </c>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3">
+        <v>4.8660300000000003</v>
+      </c>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3">
+        <v>3.8866299999999998</v>
+      </c>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3">
+        <v>3.6355400000000002</v>
+      </c>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3">
         <f>AVERAGE(D99,F99,H99,J99,L99,N99)</f>
-        <v>5.4532516666666666</v>
+        <v>4.5894683333333335</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9"/>
-      <c r="B100" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="10"/>
-      <c r="M100" s="10"/>
-      <c r="N100" s="10"/>
-      <c r="O100" s="10"/>
-      <c r="P100" s="10"/>
+      <c r="B100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3">
+        <v>4.66181</v>
+      </c>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3">
+        <v>5.6358699999999997</v>
+      </c>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3">
+        <v>5.5303500000000003</v>
+      </c>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3">
+        <v>4.9067100000000003</v>
+      </c>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3">
+        <v>4.1264799999999999</v>
+      </c>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3">
+        <v>3.8291499999999998</v>
+      </c>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3">
+        <f>AVERAGE(D100,F100,H100,J100,L100,N100)</f>
+        <v>4.7817283333333336</v>
+      </c>
     </row>
     <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
-      <c r="B101" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="11"/>
-      <c r="I101" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="11"/>
-      <c r="K101" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="11"/>
-      <c r="M101" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N101" s="11"/>
-      <c r="O101" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P101" s="11"/>
+      <c r="B101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3">
+        <v>4.8665000000000003</v>
+      </c>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3">
+        <v>5.8399900000000002</v>
+      </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3">
+        <v>5.65158</v>
+      </c>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3">
+        <v>5.07212</v>
+      </c>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3">
+        <v>4.3304900000000002</v>
+      </c>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3">
+        <v>3.9704700000000002</v>
+      </c>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3">
+        <f>AVERAGE(D101,F101,H101,J101,L101,N101)</f>
+        <v>4.9551916666666669</v>
+      </c>
     </row>
     <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P102" s="2" t="s">
-        <v>16</v>
+      <c r="B102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3">
+        <v>4.9245000000000001</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3">
+        <v>5.9912099999999997</v>
+      </c>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3">
+        <v>5.8172800000000002</v>
+      </c>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3">
+        <v>5.1707700000000001</v>
+      </c>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3">
+        <v>4.4135600000000004</v>
+      </c>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3">
+        <v>4.1507300000000003</v>
+      </c>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3">
+        <f>AVERAGE(D102,F102,H102,J102,L102,N102)</f>
+        <v>5.0780083333333339</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9"/>
-      <c r="B103" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3">
-        <v>4.4249700000000001</v>
-      </c>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3">
-        <v>5.5333399999999999</v>
-      </c>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3">
-        <v>5.1902999999999997</v>
-      </c>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3">
-        <v>4.8660300000000003</v>
-      </c>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3">
-        <v>3.8866299999999998</v>
-      </c>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3">
-        <v>3.6355400000000002</v>
-      </c>
-      <c r="O103" s="3"/>
-      <c r="P103" s="3">
+      <c r="B103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4">
+        <v>4.8952299999999997</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4">
+        <v>6.0022099999999998</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4">
+        <v>5.8484299999999996</v>
+      </c>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4">
+        <v>5.3302800000000001</v>
+      </c>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4">
+        <v>4.4426100000000002</v>
+      </c>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4">
+        <v>4.1807600000000003</v>
+      </c>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4">
         <f>AVERAGE(D103,F103,H103,J103,L103,N103)</f>
-        <v>4.5894683333333335</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="9"/>
-      <c r="B104" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3">
-        <v>4.66181</v>
-      </c>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3">
-        <v>5.6358699999999997</v>
-      </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3">
-        <v>5.5303500000000003</v>
-      </c>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3">
-        <v>4.9067100000000003</v>
-      </c>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3">
-        <v>4.1264799999999999</v>
-      </c>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3">
-        <v>3.8291499999999998</v>
-      </c>
-      <c r="O104" s="3"/>
-      <c r="P104" s="3">
-        <f>AVERAGE(D104,F104,H104,J104,L104,N104)</f>
-        <v>4.7817283333333336</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="9"/>
-      <c r="B105" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3">
-        <v>4.8665000000000003</v>
-      </c>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3">
-        <v>5.8399900000000002</v>
-      </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3">
-        <v>5.65158</v>
-      </c>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3">
-        <v>5.07212</v>
-      </c>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3">
-        <v>4.3304900000000002</v>
-      </c>
-      <c r="M105" s="3"/>
-      <c r="N105" s="3">
-        <v>3.9704700000000002</v>
-      </c>
-      <c r="O105" s="3"/>
-      <c r="P105" s="3">
-        <f>AVERAGE(D105,F105,H105,J105,L105,N105)</f>
-        <v>4.9551916666666669</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9"/>
-      <c r="B106" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3">
-        <v>4.9245000000000001</v>
-      </c>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3">
-        <v>5.9912099999999997</v>
-      </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3">
-        <v>5.8172800000000002</v>
-      </c>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3">
-        <v>5.1707700000000001</v>
-      </c>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3">
-        <v>4.4135600000000004</v>
-      </c>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3">
-        <v>4.1507300000000003</v>
-      </c>
-      <c r="O106" s="3"/>
-      <c r="P106" s="3">
-        <f>AVERAGE(D106,F106,H106,J106,L106,N106)</f>
-        <v>5.0780083333333339</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="9"/>
-      <c r="B107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4">
-        <v>4.8952299999999997</v>
-      </c>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4">
-        <v>6.0022099999999998</v>
-      </c>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4">
-        <v>5.8484299999999996</v>
-      </c>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4">
-        <v>5.3302800000000001</v>
-      </c>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4">
-        <v>4.4426100000000002</v>
-      </c>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4">
-        <v>4.1807600000000003</v>
-      </c>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4">
-        <f>AVERAGE(D107,F107,H107,J107,L107,N107)</f>
         <v>5.1165866666666666</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="115">
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="A56:A67"/>
     <mergeCell ref="B56:P56"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="C57:D57"/>
@@ -7959,50 +7975,50 @@
     <mergeCell ref="K57:L57"/>
     <mergeCell ref="M57:N57"/>
     <mergeCell ref="O57:P57"/>
-    <mergeCell ref="B64:P64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="O101:P101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="O75:P75"/>
-    <mergeCell ref="B82:P82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="M83:N83"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="O83:P83"/>
-    <mergeCell ref="A92:A107"/>
-    <mergeCell ref="B92:P92"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="M93:N93"/>
-    <mergeCell ref="O93:P93"/>
-    <mergeCell ref="B100:P100"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A74:A89"/>
-    <mergeCell ref="B74:P74"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="O71:P71"/>
+    <mergeCell ref="B78:P78"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="A88:A103"/>
+    <mergeCell ref="B88:P88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="B96:P96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="A70:A85"/>
+    <mergeCell ref="B70:P70"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
@@ -8032,7 +8048,7 @@
     <mergeCell ref="E47:F47"/>
     <mergeCell ref="G47:H47"/>
     <mergeCell ref="I47:J47"/>
-    <mergeCell ref="R2:T89"/>
+    <mergeCell ref="R2:T85"/>
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:B4"/>
@@ -8049,6 +8065,9 @@
     <mergeCell ref="M47:N47"/>
     <mergeCell ref="O47:P47"/>
     <mergeCell ref="A38:A53"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D47"/>
     <mergeCell ref="B38:P38"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C39:D39"/>
@@ -8058,9 +8077,6 @@
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="O39:P39"/>
-    <mergeCell ref="B46:P46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:D47"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124EE7BD-FF67-4EF7-9123-7612D11DA046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D78DBF-9290-469E-92C0-B0A608F0AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="48">
   <si>
     <t>Data Num.</t>
   </si>
@@ -235,6 +235,11 @@
 Align-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>PRISM
+from HASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +248,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -265,6 +270,13 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Times New Roman"/>
@@ -368,11 +380,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4487,7 +4499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D606126C-3FE1-428A-BDA2-93CD7E4A00CB}">
-  <dimension ref="A2:T103"/>
+  <dimension ref="A2:T157"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -4518,8 +4530,8 @@
       <c r="R2" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
@@ -4554,9 +4566,9 @@
         <v>7</v>
       </c>
       <c r="P3" s="11"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
@@ -4603,9 +4615,9 @@
       <c r="P4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
@@ -4641,9 +4653,9 @@
         <f>AVERAGE(D5,F5,H5,J5,L5,N5)</f>
         <v>4.3627033333333332</v>
       </c>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -4679,9 +4691,9 @@
         <f>AVERAGE(D6,F6,H6,J6,L6,N6)</f>
         <v>4.4955516666666666</v>
       </c>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
@@ -4717,9 +4729,9 @@
         <f>AVERAGE(D7,F7,H7,J7,L7,N7)</f>
         <v>4.6067383333333325</v>
       </c>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
@@ -4755,9 +4767,9 @@
         <f>AVERAGE(D8,F8,H8,J8,L8,N8)</f>
         <v>4.6550816666666668</v>
       </c>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
@@ -4793,9 +4805,9 @@
         <f>AVERAGE(D9,F9,H9,J9,L9,N9)</f>
         <v>4.6418983333333328</v>
       </c>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
@@ -4816,9 +4828,9 @@
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
@@ -4853,9 +4865,9 @@
         <v>7</v>
       </c>
       <c r="P11" s="11"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
@@ -4902,9 +4914,9 @@
       <c r="P12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
@@ -4940,9 +4952,9 @@
         <f>AVERAGE(D13,F13,H13,J13,L13,N13)</f>
         <v>4.105666666666667</v>
       </c>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
@@ -4978,9 +4990,9 @@
         <f>AVERAGE(D14,F14,H14,J14,L14,N14)</f>
         <v>4.2753199999999998</v>
       </c>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
@@ -5016,9 +5028,9 @@
         <f>AVERAGE(D15,F15,H15,J15,L15,N15)</f>
         <v>4.3534666666666668</v>
       </c>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
@@ -5054,9 +5066,9 @@
         <f>AVERAGE(D16,F16,H16,J16,L16,N16)</f>
         <v>4.4003916666666667</v>
       </c>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
     </row>
     <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
@@ -5092,9 +5104,9 @@
         <f>AVERAGE(D17,F17,H17,J17,L17,N17)</f>
         <v>4.3763583333333331</v>
       </c>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
     </row>
     <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
@@ -5111,14 +5123,14 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
     </row>
     <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
     </row>
     <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
@@ -5141,9 +5153,9 @@
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
     </row>
     <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
@@ -5178,9 +5190,9 @@
         <v>7</v>
       </c>
       <c r="P21" s="11"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
     </row>
     <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
@@ -5227,9 +5239,9 @@
       <c r="P22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
     </row>
     <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
@@ -5265,9 +5277,9 @@
         <f>AVERAGE(D23,F23,H23,J23,L23,N23)</f>
         <v>4.7786633333333333</v>
       </c>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
     </row>
     <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
@@ -5303,9 +5315,9 @@
         <f>AVERAGE(D24,F24,H24,J24,L24,N24)</f>
         <v>4.9328433333333326</v>
       </c>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
     </row>
     <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
@@ -5341,9 +5353,9 @@
         <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
         <v>5.0321399999999992</v>
       </c>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
     </row>
     <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
@@ -5379,9 +5391,9 @@
         <f>AVERAGE(D26,F26,H26,J26,L26,N26)</f>
         <v>5.0552866666666665</v>
       </c>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
@@ -5417,9 +5429,9 @@
         <f>AVERAGE(D27,F27,H27,J27,L27,N27)</f>
         <v>5.0574983333333341</v>
       </c>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
@@ -5440,9 +5452,9 @@
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
@@ -5477,9 +5489,9 @@
         <v>7</v>
       </c>
       <c r="P29" s="11"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
     </row>
     <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
@@ -5526,9 +5538,9 @@
       <c r="P30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
     </row>
     <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
@@ -5564,9 +5576,9 @@
         <f>AVERAGE(D31,F31,H31,J31,L31,N31)</f>
         <v>4.4963716666666658</v>
       </c>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
@@ -5602,9 +5614,9 @@
         <f>AVERAGE(D32,F32,H32,J32,L32,N32)</f>
         <v>4.6095549999999994</v>
       </c>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
@@ -5640,9 +5652,9 @@
         <f>AVERAGE(D33,F33,H33,J33,L33,N33)</f>
         <v>4.7083816666666669</v>
       </c>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
@@ -5678,9 +5690,9 @@
         <f>AVERAGE(D34,F34,H34,J34,L34,N34)</f>
         <v>4.7704933333333335</v>
       </c>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
@@ -5716,9 +5728,9 @@
         <f>AVERAGE(D35,F35,H35,J35,L35,N35)</f>
         <v>4.7335233333333333</v>
       </c>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="3"/>
@@ -5735,9 +5747,9 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="3"/>
@@ -5754,13 +5766,13 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>13</v>
@@ -5779,9 +5791,9 @@
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
     </row>
     <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
@@ -5816,9 +5828,9 @@
         <v>7</v>
       </c>
       <c r="P39" s="11"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
@@ -5865,9 +5877,9 @@
       <c r="P40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
@@ -5875,37 +5887,22 @@
         <v>8</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3">
-        <v>4.5689299999999999</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>5.5732100000000004</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3">
-        <v>5.1474900000000003</v>
-      </c>
+      <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3">
-        <v>4.7865599999999997</v>
-      </c>
+      <c r="J41" s="3"/>
       <c r="K41" s="3"/>
-      <c r="L41" s="3">
-        <v>4.1556199999999999</v>
-      </c>
+      <c r="L41" s="3"/>
       <c r="M41" s="3"/>
-      <c r="N41" s="3">
-        <v>3.6334300000000002</v>
-      </c>
+      <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="3">
-        <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
-        <v>4.6442066666666673</v>
-      </c>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
+      <c r="P41" s="3"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
     </row>
     <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
@@ -5913,37 +5910,22 @@
         <v>9</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>4.9636199999999997</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="3">
-        <v>5.8313199999999998</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3">
-        <v>5.6455599999999997</v>
-      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3">
-        <v>5.1763000000000003</v>
-      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="3">
-        <v>4.6677099999999996</v>
-      </c>
+      <c r="L42" s="3"/>
       <c r="M42" s="3"/>
-      <c r="N42" s="3">
-        <v>4.0916800000000002</v>
-      </c>
+      <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="3">
-        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
-        <v>5.0626983333333335</v>
-      </c>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
+      <c r="P42" s="3"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
@@ -5951,37 +5933,22 @@
         <v>10</v>
       </c>
       <c r="C43" s="3"/>
-      <c r="D43" s="3">
-        <v>5.1536600000000004</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="3">
-        <v>6.0681799999999999</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3">
-        <v>5.8374499999999996</v>
-      </c>
+      <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3">
-        <v>5.4357300000000004</v>
-      </c>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
-      <c r="L43" s="3">
-        <v>4.9444400000000002</v>
-      </c>
+      <c r="L43" s="3"/>
       <c r="M43" s="3"/>
-      <c r="N43" s="3">
-        <v>4.3256100000000002</v>
-      </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="3"/>
-      <c r="P43" s="3">
-        <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
-        <v>5.2941783333333339</v>
-      </c>
-      <c r="R43" s="14"/>
-      <c r="S43" s="14"/>
-      <c r="T43" s="14"/>
+      <c r="P43" s="3"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
@@ -6002,9 +5969,9 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
     </row>
     <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
@@ -6025,9 +5992,9 @@
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
-      <c r="R45" s="14"/>
-      <c r="S45" s="14"/>
-      <c r="T45" s="14"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
     </row>
     <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
@@ -6048,9 +6015,9 @@
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
-      <c r="R46" s="14"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
     </row>
     <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
@@ -6085,9 +6052,9 @@
         <v>7</v>
       </c>
       <c r="P47" s="11"/>
-      <c r="R47" s="14"/>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
@@ -6134,9 +6101,9 @@
       <c r="P48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
     </row>
     <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
@@ -6144,37 +6111,22 @@
         <v>8</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3">
-        <v>4.1356999999999999</v>
-      </c>
+      <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="3">
-        <v>5.3262299999999998</v>
-      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="3">
-        <v>4.8702199999999998</v>
-      </c>
+      <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3">
-        <v>4.4009</v>
-      </c>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
-      <c r="L49" s="3">
-        <v>3.8662399999999999</v>
-      </c>
+      <c r="L49" s="3"/>
       <c r="M49" s="3"/>
-      <c r="N49" s="3">
-        <v>3.46048</v>
-      </c>
+      <c r="N49" s="3"/>
       <c r="O49" s="3"/>
-      <c r="P49" s="3">
-        <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
-        <v>4.3432950000000003</v>
-      </c>
-      <c r="R49" s="14"/>
-      <c r="S49" s="14"/>
-      <c r="T49" s="14"/>
+      <c r="P49" s="3"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
     </row>
     <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
@@ -6182,37 +6134,22 @@
         <v>9</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="3">
-        <v>4.47675</v>
-      </c>
+      <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3">
-        <v>5.66073</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3">
-        <v>5.4292499999999997</v>
-      </c>
+      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3">
-        <v>4.84232</v>
-      </c>
+      <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-      <c r="L50" s="3">
-        <v>4.2573600000000003</v>
-      </c>
+      <c r="L50" s="3"/>
       <c r="M50" s="3"/>
-      <c r="N50" s="3">
-        <v>3.7513200000000002</v>
-      </c>
+      <c r="N50" s="3"/>
       <c r="O50" s="3"/>
-      <c r="P50" s="3">
-        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
-        <v>4.7362883333333334</v>
-      </c>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
+      <c r="P50" s="3"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
     </row>
     <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
@@ -6220,37 +6157,22 @@
         <v>10</v>
       </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3">
-        <v>4.6834899999999999</v>
-      </c>
+      <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="3">
-        <v>5.8116199999999996</v>
-      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3">
-        <v>5.6635</v>
-      </c>
+      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3">
-        <v>5.0595999999999997</v>
-      </c>
+      <c r="J51" s="3"/>
       <c r="K51" s="3"/>
-      <c r="L51" s="3">
-        <v>4.5441099999999999</v>
-      </c>
+      <c r="L51" s="3"/>
       <c r="M51" s="3"/>
-      <c r="N51" s="3">
-        <v>4.0245899999999999</v>
-      </c>
+      <c r="N51" s="3"/>
       <c r="O51" s="3"/>
-      <c r="P51" s="3">
-        <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
-        <v>4.9644849999999998</v>
-      </c>
-      <c r="R51" s="14"/>
-      <c r="S51" s="14"/>
-      <c r="T51" s="14"/>
+      <c r="P51" s="3"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
     </row>
     <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
@@ -6271,9 +6193,9 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
-      <c r="T52" s="14"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
     </row>
     <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
@@ -6294,9 +6216,9 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
-      <c r="R53" s="14"/>
-      <c r="S53" s="14"/>
-      <c r="T53" s="14"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
     </row>
     <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="3"/>
@@ -6313,9 +6235,9 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
-      <c r="R54" s="14"/>
-      <c r="S54" s="14"/>
-      <c r="T54" s="14"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
     </row>
     <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="3"/>
@@ -6332,13 +6254,13 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-      <c r="R55" s="14"/>
-      <c r="S55" s="14"/>
-      <c r="T55" s="14"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
     </row>
     <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="s">
-        <v>46</v>
+      <c r="A56" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>13</v>
@@ -6357,9 +6279,9 @@
       <c r="N56" s="10"/>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
-      <c r="R56" s="14"/>
-      <c r="S56" s="14"/>
-      <c r="T56" s="14"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
     </row>
     <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
@@ -6394,9 +6316,9 @@
         <v>7</v>
       </c>
       <c r="P57" s="11"/>
-      <c r="R57" s="14"/>
-      <c r="S57" s="14"/>
-      <c r="T57" s="14"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
     </row>
     <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
@@ -6443,9 +6365,9 @@
       <c r="P58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R58" s="14"/>
-      <c r="S58" s="14"/>
-      <c r="T58" s="14"/>
+      <c r="R58" s="7"/>
+      <c r="S58" s="7"/>
+      <c r="T58" s="7"/>
     </row>
     <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
@@ -6454,963 +6376,1001 @@
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3">
-        <v>4.6461800000000002</v>
+        <v>4.5689299999999999</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3">
-        <v>5.7082499999999996</v>
+        <v>5.5732100000000004</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3">
-        <v>5.4791999999999996</v>
+        <v>5.1474900000000003</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3">
-        <v>4.8402599999999998</v>
+        <v>4.7865599999999997</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3">
-        <v>4.3976300000000004</v>
+        <v>4.1556199999999999</v>
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3">
-        <v>3.82822</v>
+        <v>3.6334300000000002</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3">
         <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
-        <v>4.8166233333333333</v>
-      </c>
-      <c r="R59" s="14"/>
-      <c r="S59" s="14"/>
-      <c r="T59" s="14"/>
+        <v>4.6442066666666673</v>
+      </c>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
     </row>
     <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
-        <v>4.8698699999999997</v>
+        <v>4.9636199999999997</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3">
-        <v>5.9710700000000001</v>
+        <v>5.8313199999999998</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3">
-        <v>5.6823300000000003</v>
+        <v>5.6455599999999997</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="3">
-        <v>5.1452799999999996</v>
+        <v>5.1763000000000003</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3">
-        <v>4.7675299999999998</v>
+        <v>4.6677099999999996</v>
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3">
-        <v>4.1111500000000003</v>
+        <v>4.0916800000000002</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3">
         <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
-        <v>5.0912049999999995</v>
-      </c>
-      <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-      <c r="T60" s="14"/>
+        <v>5.0626983333333335</v>
+      </c>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
     </row>
     <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
-      <c r="B61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4">
-        <v>4.9489000000000001</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4">
-        <v>6.0358900000000002</v>
-      </c>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4">
-        <v>5.8227900000000004</v>
-      </c>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4">
-        <v>5.1799600000000003</v>
-      </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4">
-        <v>4.76105</v>
-      </c>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4">
-        <v>4.1094099999999996</v>
-      </c>
-      <c r="O61" s="4"/>
+      <c r="B61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3">
+        <v>5.1536600000000004</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3">
+        <v>6.0681799999999999</v>
+      </c>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3">
+        <v>5.8374499999999996</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3">
+        <v>5.4357300000000004</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3">
+        <v>4.9444400000000002</v>
+      </c>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3">
+        <v>4.3256100000000002</v>
+      </c>
+      <c r="O61" s="3"/>
       <c r="P61" s="3">
         <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
-        <v>5.1430000000000007</v>
-      </c>
-      <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
+        <v>5.2941783333333339</v>
+      </c>
+      <c r="R61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
-      <c r="B62" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
+      <c r="B62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3">
+        <v>5.2013699999999998</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <v>6.0914299999999999</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3">
+        <v>5.9162600000000003</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3">
+        <v>5.4433999999999996</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3">
+        <v>4.88727</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3">
+        <v>4.2856500000000004</v>
+      </c>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3">
+        <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
+        <v>5.3042300000000004</v>
+      </c>
+      <c r="R62" s="7"/>
+      <c r="S62" s="7"/>
+      <c r="T62" s="7"/>
     </row>
     <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
-      <c r="B63" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P63" s="11"/>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="14"/>
+      <c r="B63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4">
+        <v>5.2447999999999997</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4">
+        <v>6.1273299999999997</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4">
+        <v>5.9121600000000001</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4">
+        <v>5.4331800000000001</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4">
+        <v>5.1311099999999996</v>
+      </c>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4">
+        <v>4.3350200000000001</v>
+      </c>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4">
+        <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
+        <v>5.3639333333333328</v>
+      </c>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
     </row>
     <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R64" s="14"/>
-      <c r="S64" s="14"/>
-      <c r="T64" s="14"/>
+      <c r="B64" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+      <c r="R64" s="7"/>
+      <c r="S64" s="7"/>
+      <c r="T64" s="7"/>
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
-      <c r="B65" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3">
-        <v>4.2968700000000002</v>
-      </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3">
-        <v>5.4696899999999999</v>
-      </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3">
-        <v>5.2728200000000003</v>
-      </c>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3">
-        <v>4.5333500000000004</v>
-      </c>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
-        <v>4.0951500000000003</v>
-      </c>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3">
-        <v>3.5975899999999998</v>
-      </c>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3">
-        <f>AVERAGE(D65,F65,H65,J65,L65,N65)</f>
-        <v>4.5442450000000001</v>
-      </c>
-      <c r="R65" s="14"/>
-      <c r="S65" s="14"/>
-      <c r="T65" s="14"/>
+      <c r="B65" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P65" s="11"/>
+      <c r="R65" s="7"/>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
-      <c r="B66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3">
-        <v>4.4737999999999998</v>
-      </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3">
-        <v>5.60236</v>
-      </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3">
-        <v>5.5017800000000001</v>
-      </c>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3">
-        <v>4.8213200000000001</v>
-      </c>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3">
-        <v>4.4157700000000002</v>
-      </c>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3">
-        <v>3.8286199999999999</v>
-      </c>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3">
-        <f>AVERAGE(D66,F66,H66,J66,L66,N66)</f>
-        <v>4.7739416666666665</v>
-      </c>
-      <c r="R66" s="14"/>
-      <c r="S66" s="14"/>
-      <c r="T66" s="14"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R66" s="7"/>
+      <c r="S66" s="7"/>
+      <c r="T66" s="7"/>
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
-      <c r="B67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4">
-        <v>4.5378999999999996</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4">
-        <v>5.7141900000000003</v>
-      </c>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4">
-        <v>5.5835900000000001</v>
-      </c>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4">
-        <v>4.79148</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4">
-        <v>4.3329700000000004</v>
-      </c>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4">
-        <v>3.7964500000000001</v>
-      </c>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4">
+      <c r="B67" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3">
+        <v>4.1356999999999999</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3">
+        <v>5.3262299999999998</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3">
+        <v>4.8702199999999998</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3">
+        <v>4.4009</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3">
+        <v>3.8662399999999999</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3">
+        <v>3.46048</v>
+      </c>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3">
         <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
-        <v>4.7927633333333333</v>
-      </c>
-      <c r="R67" s="14"/>
-      <c r="S67" s="14"/>
-      <c r="T67" s="14"/>
+        <v>4.3432950000000003</v>
+      </c>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9"/>
+      <c r="B68" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>4.47675</v>
+      </c>
       <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3">
+        <v>5.66073</v>
+      </c>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="H68" s="3">
+        <v>5.4292499999999997</v>
+      </c>
       <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
+      <c r="J68" s="3">
+        <v>4.84232</v>
+      </c>
       <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="L68" s="3">
+        <v>4.2573600000000003</v>
+      </c>
       <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
+      <c r="N68" s="3">
+        <v>3.7513200000000002</v>
+      </c>
       <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="R68" s="14"/>
-      <c r="S68" s="14"/>
-      <c r="T68" s="14"/>
+      <c r="P68" s="3">
+        <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
+        <v>4.7362883333333334</v>
+      </c>
+      <c r="R68" s="7"/>
+      <c r="S68" s="7"/>
+      <c r="T68" s="7"/>
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R69" s="14"/>
-      <c r="S69" s="14"/>
-      <c r="T69" s="14"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3">
+        <v>4.6834899999999999</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3">
+        <v>5.8116199999999996</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3">
+        <v>5.6635</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3">
+        <v>5.0595999999999997</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3">
+        <v>4.5441099999999999</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3">
+        <v>4.0245899999999999</v>
+      </c>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3">
+        <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
+        <v>4.9644849999999998</v>
+      </c>
+      <c r="R69" s="7"/>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="R70" s="14"/>
-      <c r="S70" s="14"/>
-      <c r="T70" s="14"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3">
+        <v>4.76328</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3">
+        <v>5.8237800000000002</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3">
+        <v>5.6883499999999998</v>
+      </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3">
+        <v>5.0670299999999999</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3">
+        <v>4.43344</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3">
+        <v>4.1517099999999996</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3">
+        <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
+        <v>4.9879316666666673</v>
+      </c>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
-      <c r="B71" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P71" s="11"/>
-      <c r="R71" s="14"/>
-      <c r="S71" s="14"/>
-      <c r="T71" s="14"/>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4">
+        <v>4.8011799999999996</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4">
+        <v>5.8531700000000004</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4">
+        <v>5.7463300000000004</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4">
+        <v>5.0921599999999998</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4">
+        <v>4.6106199999999999</v>
+      </c>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4">
+        <v>4.0481800000000003</v>
+      </c>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4">
+        <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
+        <v>5.0252733333333337</v>
+      </c>
+      <c r="R71" s="7"/>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R72" s="14"/>
-      <c r="S72" s="14"/>
-      <c r="T72" s="14"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="R72" s="7"/>
+      <c r="S72" s="7"/>
+      <c r="T72" s="7"/>
     </row>
     <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9"/>
-      <c r="B73" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C73" s="3"/>
-      <c r="D73" s="3">
-        <v>4.8613999999999997</v>
-      </c>
+      <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3">
-        <v>5.88361</v>
-      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3"/>
-      <c r="H73" s="3">
-        <v>5.5696399999999997</v>
-      </c>
+      <c r="H73" s="3"/>
       <c r="I73" s="3"/>
-      <c r="J73" s="3">
-        <v>5.0985699999999996</v>
-      </c>
+      <c r="J73" s="3"/>
       <c r="K73" s="3"/>
-      <c r="L73" s="3">
-        <v>4.5044000000000004</v>
-      </c>
+      <c r="L73" s="3"/>
       <c r="M73" s="3"/>
-      <c r="N73" s="3">
-        <v>4.0416400000000001</v>
-      </c>
+      <c r="N73" s="3"/>
       <c r="O73" s="3"/>
-      <c r="P73" s="3">
-        <f>AVERAGE(D73,F73,H73,J73,L73,N73)</f>
-        <v>4.9932100000000004</v>
-      </c>
-      <c r="R73" s="14"/>
-      <c r="S73" s="14"/>
-      <c r="T73" s="14"/>
+      <c r="P73" s="3"/>
+      <c r="R73" s="7"/>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
     </row>
     <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9"/>
-      <c r="B74" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3">
-        <v>5.0363800000000003</v>
-      </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3">
-        <v>6.0898700000000003</v>
-      </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3">
-        <v>5.7049899999999996</v>
-      </c>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3">
-        <v>5.3215500000000002</v>
-      </c>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3">
-        <v>4.7849199999999996</v>
-      </c>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3">
-        <v>4.2842399999999996</v>
-      </c>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3">
-        <f>AVERAGE(D74,F74,H74,J74,L74,N74)</f>
-        <v>5.2036583333333342</v>
-      </c>
-      <c r="R74" s="14"/>
-      <c r="S74" s="14"/>
-      <c r="T74" s="14"/>
+      <c r="A74" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="R74" s="7"/>
+      <c r="S74" s="7"/>
+      <c r="T74" s="7"/>
     </row>
     <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
-      <c r="B75" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3">
-        <v>5.1776600000000004</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3">
-        <v>6.1842800000000002</v>
-      </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3">
-        <v>5.8865100000000004</v>
-      </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3">
-        <v>5.48346</v>
-      </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3">
-        <v>4.9375</v>
-      </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3">
-        <v>4.3942699999999997</v>
-      </c>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3">
-        <f>AVERAGE(D75,F75,H75,J75,L75,N75)</f>
-        <v>5.3439466666666675</v>
-      </c>
-      <c r="R75" s="14"/>
-      <c r="S75" s="14"/>
-      <c r="T75" s="14"/>
+      <c r="B75" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="11"/>
+      <c r="R75" s="7"/>
+      <c r="S75" s="7"/>
+      <c r="T75" s="7"/>
     </row>
     <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
-      <c r="B76" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3">
-        <v>5.2876300000000001</v>
-      </c>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3">
-        <v>6.2506199999999996</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3">
-        <v>5.9457700000000004</v>
-      </c>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3">
-        <v>5.5481100000000003</v>
-      </c>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3">
-        <v>5.0165199999999999</v>
-      </c>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3">
-        <v>4.5465</v>
-      </c>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3">
-        <f>AVERAGE(D76,F76,H76,J76,L76,N76)</f>
-        <v>5.4325250000000009</v>
-      </c>
-      <c r="R76" s="14"/>
-      <c r="S76" s="14"/>
-      <c r="T76" s="14"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R76" s="7"/>
+      <c r="S76" s="7"/>
+      <c r="T76" s="7"/>
     </row>
     <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
-      <c r="B77" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4">
-        <v>5.2888599999999997</v>
-      </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4">
-        <v>6.2779600000000002</v>
-      </c>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4">
-        <v>6.0451699999999997</v>
-      </c>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4">
-        <v>5.5814599999999999</v>
-      </c>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4">
-        <v>5.0148900000000003</v>
-      </c>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4">
-        <v>4.53064</v>
-      </c>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4">
+      <c r="B77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>4.6461800000000002</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3">
+        <v>5.7082499999999996</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3">
+        <v>5.4791999999999996</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3">
+        <v>4.8402599999999998</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>4.3976300000000004</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>3.82822</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3">
         <f>AVERAGE(D77,F77,H77,J77,L77,N77)</f>
-        <v>5.4564966666666663</v>
-      </c>
-      <c r="R77" s="14"/>
-      <c r="S77" s="14"/>
-      <c r="T77" s="14"/>
+        <v>4.8166233333333333</v>
+      </c>
+      <c r="R77" s="7"/>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
     </row>
     <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
-      <c r="B78" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="10"/>
-      <c r="O78" s="10"/>
-      <c r="P78" s="10"/>
-      <c r="R78" s="14"/>
-      <c r="S78" s="14"/>
-      <c r="T78" s="14"/>
+      <c r="B78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>4.8698699999999997</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <v>5.9710700000000001</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
+        <v>5.6823300000000003</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3">
+        <v>5.1452799999999996</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>4.7675299999999998</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3">
+        <v>4.1111500000000003</v>
+      </c>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3">
+        <f>AVERAGE(D78,F78,H78,J78,L78,N78)</f>
+        <v>5.0912049999999995</v>
+      </c>
+      <c r="R78" s="7"/>
+      <c r="S78" s="7"/>
+      <c r="T78" s="7"/>
     </row>
     <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
-      <c r="B79" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="N79" s="11"/>
-      <c r="O79" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P79" s="11"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14"/>
-      <c r="T79" s="14"/>
+      <c r="B79" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4">
+        <v>4.9489000000000001</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4">
+        <v>6.0358900000000002</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4">
+        <v>5.8227900000000004</v>
+      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4">
+        <v>5.1799600000000003</v>
+      </c>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4">
+        <v>4.76105</v>
+      </c>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4">
+        <v>4.1094099999999996</v>
+      </c>
+      <c r="O79" s="4"/>
+      <c r="P79" s="3">
+        <f>AVERAGE(D79,F79,H79,J79,L79,N79)</f>
+        <v>5.1430000000000007</v>
+      </c>
+      <c r="R79" s="7"/>
+      <c r="S79" s="7"/>
+      <c r="T79" s="7"/>
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R80" s="14"/>
-      <c r="S80" s="14"/>
-      <c r="T80" s="14"/>
+      <c r="B80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="10"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="10"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="10"/>
+      <c r="P80" s="10"/>
+      <c r="R80" s="7"/>
+      <c r="S80" s="7"/>
+      <c r="T80" s="7"/>
     </row>
     <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
-      <c r="B81" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3">
-        <v>4.39011</v>
-      </c>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3">
-        <v>5.6082400000000003</v>
-      </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3">
-        <v>5.3261500000000002</v>
-      </c>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3">
-        <v>4.6698899999999997</v>
-      </c>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3">
-        <v>4.1432399999999996</v>
-      </c>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3">
-        <v>3.7595499999999999</v>
-      </c>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3">
-        <f>AVERAGE(D81,F81,H81,J81,L81,N81)</f>
-        <v>4.6495299999999995</v>
-      </c>
-      <c r="R81" s="14"/>
-      <c r="S81" s="14"/>
-      <c r="T81" s="14"/>
+      <c r="B81" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="11"/>
+      <c r="M81" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N81" s="11"/>
+      <c r="O81" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P81" s="11"/>
+      <c r="R81" s="7"/>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
     </row>
     <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
-      <c r="B82" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3">
-        <v>4.5535100000000002</v>
-      </c>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3">
-        <v>5.7491000000000003</v>
-      </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3">
-        <v>5.4894600000000002</v>
-      </c>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3">
-        <v>4.9547800000000004</v>
-      </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3">
-        <v>4.3115500000000004</v>
-      </c>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3">
-        <v>4.0073100000000004</v>
-      </c>
-      <c r="O82" s="3"/>
-      <c r="P82" s="3">
-        <f>AVERAGE(D82,F82,H82,J82,L82,N82)</f>
-        <v>4.8442850000000002</v>
-      </c>
-      <c r="R82" s="14"/>
-      <c r="S82" s="14"/>
-      <c r="T82" s="14"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R82" s="7"/>
+      <c r="S82" s="7"/>
+      <c r="T82" s="7"/>
     </row>
     <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3">
-        <v>4.7401799999999996</v>
+        <v>4.2968700000000002</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3">
-        <v>5.87758</v>
+        <v>5.4696899999999999</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="3">
-        <v>5.6888500000000004</v>
+        <v>5.2728200000000003</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="3">
-        <v>5.1455900000000003</v>
+        <v>4.5333500000000004</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="3">
-        <v>4.44956</v>
+        <v>4.0951500000000003</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3">
-        <v>4.04033</v>
+        <v>3.5975899999999998</v>
       </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3">
         <f>AVERAGE(D83,F83,H83,J83,L83,N83)</f>
-        <v>4.9903483333333325</v>
-      </c>
-      <c r="R83" s="14"/>
-      <c r="S83" s="14"/>
-      <c r="T83" s="14"/>
+        <v>4.5442450000000001</v>
+      </c>
+      <c r="R83" s="7"/>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3">
-        <v>4.8115199999999998</v>
+        <v>4.4737999999999998</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3">
-        <v>5.9385199999999996</v>
+        <v>5.60236</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="3">
-        <v>5.6940099999999996</v>
+        <v>5.5017800000000001</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="3">
-        <v>5.04535</v>
+        <v>4.8213200000000001</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="3">
-        <v>4.57951</v>
+        <v>4.4157700000000002</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3">
-        <v>4.1412100000000001</v>
+        <v>3.8286199999999999</v>
       </c>
       <c r="O84" s="3"/>
       <c r="P84" s="3">
         <f>AVERAGE(D84,F84,H84,J84,L84,N84)</f>
-        <v>5.0350199999999994</v>
-      </c>
-      <c r="R84" s="14"/>
-      <c r="S84" s="14"/>
-      <c r="T84" s="14"/>
+        <v>4.7739416666666665</v>
+      </c>
+      <c r="R84" s="7"/>
+      <c r="S84" s="7"/>
+      <c r="T84" s="7"/>
     </row>
     <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4">
-        <v>4.7477600000000004</v>
+        <v>4.5378999999999996</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4">
-        <v>6.0426799999999998</v>
+        <v>5.7141900000000003</v>
       </c>
       <c r="G85" s="4"/>
       <c r="H85" s="4">
-        <v>5.7625099999999998</v>
+        <v>5.5835900000000001</v>
       </c>
       <c r="I85" s="4"/>
       <c r="J85" s="4">
-        <v>5.2044899999999998</v>
+        <v>4.79148</v>
       </c>
       <c r="K85" s="4"/>
       <c r="L85" s="4">
-        <v>4.6174200000000001</v>
+        <v>4.3329700000000004</v>
       </c>
       <c r="M85" s="4"/>
       <c r="N85" s="4">
-        <v>4.1296299999999997</v>
+        <v>3.7964500000000001</v>
       </c>
       <c r="O85" s="4"/>
       <c r="P85" s="4">
         <f>AVERAGE(D85,F85,H85,J85,L85,N85)</f>
-        <v>5.0840816666666662</v>
-      </c>
-      <c r="R85" s="14"/>
-      <c r="S85" s="14"/>
-      <c r="T85" s="14"/>
+        <v>4.7927633333333333</v>
+      </c>
+      <c r="R85" s="7"/>
+      <c r="S85" s="7"/>
+      <c r="T85" s="7"/>
+    </row>
+    <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="R86" s="7"/>
+      <c r="S86" s="7"/>
+      <c r="T86" s="7"/>
+    </row>
+    <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R87" s="7"/>
+      <c r="S87" s="7"/>
+      <c r="T87" s="7"/>
     </row>
     <row r="88" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>13</v>
@@ -7429,6 +7389,9 @@
       <c r="N88" s="10"/>
       <c r="O88" s="10"/>
       <c r="P88" s="10"/>
+      <c r="R88" s="7"/>
+      <c r="S88" s="7"/>
+      <c r="T88" s="7"/>
     </row>
     <row r="89" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
@@ -7463,6 +7426,9 @@
         <v>7</v>
       </c>
       <c r="P89" s="11"/>
+      <c r="R89" s="7"/>
+      <c r="S89" s="7"/>
+      <c r="T89" s="7"/>
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9"/>
@@ -7509,181 +7475,199 @@
       <c r="P90" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R90" s="7"/>
+      <c r="S90" s="7"/>
+      <c r="T90" s="7"/>
     </row>
     <row r="91" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9"/>
       <c r="B91" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3">
-        <v>4.8350999999999997</v>
+        <v>4.8613999999999997</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3">
-        <v>5.8418599999999996</v>
+        <v>5.88361</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3">
-        <v>5.3804100000000004</v>
+        <v>5.5696399999999997</v>
       </c>
       <c r="I91" s="3"/>
       <c r="J91" s="3">
-        <v>5.1307099999999997</v>
+        <v>5.0985699999999996</v>
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="3">
-        <v>4.2869599999999997</v>
+        <v>4.5044000000000004</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3">
-        <v>3.9249200000000002</v>
+        <v>4.0416400000000001</v>
       </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3">
         <f>AVERAGE(D91,F91,H91,J91,L91,N91)</f>
-        <v>4.8999933333333336</v>
-      </c>
+        <v>4.9932100000000004</v>
+      </c>
+      <c r="R91" s="7"/>
+      <c r="S91" s="7"/>
+      <c r="T91" s="7"/>
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9"/>
       <c r="B92" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3">
-        <v>5.0928699999999996</v>
+        <v>5.0363800000000003</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3">
-        <v>5.9963899999999999</v>
+        <v>6.0898700000000003</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3">
-        <v>5.7409499999999998</v>
+        <v>5.7049899999999996</v>
       </c>
       <c r="I92" s="3"/>
       <c r="J92" s="3">
-        <v>5.3913000000000002</v>
+        <v>5.3215500000000002</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="3">
-        <v>4.4194800000000001</v>
+        <v>4.7849199999999996</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3">
-        <v>4.1529199999999999</v>
+        <v>4.2842399999999996</v>
       </c>
       <c r="O92" s="3"/>
       <c r="P92" s="3">
         <f>AVERAGE(D92,F92,H92,J92,L92,N92)</f>
-        <v>5.132318333333334</v>
-      </c>
+        <v>5.2036583333333342</v>
+      </c>
+      <c r="R92" s="7"/>
+      <c r="S92" s="7"/>
+      <c r="T92" s="7"/>
     </row>
     <row r="93" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9"/>
       <c r="B93" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3">
-        <v>5.3201000000000001</v>
+        <v>5.1776600000000004</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3">
-        <v>6.1637899999999997</v>
+        <v>6.1842800000000002</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3">
-        <v>5.9080199999999996</v>
+        <v>5.8865100000000004</v>
       </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3">
-        <v>5.5360100000000001</v>
+        <v>5.48346</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="3">
-        <v>4.71347</v>
+        <v>4.9375</v>
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3">
-        <v>4.3147200000000003</v>
+        <v>4.3942699999999997</v>
       </c>
       <c r="O93" s="3"/>
       <c r="P93" s="3">
         <f>AVERAGE(D93,F93,H93,J93,L93,N93)</f>
-        <v>5.3260183333333337</v>
-      </c>
+        <v>5.3439466666666675</v>
+      </c>
+      <c r="R93" s="7"/>
+      <c r="S93" s="7"/>
+      <c r="T93" s="7"/>
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9"/>
       <c r="B94" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3">
-        <v>5.36137</v>
+        <v>5.2876300000000001</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3">
-        <v>6.2123900000000001</v>
+        <v>6.2506199999999996</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3">
-        <v>6.0613599999999996</v>
+        <v>5.9457700000000004</v>
       </c>
       <c r="I94" s="3"/>
       <c r="J94" s="3">
-        <v>5.5939699999999997</v>
+        <v>5.5481100000000003</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="3">
-        <v>4.8575299999999997</v>
+        <v>5.0165199999999999</v>
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3">
-        <v>4.4312899999999997</v>
+        <v>4.5465</v>
       </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3">
         <f>AVERAGE(D94,F94,H94,J94,L94,N94)</f>
-        <v>5.4196516666666668</v>
-      </c>
+        <v>5.4325250000000009</v>
+      </c>
+      <c r="R94" s="7"/>
+      <c r="S94" s="7"/>
+      <c r="T94" s="7"/>
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9"/>
       <c r="B95" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4">
-        <v>5.4131900000000002</v>
+        <v>5.2888599999999997</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4">
-        <v>6.2545000000000002</v>
+        <v>6.2779600000000002</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4">
-        <v>6.0812799999999996</v>
+        <v>6.0451699999999997</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4">
-        <v>5.6418999999999997</v>
+        <v>5.5814599999999999</v>
       </c>
       <c r="K95" s="4"/>
       <c r="L95" s="4">
-        <v>4.8334400000000004</v>
+        <v>5.0148900000000003</v>
       </c>
       <c r="M95" s="4"/>
       <c r="N95" s="4">
-        <v>4.4951999999999996</v>
+        <v>4.53064</v>
       </c>
       <c r="O95" s="4"/>
       <c r="P95" s="4">
         <f>AVERAGE(D95,F95,H95,J95,L95,N95)</f>
-        <v>5.4532516666666666</v>
-      </c>
+        <v>5.4564966666666663</v>
+      </c>
+      <c r="R95" s="7"/>
+      <c r="S95" s="7"/>
+      <c r="T95" s="7"/>
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9"/>
@@ -7704,8 +7688,11 @@
       <c r="N96" s="10"/>
       <c r="O96" s="10"/>
       <c r="P96" s="10"/>
-    </row>
-    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R96" s="7"/>
+      <c r="S96" s="7"/>
+      <c r="T96" s="7"/>
+    </row>
+    <row r="97" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9"/>
       <c r="B97" s="11" t="s">
         <v>0</v>
@@ -7738,8 +7725,11 @@
         <v>7</v>
       </c>
       <c r="P97" s="11"/>
-    </row>
-    <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R97" s="7"/>
+      <c r="S97" s="7"/>
+      <c r="T97" s="7"/>
+    </row>
+    <row r="98" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9"/>
       <c r="B98" s="12"/>
       <c r="C98" s="2" t="s">
@@ -7784,248 +7774,2059 @@
       <c r="P98" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R98" s="7"/>
+      <c r="S98" s="7"/>
+      <c r="T98" s="7"/>
+    </row>
+    <row r="99" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9"/>
       <c r="B99" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3">
-        <v>4.4249700000000001</v>
+        <v>4.39011</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3">
-        <v>5.5333399999999999</v>
+        <v>5.6082400000000003</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="3">
-        <v>5.1902999999999997</v>
+        <v>5.3261500000000002</v>
       </c>
       <c r="I99" s="3"/>
       <c r="J99" s="3">
-        <v>4.8660300000000003</v>
+        <v>4.6698899999999997</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3">
-        <v>3.8866299999999998</v>
+        <v>4.1432399999999996</v>
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="3">
-        <v>3.6355400000000002</v>
+        <v>3.7595499999999999</v>
       </c>
       <c r="O99" s="3"/>
       <c r="P99" s="3">
         <f>AVERAGE(D99,F99,H99,J99,L99,N99)</f>
-        <v>4.5894683333333335</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.6495299999999995</v>
+      </c>
+      <c r="R99" s="7"/>
+      <c r="S99" s="7"/>
+      <c r="T99" s="7"/>
+    </row>
+    <row r="100" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9"/>
       <c r="B100" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3">
-        <v>4.66181</v>
+        <v>4.5535100000000002</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3">
-        <v>5.6358699999999997</v>
+        <v>5.7491000000000003</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3">
-        <v>5.5303500000000003</v>
+        <v>5.4894600000000002</v>
       </c>
       <c r="I100" s="3"/>
       <c r="J100" s="3">
-        <v>4.9067100000000003</v>
+        <v>4.9547800000000004</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="3">
-        <v>4.1264799999999999</v>
+        <v>4.3115500000000004</v>
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="3">
-        <v>3.8291499999999998</v>
+        <v>4.0073100000000004</v>
       </c>
       <c r="O100" s="3"/>
       <c r="P100" s="3">
         <f>AVERAGE(D100,F100,H100,J100,L100,N100)</f>
-        <v>4.7817283333333336</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.8442850000000002</v>
+      </c>
+      <c r="R100" s="7"/>
+      <c r="S100" s="7"/>
+      <c r="T100" s="7"/>
+    </row>
+    <row r="101" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9"/>
       <c r="B101" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3">
-        <v>4.8665000000000003</v>
+        <v>4.7401799999999996</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3">
-        <v>5.8399900000000002</v>
+        <v>5.87758</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3">
-        <v>5.65158</v>
+        <v>5.6888500000000004</v>
       </c>
       <c r="I101" s="3"/>
       <c r="J101" s="3">
-        <v>5.07212</v>
+        <v>5.1455900000000003</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="3">
-        <v>4.3304900000000002</v>
+        <v>4.44956</v>
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="3">
-        <v>3.9704700000000002</v>
+        <v>4.04033</v>
       </c>
       <c r="O101" s="3"/>
       <c r="P101" s="3">
         <f>AVERAGE(D101,F101,H101,J101,L101,N101)</f>
-        <v>4.9551916666666669</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.9903483333333325</v>
+      </c>
+      <c r="R101" s="7"/>
+      <c r="S101" s="7"/>
+      <c r="T101" s="7"/>
+    </row>
+    <row r="102" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9"/>
       <c r="B102" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3">
-        <v>4.9245000000000001</v>
+        <v>4.8115199999999998</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3">
-        <v>5.9912099999999997</v>
+        <v>5.9385199999999996</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3">
-        <v>5.8172800000000002</v>
+        <v>5.6940099999999996</v>
       </c>
       <c r="I102" s="3"/>
       <c r="J102" s="3">
-        <v>5.1707700000000001</v>
+        <v>5.04535</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="3">
-        <v>4.4135600000000004</v>
+        <v>4.57951</v>
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="3">
-        <v>4.1507300000000003</v>
+        <v>4.1412100000000001</v>
       </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3">
         <f>AVERAGE(D102,F102,H102,J102,L102,N102)</f>
-        <v>5.0780083333333339</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.0350199999999994</v>
+      </c>
+      <c r="R102" s="7"/>
+      <c r="S102" s="7"/>
+      <c r="T102" s="7"/>
+    </row>
+    <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9"/>
       <c r="B103" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4">
-        <v>4.8952299999999997</v>
+        <v>4.7477600000000004</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4">
-        <v>6.0022099999999998</v>
+        <v>6.0426799999999998</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4">
-        <v>5.8484299999999996</v>
+        <v>5.7625099999999998</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="4">
-        <v>5.3302800000000001</v>
+        <v>5.2044899999999998</v>
       </c>
       <c r="K103" s="4"/>
       <c r="L103" s="4">
-        <v>4.4426100000000002</v>
+        <v>4.6174200000000001</v>
       </c>
       <c r="M103" s="4"/>
       <c r="N103" s="4">
-        <v>4.1807600000000003</v>
+        <v>4.1296299999999997</v>
       </c>
       <c r="O103" s="4"/>
       <c r="P103" s="4">
         <f>AVERAGE(D103,F103,H103,J103,L103,N103)</f>
+        <v>5.0840816666666662</v>
+      </c>
+      <c r="R103" s="7"/>
+      <c r="S103" s="7"/>
+      <c r="T103" s="7"/>
+    </row>
+    <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R104" s="7"/>
+      <c r="S104" s="7"/>
+      <c r="T104" s="7"/>
+    </row>
+    <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R105" s="7"/>
+      <c r="S105" s="7"/>
+      <c r="T105" s="7"/>
+    </row>
+    <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="10"/>
+      <c r="H106" s="10"/>
+      <c r="I106" s="10"/>
+      <c r="J106" s="10"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
+      <c r="R106" s="7"/>
+      <c r="S106" s="7"/>
+      <c r="T106" s="7"/>
+    </row>
+    <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="9"/>
+      <c r="B107" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J107" s="11"/>
+      <c r="K107" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L107" s="11"/>
+      <c r="M107" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N107" s="11"/>
+      <c r="O107" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P107" s="11"/>
+      <c r="R107" s="7"/>
+      <c r="S107" s="7"/>
+      <c r="T107" s="7"/>
+    </row>
+    <row r="108" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="9"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R108" s="7"/>
+      <c r="S108" s="7"/>
+      <c r="T108" s="7"/>
+    </row>
+    <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="9"/>
+      <c r="B109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3">
+        <v>4.8350999999999997</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3">
+        <v>5.8418599999999996</v>
+      </c>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3">
+        <v>5.3804100000000004</v>
+      </c>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3">
+        <v>5.1307099999999997</v>
+      </c>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3">
+        <v>4.2869599999999997</v>
+      </c>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3">
+        <v>3.9249200000000002</v>
+      </c>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3">
+        <f>AVERAGE(D109,F109,H109,J109,L109,N109)</f>
+        <v>4.8999933333333336</v>
+      </c>
+      <c r="R109" s="7"/>
+      <c r="S109" s="7"/>
+      <c r="T109" s="7"/>
+    </row>
+    <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="9"/>
+      <c r="B110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3">
+        <v>5.0928699999999996</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3">
+        <v>5.9963899999999999</v>
+      </c>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3">
+        <v>5.7409499999999998</v>
+      </c>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3">
+        <v>5.3913000000000002</v>
+      </c>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3">
+        <v>4.4194800000000001</v>
+      </c>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3">
+        <v>4.1529199999999999</v>
+      </c>
+      <c r="O110" s="3"/>
+      <c r="P110" s="3">
+        <f>AVERAGE(D110,F110,H110,J110,L110,N110)</f>
+        <v>5.132318333333334</v>
+      </c>
+      <c r="R110" s="7"/>
+      <c r="S110" s="7"/>
+      <c r="T110" s="7"/>
+    </row>
+    <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="9"/>
+      <c r="B111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3">
+        <v>5.3201000000000001</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3">
+        <v>6.1637899999999997</v>
+      </c>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3">
+        <v>5.9080199999999996</v>
+      </c>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3">
+        <v>5.5360100000000001</v>
+      </c>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3">
+        <v>4.71347</v>
+      </c>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3">
+        <v>4.3147200000000003</v>
+      </c>
+      <c r="O111" s="3"/>
+      <c r="P111" s="3">
+        <f>AVERAGE(D111,F111,H111,J111,L111,N111)</f>
+        <v>5.3260183333333337</v>
+      </c>
+      <c r="R111" s="7"/>
+      <c r="S111" s="7"/>
+      <c r="T111" s="7"/>
+    </row>
+    <row r="112" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="9"/>
+      <c r="B112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3">
+        <v>5.36137</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3">
+        <v>6.2123900000000001</v>
+      </c>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3">
+        <v>6.0613599999999996</v>
+      </c>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3">
+        <v>5.5939699999999997</v>
+      </c>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3">
+        <v>4.8575299999999997</v>
+      </c>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3">
+        <v>4.4312899999999997</v>
+      </c>
+      <c r="O112" s="3"/>
+      <c r="P112" s="3">
+        <f>AVERAGE(D112,F112,H112,J112,L112,N112)</f>
+        <v>5.4196516666666668</v>
+      </c>
+      <c r="R112" s="7"/>
+      <c r="S112" s="7"/>
+      <c r="T112" s="7"/>
+    </row>
+    <row r="113" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="9"/>
+      <c r="B113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4">
+        <v>5.4131900000000002</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4">
+        <v>6.2545000000000002</v>
+      </c>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4">
+        <v>6.0812799999999996</v>
+      </c>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4">
+        <v>5.6418999999999997</v>
+      </c>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4">
+        <v>4.8334400000000004</v>
+      </c>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4">
+        <v>4.4951999999999996</v>
+      </c>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4">
+        <f>AVERAGE(D113,F113,H113,J113,L113,N113)</f>
+        <v>5.4532516666666666</v>
+      </c>
+      <c r="R113" s="7"/>
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+    </row>
+    <row r="114" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="9"/>
+      <c r="B114" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" s="10"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
+      <c r="G114" s="10"/>
+      <c r="H114" s="10"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="10"/>
+      <c r="N114" s="10"/>
+      <c r="O114" s="10"/>
+      <c r="P114" s="10"/>
+      <c r="R114" s="7"/>
+      <c r="S114" s="7"/>
+      <c r="T114" s="7"/>
+    </row>
+    <row r="115" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="9"/>
+      <c r="B115" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" s="11"/>
+      <c r="G115" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J115" s="11"/>
+      <c r="K115" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L115" s="11"/>
+      <c r="M115" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N115" s="11"/>
+      <c r="O115" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P115" s="11"/>
+      <c r="R115" s="7"/>
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+    </row>
+    <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="9"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R116" s="7"/>
+      <c r="S116" s="7"/>
+      <c r="T116" s="7"/>
+    </row>
+    <row r="117" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="9"/>
+      <c r="B117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3">
+        <v>4.4249700000000001</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3">
+        <v>5.5333399999999999</v>
+      </c>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3">
+        <v>5.1902999999999997</v>
+      </c>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3">
+        <v>4.8660300000000003</v>
+      </c>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3">
+        <v>3.8866299999999998</v>
+      </c>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3">
+        <v>3.6355400000000002</v>
+      </c>
+      <c r="O117" s="3"/>
+      <c r="P117" s="3">
+        <f>AVERAGE(D117,F117,H117,J117,L117,N117)</f>
+        <v>4.5894683333333335</v>
+      </c>
+      <c r="R117" s="7"/>
+      <c r="S117" s="7"/>
+      <c r="T117" s="7"/>
+    </row>
+    <row r="118" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="9"/>
+      <c r="B118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3">
+        <v>4.66181</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3">
+        <v>5.6358699999999997</v>
+      </c>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3">
+        <v>5.5303500000000003</v>
+      </c>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3">
+        <v>4.9067100000000003</v>
+      </c>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3">
+        <v>4.1264799999999999</v>
+      </c>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3">
+        <v>3.8291499999999998</v>
+      </c>
+      <c r="O118" s="3"/>
+      <c r="P118" s="3">
+        <f>AVERAGE(D118,F118,H118,J118,L118,N118)</f>
+        <v>4.7817283333333336</v>
+      </c>
+      <c r="R118" s="7"/>
+      <c r="S118" s="7"/>
+      <c r="T118" s="7"/>
+    </row>
+    <row r="119" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="9"/>
+      <c r="B119" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3">
+        <v>4.8665000000000003</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3">
+        <v>5.8399900000000002</v>
+      </c>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3">
+        <v>5.65158</v>
+      </c>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3">
+        <v>5.07212</v>
+      </c>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3">
+        <v>4.3304900000000002</v>
+      </c>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3">
+        <v>3.9704700000000002</v>
+      </c>
+      <c r="O119" s="3"/>
+      <c r="P119" s="3">
+        <f>AVERAGE(D119,F119,H119,J119,L119,N119)</f>
+        <v>4.9551916666666669</v>
+      </c>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+    </row>
+    <row r="120" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="9"/>
+      <c r="B120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3">
+        <v>4.9245000000000001</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3">
+        <v>5.9912099999999997</v>
+      </c>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3">
+        <v>5.8172800000000002</v>
+      </c>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3">
+        <v>5.1707700000000001</v>
+      </c>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3">
+        <v>4.4135600000000004</v>
+      </c>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3">
+        <v>4.1507300000000003</v>
+      </c>
+      <c r="O120" s="3"/>
+      <c r="P120" s="3">
+        <f>AVERAGE(D120,F120,H120,J120,L120,N120)</f>
+        <v>5.0780083333333339</v>
+      </c>
+      <c r="R120" s="7"/>
+      <c r="S120" s="7"/>
+      <c r="T120" s="7"/>
+    </row>
+    <row r="121" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="9"/>
+      <c r="B121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4">
+        <v>4.8952299999999997</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4">
+        <v>6.0022099999999998</v>
+      </c>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4">
+        <v>5.8484299999999996</v>
+      </c>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4">
+        <v>5.3302800000000001</v>
+      </c>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4">
+        <v>4.4426100000000002</v>
+      </c>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4">
+        <v>4.1807600000000003</v>
+      </c>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4">
+        <f>AVERAGE(D121,F121,H121,J121,L121,N121)</f>
         <v>5.1165866666666666</v>
       </c>
+      <c r="R121" s="7"/>
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+    </row>
+    <row r="122" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R122" s="7"/>
+      <c r="S122" s="7"/>
+      <c r="T122" s="7"/>
+    </row>
+    <row r="123" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R123" s="7"/>
+      <c r="S123" s="7"/>
+      <c r="T123" s="7"/>
+    </row>
+    <row r="124" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="10"/>
+      <c r="D124" s="10"/>
+      <c r="E124" s="10"/>
+      <c r="F124" s="10"/>
+      <c r="G124" s="10"/>
+      <c r="H124" s="10"/>
+      <c r="I124" s="10"/>
+      <c r="J124" s="10"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="10"/>
+      <c r="M124" s="10"/>
+      <c r="N124" s="10"/>
+      <c r="O124" s="10"/>
+      <c r="P124" s="10"/>
+      <c r="R124" s="7"/>
+      <c r="S124" s="7"/>
+      <c r="T124" s="7"/>
+    </row>
+    <row r="125" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="9"/>
+      <c r="B125" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H125" s="11"/>
+      <c r="I125" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J125" s="11"/>
+      <c r="K125" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L125" s="11"/>
+      <c r="M125" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N125" s="11"/>
+      <c r="O125" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P125" s="11"/>
+      <c r="R125" s="7"/>
+      <c r="S125" s="7"/>
+      <c r="T125" s="7"/>
+    </row>
+    <row r="126" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="9"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R126" s="7"/>
+      <c r="S126" s="7"/>
+      <c r="T126" s="7"/>
+    </row>
+    <row r="127" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="9"/>
+      <c r="B127" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3">
+        <v>4.9519799999999998</v>
+      </c>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3">
+        <v>5.9587399999999997</v>
+      </c>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3">
+        <v>5.6865300000000003</v>
+      </c>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3">
+        <v>5.1108099999999999</v>
+      </c>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3">
+        <v>4.7624199999999997</v>
+      </c>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3">
+        <v>4.1029</v>
+      </c>
+      <c r="O127" s="3"/>
+      <c r="P127" s="3">
+        <f>AVERAGE(D127,F127,H127,J127,L127,N127)</f>
+        <v>5.0955633333333337</v>
+      </c>
+      <c r="R127" s="7"/>
+      <c r="S127" s="7"/>
+      <c r="T127" s="7"/>
+    </row>
+    <row r="128" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="9"/>
+      <c r="B128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3">
+        <v>5.0779899999999998</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3">
+        <v>6.0375899999999998</v>
+      </c>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3">
+        <v>5.8101900000000004</v>
+      </c>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3">
+        <v>5.2471800000000002</v>
+      </c>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3">
+        <v>4.8608700000000002</v>
+      </c>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3">
+        <v>4.2529199999999996</v>
+      </c>
+      <c r="O128" s="3"/>
+      <c r="P128" s="3">
+        <f>AVERAGE(D128,F128,H128,J128,L128,N128)</f>
+        <v>5.2144566666666661</v>
+      </c>
+      <c r="R128" s="7"/>
+      <c r="S128" s="7"/>
+      <c r="T128" s="7"/>
+    </row>
+    <row r="129" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="9"/>
+      <c r="B129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3">
+        <v>5.1763500000000002</v>
+      </c>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3">
+        <v>6.1347899999999997</v>
+      </c>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3">
+        <v>5.9769600000000001</v>
+      </c>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3">
+        <v>5.3600399999999997</v>
+      </c>
+      <c r="K129" s="3"/>
+      <c r="L129" s="3">
+        <v>5.03362</v>
+      </c>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3">
+        <v>4.3368500000000001</v>
+      </c>
+      <c r="O129" s="3"/>
+      <c r="P129" s="3">
+        <f>AVERAGE(D129,F129,H129,J129,L129,N129)</f>
+        <v>5.3364349999999989</v>
+      </c>
+      <c r="R129" s="7"/>
+      <c r="S129" s="7"/>
+      <c r="T129" s="7"/>
+    </row>
+    <row r="130" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="9"/>
+      <c r="B130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3">
+        <v>5.2169400000000001</v>
+      </c>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3">
+        <v>6.1267699999999996</v>
+      </c>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3">
+        <v>5.9864499999999996</v>
+      </c>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3">
+        <v>5.33589</v>
+      </c>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3">
+        <v>5.1133199999999999</v>
+      </c>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3">
+        <v>4.3840300000000001</v>
+      </c>
+      <c r="O130" s="3"/>
+      <c r="P130" s="3">
+        <f>AVERAGE(D130,F130,H130,J130,L130,N130)</f>
+        <v>5.3605666666666671</v>
+      </c>
+      <c r="R130" s="7"/>
+      <c r="S130" s="7"/>
+      <c r="T130" s="7"/>
+    </row>
+    <row r="131" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="9"/>
+      <c r="B131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4">
+        <v>5.2286099999999998</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4">
+        <v>6.20383</v>
+      </c>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4">
+        <v>5.9978999999999996</v>
+      </c>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4">
+        <v>5.39696</v>
+      </c>
+      <c r="K131" s="4"/>
+      <c r="L131" s="4">
+        <v>5.09293</v>
+      </c>
+      <c r="M131" s="4"/>
+      <c r="N131" s="4">
+        <v>4.4227499999999997</v>
+      </c>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4">
+        <f>AVERAGE(D131,F131,H131,J131,L131,N131)</f>
+        <v>5.3904966666666665</v>
+      </c>
+      <c r="R131" s="7"/>
+      <c r="S131" s="7"/>
+      <c r="T131" s="7"/>
+    </row>
+    <row r="132" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="9"/>
+      <c r="B132" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="10"/>
+      <c r="M132" s="10"/>
+      <c r="N132" s="10"/>
+      <c r="O132" s="10"/>
+      <c r="P132" s="10"/>
+      <c r="R132" s="7"/>
+      <c r="S132" s="7"/>
+      <c r="T132" s="7"/>
+    </row>
+    <row r="133" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="9"/>
+      <c r="B133" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C133" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L133" s="11"/>
+      <c r="M133" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N133" s="11"/>
+      <c r="O133" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P133" s="11"/>
+      <c r="R133" s="7"/>
+      <c r="S133" s="7"/>
+      <c r="T133" s="7"/>
+    </row>
+    <row r="134" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="9"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P134" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R134" s="7"/>
+      <c r="S134" s="7"/>
+      <c r="T134" s="7"/>
+    </row>
+    <row r="135" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="9"/>
+      <c r="B135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3">
+        <v>4.4972899999999996</v>
+      </c>
+      <c r="E135" s="3"/>
+      <c r="F135" s="3">
+        <v>5.7499900000000004</v>
+      </c>
+      <c r="G135" s="3"/>
+      <c r="H135" s="3">
+        <v>5.4779799999999996</v>
+      </c>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3">
+        <v>4.7991099999999998</v>
+      </c>
+      <c r="K135" s="3"/>
+      <c r="L135" s="3">
+        <v>4.3675600000000001</v>
+      </c>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3">
+        <v>3.8624499999999999</v>
+      </c>
+      <c r="O135" s="3"/>
+      <c r="P135" s="3">
+        <f>AVERAGE(D135,F135,H135,J135,L135,N135)</f>
+        <v>4.792396666666666</v>
+      </c>
+      <c r="R135" s="7"/>
+      <c r="S135" s="7"/>
+      <c r="T135" s="7"/>
+    </row>
+    <row r="136" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="9"/>
+      <c r="B136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3">
+        <v>4.53803</v>
+      </c>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3">
+        <v>5.7977699999999999</v>
+      </c>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3">
+        <v>5.5980499999999997</v>
+      </c>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3">
+        <v>4.8517099999999997</v>
+      </c>
+      <c r="K136" s="3"/>
+      <c r="L136" s="3">
+        <v>4.5068400000000004</v>
+      </c>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3">
+        <v>3.93241</v>
+      </c>
+      <c r="O136" s="3"/>
+      <c r="P136" s="3">
+        <f>AVERAGE(D136,F136,H136,J136,L136,N136)</f>
+        <v>4.8708016666666669</v>
+      </c>
+      <c r="R136" s="7"/>
+      <c r="S136" s="7"/>
+      <c r="T136" s="7"/>
+    </row>
+    <row r="137" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="9"/>
+      <c r="B137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3">
+        <v>4.7687499999999998</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3">
+        <v>5.87601</v>
+      </c>
+      <c r="G137" s="3"/>
+      <c r="H137" s="3">
+        <v>5.6713199999999997</v>
+      </c>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3">
+        <v>4.9405200000000002</v>
+      </c>
+      <c r="K137" s="3"/>
+      <c r="L137" s="3">
+        <v>4.6174600000000003</v>
+      </c>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3">
+        <v>4.0107900000000001</v>
+      </c>
+      <c r="O137" s="3"/>
+      <c r="P137" s="3">
+        <f>AVERAGE(D137,F137,H137,J137,L137,N137)</f>
+        <v>4.9808083333333331</v>
+      </c>
+      <c r="R137" s="7"/>
+      <c r="S137" s="7"/>
+      <c r="T137" s="7"/>
+    </row>
+    <row r="138" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="9"/>
+      <c r="B138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3">
+        <v>4.6977500000000001</v>
+      </c>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3">
+        <v>6.0045099999999998</v>
+      </c>
+      <c r="G138" s="3"/>
+      <c r="H138" s="3">
+        <v>5.6419800000000002</v>
+      </c>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3">
+        <v>5.0177899999999998</v>
+      </c>
+      <c r="K138" s="3"/>
+      <c r="L138" s="3">
+        <v>4.5989500000000003</v>
+      </c>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3">
+        <v>3.9584000000000001</v>
+      </c>
+      <c r="O138" s="3"/>
+      <c r="P138" s="3">
+        <f>AVERAGE(D138,F138,H138,J138,L138,N138)</f>
+        <v>4.9865633333333337</v>
+      </c>
+      <c r="R138" s="7"/>
+      <c r="S138" s="7"/>
+      <c r="T138" s="7"/>
+    </row>
+    <row r="139" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="9"/>
+      <c r="B139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4">
+        <v>4.7397299999999998</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4">
+        <v>5.8635700000000002</v>
+      </c>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4">
+        <v>5.75807</v>
+      </c>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4">
+        <v>4.9176399999999996</v>
+      </c>
+      <c r="K139" s="4"/>
+      <c r="L139" s="4">
+        <v>4.70146</v>
+      </c>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4">
+        <v>4.1309100000000001</v>
+      </c>
+      <c r="O139" s="4"/>
+      <c r="P139" s="4">
+        <f>AVERAGE(D139,F139,H139,J139,L139,N139)</f>
+        <v>5.0185633333333337</v>
+      </c>
+      <c r="R139" s="7"/>
+      <c r="S139" s="7"/>
+      <c r="T139" s="7"/>
+    </row>
+    <row r="142" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="10"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="10"/>
+      <c r="H142" s="10"/>
+      <c r="I142" s="10"/>
+      <c r="J142" s="10"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="10"/>
+      <c r="M142" s="10"/>
+      <c r="N142" s="10"/>
+      <c r="O142" s="10"/>
+      <c r="P142" s="10"/>
+    </row>
+    <row r="143" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="9"/>
+      <c r="B143" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J143" s="11"/>
+      <c r="K143" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L143" s="11"/>
+      <c r="M143" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N143" s="11"/>
+      <c r="O143" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P143" s="11"/>
+    </row>
+    <row r="144" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="9"/>
+      <c r="B144" s="12"/>
+      <c r="C144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P144" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="9"/>
+      <c r="B145" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3">
+        <v>5.1425200000000002</v>
+      </c>
+      <c r="E145" s="3"/>
+      <c r="F145" s="3">
+        <v>6.1639099999999996</v>
+      </c>
+      <c r="G145" s="3"/>
+      <c r="H145" s="3">
+        <v>5.8667699999999998</v>
+      </c>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3">
+        <v>5.2913699999999997</v>
+      </c>
+      <c r="K145" s="3"/>
+      <c r="L145" s="3">
+        <v>4.87432</v>
+      </c>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3">
+        <v>4.2484099999999998</v>
+      </c>
+      <c r="O145" s="3"/>
+      <c r="P145" s="3">
+        <f>AVERAGE(D145,F145,H145,J145,L145,N145)</f>
+        <v>5.2645499999999998</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="9"/>
+      <c r="B146" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3">
+        <v>5.2753899999999998</v>
+      </c>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3">
+        <v>6.2600499999999997</v>
+      </c>
+      <c r="G146" s="3"/>
+      <c r="H146" s="3">
+        <v>6.0030799999999997</v>
+      </c>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3">
+        <v>5.4375499999999999</v>
+      </c>
+      <c r="K146" s="3"/>
+      <c r="L146" s="3">
+        <v>5.0748699999999998</v>
+      </c>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3">
+        <v>4.4670699999999997</v>
+      </c>
+      <c r="O146" s="3"/>
+      <c r="P146" s="3">
+        <f>AVERAGE(D146,F146,H146,J146,L146,N146)</f>
+        <v>5.419668333333334</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="9"/>
+      <c r="B147" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3">
+        <v>5.4368299999999996</v>
+      </c>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3">
+        <v>6.3815799999999996</v>
+      </c>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3">
+        <v>6.1467700000000001</v>
+      </c>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3">
+        <v>5.6098600000000003</v>
+      </c>
+      <c r="K147" s="3"/>
+      <c r="L147" s="3">
+        <v>5.2762399999999996</v>
+      </c>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3">
+        <v>4.6169399999999996</v>
+      </c>
+      <c r="O147" s="3"/>
+      <c r="P147" s="3">
+        <f>AVERAGE(D147,F147,H147,J147,L147,N147)</f>
+        <v>5.5780366666666668</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="9"/>
+      <c r="B148" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3">
+        <v>5.5129400000000004</v>
+      </c>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3">
+        <v>6.4376899999999999</v>
+      </c>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3">
+        <v>6.2129799999999999</v>
+      </c>
+      <c r="I148" s="3"/>
+      <c r="J148" s="3">
+        <v>5.65036</v>
+      </c>
+      <c r="K148" s="3"/>
+      <c r="L148" s="3">
+        <v>5.3873899999999999</v>
+      </c>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3">
+        <v>4.6532299999999998</v>
+      </c>
+      <c r="O148" s="3"/>
+      <c r="P148" s="3">
+        <f>AVERAGE(D148,F148,H148,J148,L148,N148)</f>
+        <v>5.6424316666666661</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="9"/>
+      <c r="B149" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4">
+        <v>5.5522299999999998</v>
+      </c>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4">
+        <v>6.4609100000000002</v>
+      </c>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4">
+        <v>6.2358000000000002</v>
+      </c>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4">
+        <v>5.7166399999999999</v>
+      </c>
+      <c r="K149" s="4"/>
+      <c r="L149" s="4">
+        <v>5.4241799999999998</v>
+      </c>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4">
+        <v>4.7166100000000002</v>
+      </c>
+      <c r="O149" s="4"/>
+      <c r="P149" s="4">
+        <f>AVERAGE(D149,F149,H149,J149,L149,N149)</f>
+        <v>5.6843950000000012</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="9"/>
+      <c r="B150" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+      <c r="H150" s="10"/>
+      <c r="I150" s="10"/>
+      <c r="J150" s="10"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="10"/>
+      <c r="M150" s="10"/>
+      <c r="N150" s="10"/>
+      <c r="O150" s="10"/>
+      <c r="P150" s="10"/>
+    </row>
+    <row r="151" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="9"/>
+      <c r="B151" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F151" s="11"/>
+      <c r="G151" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H151" s="11"/>
+      <c r="I151" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J151" s="11"/>
+      <c r="K151" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L151" s="11"/>
+      <c r="M151" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N151" s="11"/>
+      <c r="O151" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P151" s="11"/>
+    </row>
+    <row r="152" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="9"/>
+      <c r="B152" s="12"/>
+      <c r="C152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N152" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P152" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="9"/>
+      <c r="B153" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3">
+        <v>4.6648800000000001</v>
+      </c>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3">
+        <v>5.8207300000000002</v>
+      </c>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3">
+        <v>5.5759699999999999</v>
+      </c>
+      <c r="I153" s="3"/>
+      <c r="J153" s="3">
+        <v>4.9920499999999999</v>
+      </c>
+      <c r="K153" s="3"/>
+      <c r="L153" s="3">
+        <v>4.4142200000000003</v>
+      </c>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3">
+        <v>3.9114399999999998</v>
+      </c>
+      <c r="O153" s="3"/>
+      <c r="P153" s="3">
+        <f>AVERAGE(D153,F153,H153,J153,L153,N153)</f>
+        <v>4.8965483333333326</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="9"/>
+      <c r="B154" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3">
+        <v>4.7643700000000004</v>
+      </c>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3">
+        <v>6.0061499999999999</v>
+      </c>
+      <c r="G154" s="3"/>
+      <c r="H154" s="3">
+        <v>5.7176499999999999</v>
+      </c>
+      <c r="I154" s="3"/>
+      <c r="J154" s="3">
+        <v>5.09049</v>
+      </c>
+      <c r="K154" s="3"/>
+      <c r="L154" s="3">
+        <v>4.6910800000000004</v>
+      </c>
+      <c r="M154" s="3"/>
+      <c r="N154" s="3">
+        <v>4.1724699999999997</v>
+      </c>
+      <c r="O154" s="3"/>
+      <c r="P154" s="3">
+        <f>AVERAGE(D154,F154,H154,J154,L154,N154)</f>
+        <v>5.0737016666666666</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="9"/>
+      <c r="B155" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3">
+        <v>4.9665900000000001</v>
+      </c>
+      <c r="E155" s="3"/>
+      <c r="F155" s="3">
+        <v>6.0786800000000003</v>
+      </c>
+      <c r="G155" s="3"/>
+      <c r="H155" s="3">
+        <v>5.9602599999999999</v>
+      </c>
+      <c r="I155" s="3"/>
+      <c r="J155" s="3">
+        <v>5.2721099999999996</v>
+      </c>
+      <c r="K155" s="3"/>
+      <c r="L155" s="3">
+        <v>4.7949000000000002</v>
+      </c>
+      <c r="M155" s="3"/>
+      <c r="N155" s="3">
+        <v>4.2164799999999998</v>
+      </c>
+      <c r="O155" s="3"/>
+      <c r="P155" s="3">
+        <f>AVERAGE(D155,F155,H155,J155,L155,N155)</f>
+        <v>5.2148366666666659</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="9"/>
+      <c r="B156" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3">
+        <v>5.06792</v>
+      </c>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3">
+        <v>6.1188399999999996</v>
+      </c>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3">
+        <v>6.0356500000000004</v>
+      </c>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3">
+        <v>5.2182199999999996</v>
+      </c>
+      <c r="K156" s="3"/>
+      <c r="L156" s="3">
+        <v>4.8553699999999997</v>
+      </c>
+      <c r="M156" s="3"/>
+      <c r="N156" s="3">
+        <v>4.3114299999999997</v>
+      </c>
+      <c r="O156" s="3"/>
+      <c r="P156" s="3">
+        <f>AVERAGE(D156,F156,H156,J156,L156,N156)</f>
+        <v>5.2679049999999998</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="9"/>
+      <c r="B157" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4">
+        <v>4.9878799999999996</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4">
+        <v>6.2057799999999999</v>
+      </c>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4">
+        <v>5.9762000000000004</v>
+      </c>
+      <c r="I157" s="4"/>
+      <c r="J157" s="4">
+        <v>5.2882300000000004</v>
+      </c>
+      <c r="K157" s="4"/>
+      <c r="L157" s="4">
+        <v>4.8907600000000002</v>
+      </c>
+      <c r="M157" s="4"/>
+      <c r="N157" s="4">
+        <v>4.3394599999999999</v>
+      </c>
+      <c r="O157" s="4"/>
+      <c r="P157" s="4">
+        <f>AVERAGE(D157,F157,H157,J157,L157,N157)</f>
+        <v>5.2813849999999993</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="115">
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="O63:P63"/>
-    <mergeCell ref="A56:A67"/>
-    <mergeCell ref="B56:P56"/>
-    <mergeCell ref="B57:B58"/>
+  <mergeCells count="172">
+    <mergeCell ref="O133:P133"/>
+    <mergeCell ref="B74:P74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="O81:P81"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="B96:P96"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="A74:A85"/>
+    <mergeCell ref="A124:A139"/>
+    <mergeCell ref="B124:P124"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="I125:J125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="O125:P125"/>
+    <mergeCell ref="B132:P132"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="M133:N133"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="B80:P80"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A106:A121"/>
+    <mergeCell ref="B106:P106"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="B114:P114"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="O115:P115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="I115:J115"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="A56:A71"/>
+    <mergeCell ref="B64:P64"/>
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="E57:F57"/>
     <mergeCell ref="G57:H57"/>
     <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="B62:P62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="M71:N71"/>
-    <mergeCell ref="O71:P71"/>
-    <mergeCell ref="B78:P78"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="O79:P79"/>
     <mergeCell ref="A88:A103"/>
     <mergeCell ref="B88:P88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="B96:P96"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="M97:N97"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="A70:A85"/>
-    <mergeCell ref="B70:P70"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="O29:P29"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
     <mergeCell ref="A20:A35"/>
     <mergeCell ref="B20:P20"/>
     <mergeCell ref="B21:B22"/>
@@ -8037,18 +9838,6 @@
     <mergeCell ref="M21:N21"/>
     <mergeCell ref="O21:P21"/>
     <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="R2:T85"/>
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:B4"/>
@@ -8061,13 +9850,52 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="B10:P10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="R2:T4"/>
+    <mergeCell ref="A142:A157"/>
+    <mergeCell ref="B142:P142"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="I143:J143"/>
+    <mergeCell ref="K143:L143"/>
+    <mergeCell ref="M143:N143"/>
+    <mergeCell ref="O143:P143"/>
+    <mergeCell ref="B150:P150"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="I151:J151"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K151:L151"/>
+    <mergeCell ref="M151:N151"/>
+    <mergeCell ref="O151:P151"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="B56:P56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
     <mergeCell ref="A38:A53"/>
-    <mergeCell ref="B46:P46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:D47"/>
     <mergeCell ref="B38:P38"/>
     <mergeCell ref="B39:B40"/>
     <mergeCell ref="C39:D39"/>
@@ -8077,6 +9905,15 @@
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="O39:P39"/>
+    <mergeCell ref="B46:P46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8114,11 +9951,11 @@
       <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
@@ -8153,9 +9990,9 @@
         <v>7</v>
       </c>
       <c r="P3" s="11"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
@@ -8202,9 +10039,9 @@
       <c r="P4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
@@ -8240,9 +10077,9 @@
         <f>AVERAGE(D5,F5,H5,J5,L5,N5)</f>
         <v>4.4582833333333332</v>
       </c>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -8278,9 +10115,9 @@
         <f>AVERAGE(D6,F6,H6,J6,L6,N6)</f>
         <v>4.6170416666666663</v>
       </c>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
@@ -8316,9 +10153,9 @@
         <f>AVERAGE(D7,F7,H7,J7,L7,N7)</f>
         <v>4.7523433333333331</v>
       </c>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
@@ -8354,9 +10191,9 @@
         <f>AVERAGE(D8,F8,H8,J8,L8,N8)</f>
         <v>4.8081849999999999</v>
       </c>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
@@ -8392,9 +10229,9 @@
         <f>AVERAGE(D9,F9,H9,J9,L9,N9)</f>
         <v>4.8034516666666667</v>
       </c>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
@@ -8415,9 +10252,9 @@
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
@@ -8452,9 +10289,9 @@
         <v>7</v>
       </c>
       <c r="P11" s="11"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
@@ -8501,9 +10338,9 @@
       <c r="P12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
@@ -8539,9 +10376,9 @@
         <f>AVERAGE(D13,F13,H13,J13,L13,N13)</f>
         <v>4.2027533333333329</v>
       </c>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
@@ -8577,9 +10414,9 @@
         <f>AVERAGE(D14,F14,H14,J14,L14,N14)</f>
         <v>4.3188599999999999</v>
       </c>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
@@ -8615,9 +10452,9 @@
         <f>AVERAGE(D15,F15,H15,J15,L15,N15)</f>
         <v>4.4561250000000001</v>
       </c>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
@@ -8653,9 +10490,9 @@
         <f>AVERAGE(D16,F16,H16,J16,L16,N16)</f>
         <v>4.4992200000000002</v>
       </c>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
     </row>
     <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
@@ -8691,9 +10528,9 @@
         <f>AVERAGE(D17,F17,H17,J17,L17,N17)</f>
         <v>4.4970349999999994</v>
       </c>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
     </row>
     <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="3"/>
@@ -8710,14 +10547,14 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
     </row>
     <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
     </row>
     <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
@@ -8740,9 +10577,9 @@
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
     </row>
     <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
@@ -8777,9 +10614,9 @@
         <v>7</v>
       </c>
       <c r="P21" s="11"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
     </row>
     <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
@@ -8826,9 +10663,9 @@
       <c r="P22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="13"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
     </row>
     <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
@@ -8864,9 +10701,9 @@
         <f>AVERAGE(D23,F23,H23,J23,L23,N23)</f>
         <v>5.0685666666666664</v>
       </c>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
     </row>
     <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
@@ -8902,9 +10739,9 @@
         <f>AVERAGE(D24,F24,H24,J24,L24,N24)</f>
         <v>5.2380616666666659</v>
       </c>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
     </row>
     <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
@@ -8940,9 +10777,9 @@
         <f>AVERAGE(D25,F25,H25,J25,L25,N25)</f>
         <v>5.3789299999999995</v>
       </c>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
     </row>
     <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
@@ -8978,9 +10815,9 @@
         <f>AVERAGE(D26,F26,H26,J26,L26,N26)</f>
         <v>5.4285083333333342</v>
       </c>
-      <c r="R26" s="13"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
     </row>
     <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
@@ -9016,9 +10853,9 @@
         <f>AVERAGE(D27,F27,H27,J27,L27,N27)</f>
         <v>5.4313233333333342</v>
       </c>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
     </row>
     <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
@@ -9039,9 +10876,9 @@
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
-      <c r="R28" s="13"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
@@ -9076,9 +10913,9 @@
         <v>7</v>
       </c>
       <c r="P29" s="11"/>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
     </row>
     <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
@@ -9125,9 +10962,9 @@
       <c r="P30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R30" s="13"/>
-      <c r="S30" s="13"/>
-      <c r="T30" s="13"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
     </row>
     <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
@@ -9163,9 +11000,9 @@
         <f>AVERAGE(D31,F31,H31,J31,L31,N31)</f>
         <v>4.7426500000000003</v>
       </c>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
     </row>
     <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
@@ -9201,9 +11038,9 @@
         <f>AVERAGE(D32,F32,H32,J32,L32,N32)</f>
         <v>4.8972699999999998</v>
       </c>
-      <c r="R32" s="13"/>
-      <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
@@ -9239,9 +11076,9 @@
         <f>AVERAGE(D33,F33,H33,J33,L33,N33)</f>
         <v>5.0063466666666665</v>
       </c>
-      <c r="R33" s="13"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="13"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
@@ -9277,9 +11114,9 @@
         <f>AVERAGE(D34,F34,H34,J34,L34,N34)</f>
         <v>5.0522599999999995</v>
       </c>
-      <c r="R34" s="13"/>
-      <c r="S34" s="13"/>
-      <c r="T34" s="13"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
@@ -9315,9 +11152,9 @@
         <f>AVERAGE(D35,F35,H35,J35,L35,N35)</f>
         <v>5.0503766666666676</v>
       </c>
-      <c r="R35" s="13"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="13"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="3"/>
@@ -9334,14 +11171,14 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="R36" s="13"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="13"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R37" s="13"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="13"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
@@ -9364,9 +11201,9 @@
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
-      <c r="R38" s="13"/>
-      <c r="S38" s="13"/>
-      <c r="T38" s="13"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+      <c r="T38" s="14"/>
     </row>
     <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
@@ -9401,9 +11238,9 @@
         <v>7</v>
       </c>
       <c r="P39" s="11"/>
-      <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
+      <c r="R39" s="14"/>
+      <c r="S39" s="14"/>
+      <c r="T39" s="14"/>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
@@ -9450,9 +11287,9 @@
       <c r="P40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R40" s="13"/>
-      <c r="S40" s="13"/>
-      <c r="T40" s="13"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
     </row>
     <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
@@ -9488,9 +11325,9 @@
         <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
         <v>5.3169616666666668</v>
       </c>
-      <c r="R41" s="13"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="13"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
     </row>
     <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
@@ -9526,9 +11363,9 @@
         <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
         <v>5.6161366666666668</v>
       </c>
-      <c r="R42" s="13"/>
-      <c r="S42" s="13"/>
-      <c r="T42" s="13"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
     </row>
     <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
@@ -9564,9 +11401,9 @@
         <f>AVERAGE(D43,F43,H43,J43,L43,N43)</f>
         <v>5.8235816666666667</v>
       </c>
-      <c r="R43" s="13"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="13"/>
+      <c r="R43" s="14"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="14"/>
     </row>
     <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
@@ -9602,9 +11439,9 @@
         <f>AVERAGE(D44,F44,H44,J44,L44,N44)</f>
         <v>5.9325699999999992</v>
       </c>
-      <c r="R44" s="13"/>
-      <c r="S44" s="13"/>
-      <c r="T44" s="13"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
     </row>
     <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
@@ -9640,9 +11477,9 @@
         <f>AVERAGE(D45,F45,H45,J45,L45,N45)</f>
         <v>5.9658383333333331</v>
       </c>
-      <c r="R45" s="13"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
+      <c r="R45" s="14"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
     </row>
     <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
@@ -9663,9 +11500,9 @@
       <c r="N46" s="10"/>
       <c r="O46" s="10"/>
       <c r="P46" s="10"/>
-      <c r="R46" s="13"/>
-      <c r="S46" s="13"/>
-      <c r="T46" s="13"/>
+      <c r="R46" s="14"/>
+      <c r="S46" s="14"/>
+      <c r="T46" s="14"/>
     </row>
     <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
@@ -9700,9 +11537,9 @@
         <v>7</v>
       </c>
       <c r="P47" s="11"/>
-      <c r="R47" s="13"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="13"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
@@ -9749,9 +11586,9 @@
       <c r="P48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R48" s="13"/>
-      <c r="S48" s="13"/>
-      <c r="T48" s="13"/>
+      <c r="R48" s="14"/>
+      <c r="S48" s="14"/>
+      <c r="T48" s="14"/>
     </row>
     <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
@@ -9787,9 +11624,9 @@
         <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
         <v>4.9174750000000005</v>
       </c>
-      <c r="R49" s="13"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
+      <c r="R49" s="14"/>
+      <c r="S49" s="14"/>
+      <c r="T49" s="14"/>
     </row>
     <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
@@ -9825,9 +11662,9 @@
         <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
         <v>5.1870916666666673</v>
       </c>
-      <c r="R50" s="13"/>
-      <c r="S50" s="13"/>
-      <c r="T50" s="13"/>
+      <c r="R50" s="14"/>
+      <c r="S50" s="14"/>
+      <c r="T50" s="14"/>
     </row>
     <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
@@ -9863,9 +11700,9 @@
         <f>AVERAGE(D51,F51,H51,J51,L51,N51)</f>
         <v>5.3623650000000005</v>
       </c>
-      <c r="R51" s="13"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="13"/>
+      <c r="R51" s="14"/>
+      <c r="S51" s="14"/>
+      <c r="T51" s="14"/>
     </row>
     <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
@@ -9901,9 +11738,9 @@
         <f>AVERAGE(D52,F52,H52,J52,L52,N52)</f>
         <v>5.4886949999999999</v>
       </c>
-      <c r="R52" s="13"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="13"/>
+      <c r="R52" s="14"/>
+      <c r="S52" s="14"/>
+      <c r="T52" s="14"/>
     </row>
     <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
@@ -9939,19 +11776,19 @@
         <f>AVERAGE(D53,F53,H53,J53,L53,N53)</f>
         <v>5.513703333333333</v>
       </c>
-      <c r="R53" s="13"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="13"/>
+      <c r="R53" s="14"/>
+      <c r="S53" s="14"/>
+      <c r="T53" s="14"/>
     </row>
     <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R54" s="13"/>
-      <c r="S54" s="13"/>
-      <c r="T54" s="13"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
     </row>
     <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R55" s="13"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="13"/>
+      <c r="R55" s="14"/>
+      <c r="S55" s="14"/>
+      <c r="T55" s="14"/>
     </row>
     <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
@@ -9974,9 +11811,9 @@
       <c r="N56" s="10"/>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
-      <c r="R56" s="13"/>
-      <c r="S56" s="13"/>
-      <c r="T56" s="13"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
     </row>
     <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
@@ -10011,9 +11848,9 @@
         <v>7</v>
       </c>
       <c r="P57" s="11"/>
-      <c r="R57" s="13"/>
-      <c r="S57" s="13"/>
-      <c r="T57" s="13"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
     </row>
     <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
@@ -10060,9 +11897,9 @@
       <c r="P58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R58" s="13"/>
-      <c r="S58" s="13"/>
-      <c r="T58" s="13"/>
+      <c r="R58" s="14"/>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
     </row>
     <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
@@ -10098,9 +11935,9 @@
         <f>AVERAGE(D59,F59,H59,J59,L59,N59)</f>
         <v>5.3013983333333332</v>
       </c>
-      <c r="R59" s="13"/>
-      <c r="S59" s="13"/>
-      <c r="T59" s="13"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="14"/>
+      <c r="T59" s="14"/>
     </row>
     <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
@@ -10136,9 +11973,9 @@
         <f>AVERAGE(D60,F60,H60,J60,L60,N60)</f>
         <v>5.6281533333333336</v>
       </c>
-      <c r="R60" s="13"/>
-      <c r="S60" s="13"/>
-      <c r="T60" s="13"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
     </row>
     <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
@@ -10174,9 +12011,9 @@
         <f>AVERAGE(D61,F61,H61,J61,L61,N61)</f>
         <v>5.9497950000000008</v>
       </c>
-      <c r="R61" s="13"/>
-      <c r="S61" s="13"/>
-      <c r="T61" s="13"/>
+      <c r="R61" s="14"/>
+      <c r="S61" s="14"/>
+      <c r="T61" s="14"/>
     </row>
     <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
@@ -10212,9 +12049,9 @@
         <f>AVERAGE(D62,F62,H62,J62,L62,N62)</f>
         <v>6.0984300000000005</v>
       </c>
-      <c r="R62" s="13"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="13"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
     </row>
     <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
@@ -10250,9 +12087,9 @@
         <f>AVERAGE(D63,F63,H63,J63,L63,N63)</f>
         <v>6.1350333333333333</v>
       </c>
-      <c r="R63" s="13"/>
-      <c r="S63" s="13"/>
-      <c r="T63" s="13"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
     </row>
     <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
@@ -10273,9 +12110,9 @@
       <c r="N64" s="10"/>
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
-      <c r="R64" s="13"/>
-      <c r="S64" s="13"/>
-      <c r="T64" s="13"/>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
     </row>
     <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
@@ -10310,9 +12147,9 @@
         <v>7</v>
       </c>
       <c r="P65" s="11"/>
-      <c r="R65" s="13"/>
-      <c r="S65" s="13"/>
-      <c r="T65" s="13"/>
+      <c r="R65" s="14"/>
+      <c r="S65" s="14"/>
+      <c r="T65" s="14"/>
     </row>
     <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
@@ -10359,9 +12196,9 @@
       <c r="P66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="13"/>
-      <c r="S66" s="13"/>
-      <c r="T66" s="13"/>
+      <c r="R66" s="14"/>
+      <c r="S66" s="14"/>
+      <c r="T66" s="14"/>
     </row>
     <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
@@ -10397,9 +12234,9 @@
         <f>AVERAGE(D67,F67,H67,J67,L67,N67)</f>
         <v>4.8743566666666664</v>
       </c>
-      <c r="R67" s="13"/>
-      <c r="S67" s="13"/>
-      <c r="T67" s="13"/>
+      <c r="R67" s="14"/>
+      <c r="S67" s="14"/>
+      <c r="T67" s="14"/>
     </row>
     <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
@@ -10435,9 +12272,9 @@
         <f>AVERAGE(D68,F68,H68,J68,L68,N68)</f>
         <v>5.1494650000000002</v>
       </c>
-      <c r="R68" s="13"/>
-      <c r="S68" s="13"/>
-      <c r="T68" s="13"/>
+      <c r="R68" s="14"/>
+      <c r="S68" s="14"/>
+      <c r="T68" s="14"/>
     </row>
     <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
@@ -10473,9 +12310,9 @@
         <f>AVERAGE(D69,F69,H69,J69,L69,N69)</f>
         <v>5.4268516666666669</v>
       </c>
-      <c r="R69" s="13"/>
-      <c r="S69" s="13"/>
-      <c r="T69" s="13"/>
+      <c r="R69" s="14"/>
+      <c r="S69" s="14"/>
+      <c r="T69" s="14"/>
     </row>
     <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9"/>
@@ -10511,9 +12348,9 @@
         <f>AVERAGE(D70,F70,H70,J70,L70,N70)</f>
         <v>5.5563666666666665</v>
       </c>
-      <c r="R70" s="13"/>
-      <c r="S70" s="13"/>
-      <c r="T70" s="13"/>
+      <c r="R70" s="14"/>
+      <c r="S70" s="14"/>
+      <c r="T70" s="14"/>
     </row>
     <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9"/>
@@ -10549,9 +12386,9 @@
         <f>AVERAGE(D71,F71,H71,J71,L71,N71)</f>
         <v>5.6595800000000009</v>
       </c>
-      <c r="R71" s="13"/>
-      <c r="S71" s="13"/>
-      <c r="T71" s="13"/>
+      <c r="R71" s="14"/>
+      <c r="S71" s="14"/>
+      <c r="T71" s="14"/>
     </row>
     <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R72" s="7"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D78DBF-9290-469E-92C0-B0A608F0AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896F3566-5E5F-4A3D-B3BF-65D2AE934EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
   <sheets>
     <sheet name="llama2-7b" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="48">
   <si>
     <t>Data Num.</t>
   </si>
@@ -5887,19 +5887,34 @@
         <v>8</v>
       </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
+      <c r="D41" s="3">
+        <v>4.4246600000000003</v>
+      </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3">
+        <v>5.2936300000000003</v>
+      </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
+      <c r="H41" s="3">
+        <v>5.0303100000000001</v>
+      </c>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
+      <c r="J41" s="3">
+        <v>4.6042699999999996</v>
+      </c>
       <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="L41" s="3">
+        <v>4.0099400000000003</v>
+      </c>
       <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="N41" s="3">
+        <v>3.56975</v>
+      </c>
       <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
+      <c r="P41" s="3">
+        <f>AVERAGE(D41,F41,H41,J41,L41,N41)</f>
+        <v>4.4887600000000001</v>
+      </c>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -5910,19 +5925,34 @@
         <v>9</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>4.6986999999999997</v>
+      </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3">
+        <v>5.6137300000000003</v>
+      </c>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="3">
+        <v>5.3724999999999996</v>
+      </c>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+      <c r="J42" s="3">
+        <v>4.8760899999999996</v>
+      </c>
       <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="L42" s="3">
+        <v>4.3469600000000002</v>
+      </c>
       <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="N42" s="3">
+        <v>3.8274699999999999</v>
+      </c>
       <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
+      <c r="P42" s="3">
+        <f>AVERAGE(D42,F42,H42,J42,L42,N42)</f>
+        <v>4.7892416666666664</v>
+      </c>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
@@ -6111,19 +6141,34 @@
         <v>8</v>
       </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="D49" s="3">
+        <v>4.1194499999999996</v>
+      </c>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3">
+        <v>5.1203599999999998</v>
+      </c>
       <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
+      <c r="H49" s="3">
+        <v>4.8131599999999999</v>
+      </c>
       <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
+      <c r="J49" s="3">
+        <v>4.29678</v>
+      </c>
       <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
+      <c r="L49" s="3">
+        <v>3.7155300000000002</v>
+      </c>
       <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
+      <c r="N49" s="3">
+        <v>3.2848999999999999</v>
+      </c>
       <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
+      <c r="P49" s="3">
+        <f>AVERAGE(D49,F49,H49,J49,L49,N49)</f>
+        <v>4.2250300000000003</v>
+      </c>
       <c r="R49" s="7"/>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -6134,19 +6179,34 @@
         <v>9</v>
       </c>
       <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3">
+        <v>4.2852399999999999</v>
+      </c>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3">
+        <v>5.3870699999999996</v>
+      </c>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
+      <c r="H50" s="3">
+        <v>5.17645</v>
+      </c>
       <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
+      <c r="J50" s="3">
+        <v>4.6856400000000002</v>
+      </c>
       <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
+      <c r="L50" s="3">
+        <v>4.0411799999999998</v>
+      </c>
       <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
+      <c r="N50" s="3">
+        <v>3.5925400000000001</v>
+      </c>
       <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
+      <c r="P50" s="3">
+        <f>AVERAGE(D50,F50,H50,J50,L50,N50)</f>
+        <v>4.5280199999999997</v>
+      </c>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
@@ -9923,7 +9983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E601461E-E0CB-471A-BB17-97A9D65353CC}">
-  <dimension ref="A2:T73"/>
+  <dimension ref="A2:T89"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -12400,8 +12460,579 @@
       <c r="S73" s="7"/>
       <c r="T73" s="7"/>
     </row>
+    <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+    </row>
+    <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="9"/>
+      <c r="B75" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="11"/>
+    </row>
+    <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="9"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="9"/>
+      <c r="B77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>5.5220399999999996</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3">
+        <v>6.9964899999999997</v>
+      </c>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3">
+        <v>6.54542</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3">
+        <v>5.6508099999999999</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3">
+        <v>5.1178100000000004</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>4.4133100000000001</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3">
+        <f>AVERAGE(D77,F77,H77,J77,L77,N77)</f>
+        <v>5.7076466666666663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="9"/>
+      <c r="B78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>5.7255799999999999</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3">
+        <v>7.1998300000000004</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3">
+        <v>6.7830500000000002</v>
+      </c>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3">
+        <v>5.8335900000000001</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3">
+        <v>5.4020400000000004</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3">
+        <v>4.5986900000000004</v>
+      </c>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3">
+        <f>AVERAGE(D78,F78,H78,J78,L78,N78)</f>
+        <v>5.923796666666667</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="9"/>
+      <c r="B79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3">
+        <v>5.9523999999999999</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3">
+        <v>7.4973299999999998</v>
+      </c>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3">
+        <v>6.9494199999999999</v>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3">
+        <v>6.1371000000000002</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3">
+        <v>5.6459799999999998</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>4.7589899999999998</v>
+      </c>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3">
+        <f>AVERAGE(D79,F79,H79,J79,L79,N79)</f>
+        <v>6.1568699999999987</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3">
+        <v>6.09992</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3">
+        <v>7.6119700000000003</v>
+      </c>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3">
+        <v>7.1602199999999998</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3">
+        <v>6.3007499999999999</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3">
+        <v>5.7742199999999997</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3">
+        <v>4.8783399999999997</v>
+      </c>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3">
+        <f>AVERAGE(D80,F80,H80,J80,L80,N80)</f>
+        <v>6.3042366666666672</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="9"/>
+      <c r="B81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4">
+        <v>6.1384100000000004</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4">
+        <v>7.5655200000000002</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4">
+        <v>7.27156</v>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4">
+        <v>6.3005899999999997</v>
+      </c>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4">
+        <v>5.82369</v>
+      </c>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4">
+        <v>4.9643600000000001</v>
+      </c>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4">
+        <f>AVERAGE(D81,F81,H81,J81,L81,N81)</f>
+        <v>6.3440216666666664</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
+      <c r="B82" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+    </row>
+    <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="9"/>
+      <c r="B83" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="11"/>
+      <c r="M83" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N83" s="11"/>
+      <c r="O83" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="P83" s="11"/>
+    </row>
+    <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="9"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="9"/>
+      <c r="B85" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3">
+        <v>4.9509299999999996</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3">
+        <v>6.5409800000000002</v>
+      </c>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3">
+        <v>6.1789199999999997</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3">
+        <v>5.19</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3">
+        <v>4.6705500000000004</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3">
+        <v>4.0139300000000002</v>
+      </c>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3">
+        <f>AVERAGE(D85,F85,H85,J85,L85,N85)</f>
+        <v>5.257551666666668</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="9"/>
+      <c r="B86" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3">
+        <v>5.1339100000000002</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3">
+        <v>6.6997200000000001</v>
+      </c>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3">
+        <v>6.3095100000000004</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3">
+        <v>5.3921700000000001</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3">
+        <v>4.7391899999999998</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3">
+        <v>4.2642600000000002</v>
+      </c>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3">
+        <f>AVERAGE(D86,F86,H86,J86,L86,N86)</f>
+        <v>5.4231266666666658</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="9"/>
+      <c r="B87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3">
+        <v>5.3834299999999997</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3">
+        <v>6.9919500000000001</v>
+      </c>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3">
+        <v>6.6197800000000004</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3">
+        <v>5.5469200000000001</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3">
+        <v>5.0340600000000002</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3">
+        <v>4.3357999999999999</v>
+      </c>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3">
+        <f>AVERAGE(D87,F87,H87,J87,L87,N87)</f>
+        <v>5.6519900000000005</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="9"/>
+      <c r="B88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>5.4582300000000004</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3">
+        <v>7.0065799999999996</v>
+      </c>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3">
+        <v>6.8334700000000002</v>
+      </c>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3">
+        <v>5.6489799999999999</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3">
+        <v>5.1306500000000002</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3">
+        <v>4.4939499999999999</v>
+      </c>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3">
+        <f>AVERAGE(D88,F88,H88,J88,L88,N88)</f>
+        <v>5.7619766666666665</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="9"/>
+      <c r="B89" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4">
+        <v>5.4510300000000003</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4">
+        <v>7.1321500000000002</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4">
+        <v>6.8049299999999997</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4">
+        <v>5.7448199999999998</v>
+      </c>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4">
+        <v>5.2659399999999996</v>
+      </c>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4">
+        <v>4.3027300000000004</v>
+      </c>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4">
+        <f>AVERAGE(D89,F89,H89,J89,L89,N89)</f>
+        <v>5.7835999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="96">
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="A74:A89"/>
+    <mergeCell ref="B74:P74"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="B82:P82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="I83:J83"/>
     <mergeCell ref="A56:A71"/>
     <mergeCell ref="B56:P56"/>
     <mergeCell ref="B57:B58"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3362A4-ABE7-403D-AC56-C4587166A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4EA924-BED3-4BF5-8B80-BDB632750C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
   <sheets>
     <sheet name="llama2-7b" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="52">
   <si>
     <t>Data Num.</t>
   </si>
@@ -732,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA153E9-5DFB-45B3-8931-84232E27E98E}">
-  <dimension ref="A2:P117"/>
+  <dimension ref="A2:P153"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -4387,8 +4387,932 @@
         <v>4.2067850000000009</v>
       </c>
     </row>
+    <row r="120" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="11"/>
+      <c r="K120" s="11"/>
+      <c r="L120" s="11"/>
+      <c r="M120" s="11"/>
+      <c r="N120" s="11"/>
+      <c r="O120" s="11"/>
+      <c r="P120" s="11"/>
+    </row>
+    <row r="121" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="10"/>
+      <c r="B121" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P121" s="12"/>
+    </row>
+    <row r="122" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="10"/>
+      <c r="B122" s="13"/>
+      <c r="C122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="10"/>
+      <c r="B123" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3">
+        <v>5.3084199999999999</v>
+      </c>
+      <c r="E123" s="3"/>
+      <c r="F123" s="3">
+        <v>5.9846700000000004</v>
+      </c>
+      <c r="G123" s="3"/>
+      <c r="H123" s="3">
+        <v>5.3923100000000002</v>
+      </c>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3">
+        <v>5.1606800000000002</v>
+      </c>
+      <c r="K123" s="3"/>
+      <c r="L123" s="3">
+        <v>5.0110099999999997</v>
+      </c>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3">
+        <v>4.8119699999999996</v>
+      </c>
+      <c r="O123" s="3"/>
+      <c r="P123" s="3">
+        <f>AVERAGE(D123,F123,H123,J123,L123,N123)</f>
+        <v>5.2781766666666661</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="10"/>
+      <c r="B124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3">
+        <v>5.4507500000000002</v>
+      </c>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3">
+        <v>6.1112000000000002</v>
+      </c>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3">
+        <v>5.5802399999999999</v>
+      </c>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3">
+        <v>5.29922</v>
+      </c>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3">
+        <v>5.1404800000000002</v>
+      </c>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3">
+        <v>4.9340000000000002</v>
+      </c>
+      <c r="O124" s="3"/>
+      <c r="P124" s="3">
+        <f>AVERAGE(D124,F124,H124,J124,L124,N124)</f>
+        <v>5.4193150000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="10"/>
+      <c r="B125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+    </row>
+    <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="10"/>
+      <c r="B126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="P126" s="3"/>
+    </row>
+    <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="10"/>
+      <c r="B127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4">
+        <v>5.5671099999999996</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4">
+        <v>6.19611</v>
+      </c>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4">
+        <v>5.7102599999999999</v>
+      </c>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4">
+        <v>5.4685300000000003</v>
+      </c>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4">
+        <v>5.2820099999999996</v>
+      </c>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4">
+        <v>5.1318999999999999</v>
+      </c>
+      <c r="O127" s="4"/>
+      <c r="P127" s="4">
+        <f>AVERAGE(D127,F127,H127,J127,L127,N127)</f>
+        <v>5.5593200000000005</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="10"/>
+      <c r="B128" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="11"/>
+      <c r="K128" s="11"/>
+      <c r="L128" s="11"/>
+      <c r="M128" s="11"/>
+      <c r="N128" s="11"/>
+      <c r="O128" s="11"/>
+      <c r="P128" s="11"/>
+    </row>
+    <row r="129" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="10"/>
+      <c r="B129" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H129" s="12"/>
+      <c r="I129" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J129" s="12"/>
+      <c r="K129" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" s="12"/>
+      <c r="M129" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N129" s="12"/>
+      <c r="O129" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P129" s="12"/>
+    </row>
+    <row r="130" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="10"/>
+      <c r="B130" s="13"/>
+      <c r="C130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P130" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="10"/>
+      <c r="B131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3">
+        <v>5.0545600000000004</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3">
+        <v>5.6094799999999996</v>
+      </c>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3">
+        <v>5.3452900000000003</v>
+      </c>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3">
+        <v>5.0238699999999996</v>
+      </c>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3">
+        <v>4.70695</v>
+      </c>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3">
+        <v>4.6079100000000004</v>
+      </c>
+      <c r="O131" s="3"/>
+      <c r="P131" s="3">
+        <f>AVERAGE(D131,F131,H131,J131,L131,N131)</f>
+        <v>5.0580099999999995</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="10"/>
+      <c r="B132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3">
+        <v>5.2711100000000002</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3">
+        <v>5.7284899999999999</v>
+      </c>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3">
+        <v>5.3707099999999999</v>
+      </c>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3">
+        <v>5.1860499999999998</v>
+      </c>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3">
+        <v>4.9246100000000004</v>
+      </c>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3">
+        <v>4.7375800000000003</v>
+      </c>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3">
+        <f>AVERAGE(D132,F132,H132,J132,L132,N132)</f>
+        <v>5.2030916666666664</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="10"/>
+      <c r="B133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
+      <c r="P133" s="3"/>
+    </row>
+    <row r="134" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="10"/>
+      <c r="B134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+      <c r="O134" s="3"/>
+      <c r="P134" s="3"/>
+    </row>
+    <row r="135" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="10"/>
+      <c r="B135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4">
+        <v>5.3418599999999996</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4">
+        <v>5.8317300000000003</v>
+      </c>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4">
+        <v>5.6138399999999997</v>
+      </c>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4">
+        <v>5.3025200000000003</v>
+      </c>
+      <c r="K135" s="4"/>
+      <c r="L135" s="4">
+        <v>5.0721499999999997</v>
+      </c>
+      <c r="M135" s="4"/>
+      <c r="N135" s="4">
+        <v>4.9667399999999997</v>
+      </c>
+      <c r="O135" s="4"/>
+      <c r="P135" s="4">
+        <f>AVERAGE(D135,F135,H135,J135,L135,N135)</f>
+        <v>5.3548066666666676</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="11"/>
+      <c r="K138" s="11"/>
+      <c r="L138" s="11"/>
+      <c r="M138" s="11"/>
+      <c r="N138" s="11"/>
+      <c r="O138" s="11"/>
+      <c r="P138" s="11"/>
+    </row>
+    <row r="139" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="10"/>
+      <c r="B139" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H139" s="12"/>
+      <c r="I139" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J139" s="12"/>
+      <c r="K139" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L139" s="12"/>
+      <c r="M139" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N139" s="12"/>
+      <c r="O139" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P139" s="12"/>
+    </row>
+    <row r="140" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="10"/>
+      <c r="B140" s="13"/>
+      <c r="C140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P140" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="10"/>
+      <c r="B141" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3">
+        <v>5.3713899999999999</v>
+      </c>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3">
+        <v>6.0194299999999998</v>
+      </c>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3">
+        <v>5.3910799999999997</v>
+      </c>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3">
+        <v>5.2080599999999997</v>
+      </c>
+      <c r="K141" s="3"/>
+      <c r="L141" s="3">
+        <v>5.0383800000000001</v>
+      </c>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3">
+        <v>4.78667</v>
+      </c>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3">
+        <f>AVERAGE(D141,F141,H141,J141,L141,N141)</f>
+        <v>5.3025016666666671</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="10"/>
+      <c r="B142" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+    </row>
+    <row r="143" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="10"/>
+      <c r="B143" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+      <c r="P143" s="3"/>
+    </row>
+    <row r="144" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="10"/>
+      <c r="B144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+      <c r="P144" s="3"/>
+    </row>
+    <row r="145" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="10"/>
+      <c r="B145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+      <c r="L145" s="4"/>
+      <c r="M145" s="4"/>
+      <c r="N145" s="4"/>
+      <c r="O145" s="4"/>
+      <c r="P145" s="4"/>
+    </row>
+    <row r="146" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="10"/>
+      <c r="B146" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="11"/>
+      <c r="K146" s="11"/>
+      <c r="L146" s="11"/>
+      <c r="M146" s="11"/>
+      <c r="N146" s="11"/>
+      <c r="O146" s="11"/>
+      <c r="P146" s="11"/>
+    </row>
+    <row r="147" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="10"/>
+      <c r="B147" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D147" s="12"/>
+      <c r="E147" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H147" s="12"/>
+      <c r="I147" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J147" s="12"/>
+      <c r="K147" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L147" s="12"/>
+      <c r="M147" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N147" s="12"/>
+      <c r="O147" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P147" s="12"/>
+    </row>
+    <row r="148" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="10"/>
+      <c r="B148" s="13"/>
+      <c r="C148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P148" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="10"/>
+      <c r="B149" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3">
+        <v>5.1380600000000003</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3">
+        <v>5.7798699999999998</v>
+      </c>
+      <c r="G149" s="3"/>
+      <c r="H149" s="3">
+        <v>5.4028099999999997</v>
+      </c>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3">
+        <v>5.0453799999999998</v>
+      </c>
+      <c r="K149" s="3"/>
+      <c r="L149" s="3">
+        <v>4.7468599999999999</v>
+      </c>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3">
+        <v>4.52386</v>
+      </c>
+      <c r="O149" s="3"/>
+      <c r="P149" s="3">
+        <f>AVERAGE(D149,F149,H149,J149,L149,N149)</f>
+        <v>5.1061399999999999</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="10"/>
+      <c r="B150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+      <c r="L150" s="3"/>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+      <c r="O150" s="3"/>
+      <c r="P150" s="3"/>
+    </row>
+    <row r="151" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="10"/>
+      <c r="B151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3"/>
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
+    </row>
+    <row r="152" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="10"/>
+      <c r="B152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="3"/>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+      <c r="O152" s="3"/>
+      <c r="P152" s="3"/>
+    </row>
+    <row r="153" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="10"/>
+      <c r="B153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4"/>
+      <c r="P153" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="133">
+  <mergeCells count="171">
     <mergeCell ref="A74:A89"/>
     <mergeCell ref="B82:P82"/>
     <mergeCell ref="B83:B84"/>
@@ -4522,6 +5446,44 @@
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="M65:N65"/>
     <mergeCell ref="O65:P65"/>
+    <mergeCell ref="A120:A135"/>
+    <mergeCell ref="B120:P120"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="I121:J121"/>
+    <mergeCell ref="K121:L121"/>
+    <mergeCell ref="M121:N121"/>
+    <mergeCell ref="O121:P121"/>
+    <mergeCell ref="B128:P128"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="G129:H129"/>
+    <mergeCell ref="I129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="O129:P129"/>
+    <mergeCell ref="A138:A153"/>
+    <mergeCell ref="B138:P138"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="I139:J139"/>
+    <mergeCell ref="K139:L139"/>
+    <mergeCell ref="M139:N139"/>
+    <mergeCell ref="O139:P139"/>
+    <mergeCell ref="B146:P146"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="G147:H147"/>
+    <mergeCell ref="I147:J147"/>
+    <mergeCell ref="K147:L147"/>
+    <mergeCell ref="M147:N147"/>
+    <mergeCell ref="O147:P147"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4EA924-BED3-4BF5-8B80-BDB632750C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECA58BD-5009-4DC2-94C1-01DCBE4C2489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
   <sheets>
     <sheet name="llama2-7b" sheetId="1" r:id="rId1"/>
@@ -4565,19 +4565,34 @@
         <v>10</v>
       </c>
       <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
+      <c r="D125" s="3">
+        <v>5.5413300000000003</v>
+      </c>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
+      <c r="F125" s="3">
+        <v>6.1304800000000004</v>
+      </c>
       <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
+      <c r="H125" s="3">
+        <v>5.6616900000000001</v>
+      </c>
       <c r="I125" s="3"/>
-      <c r="J125" s="3"/>
+      <c r="J125" s="3">
+        <v>5.35581</v>
+      </c>
       <c r="K125" s="3"/>
-      <c r="L125" s="3"/>
+      <c r="L125" s="3">
+        <v>5.2620199999999997</v>
+      </c>
       <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
+      <c r="N125" s="3">
+        <v>5.0157999999999996</v>
+      </c>
       <c r="O125" s="3"/>
-      <c r="P125" s="3"/>
+      <c r="P125" s="3">
+        <f>AVERAGE(D125,F125,H125,J125,L125,N125)</f>
+        <v>5.4945216666666665</v>
+      </c>
     </row>
     <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
@@ -4585,19 +4600,34 @@
         <v>11</v>
       </c>
       <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
+      <c r="D126" s="3">
+        <v>5.5616700000000003</v>
+      </c>
       <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3">
+        <v>6.1896599999999999</v>
+      </c>
       <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
+      <c r="H126" s="3">
+        <v>5.6893200000000004</v>
+      </c>
       <c r="I126" s="3"/>
-      <c r="J126" s="3"/>
+      <c r="J126" s="3">
+        <v>5.3944900000000002</v>
+      </c>
       <c r="K126" s="3"/>
-      <c r="L126" s="3"/>
+      <c r="L126" s="3">
+        <v>5.33873</v>
+      </c>
       <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
+      <c r="N126" s="3">
+        <v>5.0751200000000001</v>
+      </c>
       <c r="O126" s="3"/>
-      <c r="P126" s="3"/>
+      <c r="P126" s="3">
+        <f>AVERAGE(D126,F126,H126,J126,L126,N126)</f>
+        <v>5.5414983333333332</v>
+      </c>
     </row>
     <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
@@ -4810,19 +4840,34 @@
         <v>10</v>
       </c>
       <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
+      <c r="D133" s="3">
+        <v>5.2300300000000002</v>
+      </c>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
+      <c r="F133" s="3">
+        <v>5.7807399999999998</v>
+      </c>
       <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
+      <c r="H133" s="3">
+        <v>5.6081000000000003</v>
+      </c>
       <c r="I133" s="3"/>
-      <c r="J133" s="3"/>
+      <c r="J133" s="3">
+        <v>5.1676700000000002</v>
+      </c>
       <c r="K133" s="3"/>
-      <c r="L133" s="3"/>
+      <c r="L133" s="3">
+        <v>5.0256100000000004</v>
+      </c>
       <c r="M133" s="3"/>
-      <c r="N133" s="3"/>
+      <c r="N133" s="3">
+        <v>4.8696200000000003</v>
+      </c>
       <c r="O133" s="3"/>
-      <c r="P133" s="3"/>
+      <c r="P133" s="3">
+        <f>AVERAGE(D133,F133,H133,J133,L133,N133)</f>
+        <v>5.2802950000000006</v>
+      </c>
     </row>
     <row r="134" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
@@ -4830,19 +4875,34 @@
         <v>11</v>
       </c>
       <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
+      <c r="D134" s="3">
+        <v>5.3484600000000002</v>
+      </c>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
+      <c r="F134" s="3">
+        <v>5.7775999999999996</v>
+      </c>
       <c r="G134" s="3"/>
-      <c r="H134" s="3"/>
+      <c r="H134" s="3">
+        <v>5.5211499999999996</v>
+      </c>
       <c r="I134" s="3"/>
-      <c r="J134" s="3"/>
+      <c r="J134" s="3">
+        <v>5.20024</v>
+      </c>
       <c r="K134" s="3"/>
-      <c r="L134" s="3"/>
+      <c r="L134" s="3">
+        <v>5.0918900000000002</v>
+      </c>
       <c r="M134" s="3"/>
-      <c r="N134" s="3"/>
+      <c r="N134" s="3">
+        <v>4.9492399999999996</v>
+      </c>
       <c r="O134" s="3"/>
-      <c r="P134" s="3"/>
+      <c r="P134" s="3">
+        <f>AVERAGE(D134,F134,H134,J134,L134,N134)</f>
+        <v>5.3147633333333326</v>
+      </c>
     </row>
     <row r="135" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
@@ -4984,7 +5044,7 @@
     <row r="141" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3">
@@ -5019,82 +5079,142 @@
     <row r="142" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
+      <c r="D142" s="3">
+        <v>5.5344300000000004</v>
+      </c>
       <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
+      <c r="F142" s="3">
+        <v>6.1561000000000003</v>
+      </c>
       <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
+      <c r="H142" s="3">
+        <v>5.5279600000000002</v>
+      </c>
       <c r="I142" s="3"/>
-      <c r="J142" s="3"/>
+      <c r="J142" s="3">
+        <v>5.4154499999999999</v>
+      </c>
       <c r="K142" s="3"/>
-      <c r="L142" s="3"/>
+      <c r="L142" s="3">
+        <v>5.1887400000000001</v>
+      </c>
       <c r="M142" s="3"/>
-      <c r="N142" s="3"/>
+      <c r="N142" s="3">
+        <v>5.0075000000000003</v>
+      </c>
       <c r="O142" s="3"/>
-      <c r="P142" s="3"/>
+      <c r="P142" s="3">
+        <f>AVERAGE(D142,F142,H142,J142,L142,N142)</f>
+        <v>5.4716966666666664</v>
+      </c>
     </row>
     <row r="143" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
+      <c r="D143" s="3">
+        <v>5.6849999999999996</v>
+      </c>
       <c r="E143" s="3"/>
-      <c r="F143" s="3"/>
+      <c r="F143" s="3">
+        <v>6.26755</v>
+      </c>
       <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
+      <c r="H143" s="3">
+        <v>5.7454999999999998</v>
+      </c>
       <c r="I143" s="3"/>
-      <c r="J143" s="3"/>
+      <c r="J143" s="3">
+        <v>5.5574700000000004</v>
+      </c>
       <c r="K143" s="3"/>
-      <c r="L143" s="3"/>
+      <c r="L143" s="3">
+        <v>5.3547799999999999</v>
+      </c>
       <c r="M143" s="3"/>
-      <c r="N143" s="3"/>
+      <c r="N143" s="3">
+        <v>5.2196300000000004</v>
+      </c>
       <c r="O143" s="3"/>
-      <c r="P143" s="3"/>
+      <c r="P143" s="3">
+        <f>AVERAGE(D143,F143,H143,J143,L143,N143)</f>
+        <v>5.6383216666666662</v>
+      </c>
     </row>
     <row r="144" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
+      <c r="D144" s="3">
+        <v>5.7656999999999998</v>
+      </c>
       <c r="E144" s="3"/>
-      <c r="F144" s="3"/>
+      <c r="F144" s="3">
+        <v>6.2893699999999999</v>
+      </c>
       <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
+      <c r="H144" s="3">
+        <v>5.8411200000000001</v>
+      </c>
       <c r="I144" s="3"/>
-      <c r="J144" s="3"/>
+      <c r="J144" s="3">
+        <v>5.6383700000000001</v>
+      </c>
       <c r="K144" s="3"/>
-      <c r="L144" s="3"/>
+      <c r="L144" s="3">
+        <v>5.4586800000000002</v>
+      </c>
       <c r="M144" s="3"/>
-      <c r="N144" s="3"/>
+      <c r="N144" s="3">
+        <v>5.2736799999999997</v>
+      </c>
       <c r="O144" s="3"/>
-      <c r="P144" s="3"/>
+      <c r="P144" s="3">
+        <f>AVERAGE(D144,F144,H144,J144,L144,N144)</f>
+        <v>5.7111533333333329</v>
+      </c>
     </row>
     <row r="145" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
+      <c r="D145" s="4">
+        <v>5.7968900000000003</v>
+      </c>
       <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
+      <c r="F145" s="4">
+        <v>6.3645399999999999</v>
+      </c>
       <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
+      <c r="H145" s="4">
+        <v>5.8893199999999997</v>
+      </c>
       <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
+      <c r="J145" s="4">
+        <v>5.6879999999999997</v>
+      </c>
       <c r="K145" s="4"/>
-      <c r="L145" s="4"/>
+      <c r="L145" s="4">
+        <v>5.5101599999999999</v>
+      </c>
       <c r="M145" s="4"/>
-      <c r="N145" s="4"/>
+      <c r="N145" s="4">
+        <v>5.3722700000000003</v>
+      </c>
       <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
+      <c r="P145" s="4">
+        <f>AVERAGE(D145,F145,H145,J145,L145,N145)</f>
+        <v>5.7701966666666662</v>
+      </c>
     </row>
     <row r="146" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
@@ -5199,7 +5319,7 @@
     <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3">
@@ -5234,82 +5354,142 @@
     <row r="150" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
+      <c r="D150" s="3">
+        <v>5.2527699999999999</v>
+      </c>
       <c r="E150" s="3"/>
-      <c r="F150" s="3"/>
+      <c r="F150" s="3">
+        <v>5.8203399999999998</v>
+      </c>
       <c r="G150" s="3"/>
-      <c r="H150" s="3"/>
+      <c r="H150" s="3">
+        <v>5.4510800000000001</v>
+      </c>
       <c r="I150" s="3"/>
-      <c r="J150" s="3"/>
+      <c r="J150" s="3">
+        <v>5.2700800000000001</v>
+      </c>
       <c r="K150" s="3"/>
-      <c r="L150" s="3"/>
+      <c r="L150" s="3">
+        <v>4.9187900000000004</v>
+      </c>
       <c r="M150" s="3"/>
-      <c r="N150" s="3"/>
+      <c r="N150" s="3">
+        <v>4.78355</v>
+      </c>
       <c r="O150" s="3"/>
-      <c r="P150" s="3"/>
+      <c r="P150" s="3">
+        <f>AVERAGE(D150,F150,H150,J150,L150,N150)</f>
+        <v>5.249435000000001</v>
+      </c>
     </row>
     <row r="151" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
+      <c r="D151" s="3">
+        <v>5.3843300000000003</v>
+      </c>
       <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
+      <c r="F151" s="3">
+        <v>5.9468800000000002</v>
+      </c>
       <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
+      <c r="H151" s="3">
+        <v>5.6490299999999998</v>
+      </c>
       <c r="I151" s="3"/>
-      <c r="J151" s="3"/>
+      <c r="J151" s="3">
+        <v>5.4015399999999998</v>
+      </c>
       <c r="K151" s="3"/>
-      <c r="L151" s="3"/>
+      <c r="L151" s="3">
+        <v>5.1441100000000004</v>
+      </c>
       <c r="M151" s="3"/>
-      <c r="N151" s="3"/>
+      <c r="N151" s="3">
+        <v>4.9908999999999999</v>
+      </c>
       <c r="O151" s="3"/>
-      <c r="P151" s="3"/>
+      <c r="P151" s="3">
+        <f>AVERAGE(D151,F151,H151,J151,L151,N151)</f>
+        <v>5.4194649999999998</v>
+      </c>
     </row>
     <row r="152" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
+      <c r="D152" s="3">
+        <v>5.5658099999999999</v>
+      </c>
       <c r="E152" s="3"/>
-      <c r="F152" s="3"/>
+      <c r="F152" s="3">
+        <v>5.9458500000000001</v>
+      </c>
       <c r="G152" s="3"/>
-      <c r="H152" s="3"/>
+      <c r="H152" s="3">
+        <v>5.7013400000000001</v>
+      </c>
       <c r="I152" s="3"/>
-      <c r="J152" s="3"/>
+      <c r="J152" s="3">
+        <v>5.4972300000000001</v>
+      </c>
       <c r="K152" s="3"/>
-      <c r="L152" s="3"/>
+      <c r="L152" s="3">
+        <v>5.1961000000000004</v>
+      </c>
       <c r="M152" s="3"/>
-      <c r="N152" s="3"/>
+      <c r="N152" s="3">
+        <v>5.11693</v>
+      </c>
       <c r="O152" s="3"/>
-      <c r="P152" s="3"/>
+      <c r="P152" s="3">
+        <f>AVERAGE(D152,F152,H152,J152,L152,N152)</f>
+        <v>5.5038766666666676</v>
+      </c>
     </row>
     <row r="153" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
+      <c r="D153" s="4">
+        <v>5.5848500000000003</v>
+      </c>
       <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
+      <c r="F153" s="4">
+        <v>5.9521800000000002</v>
+      </c>
       <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
+      <c r="H153" s="4">
+        <v>5.7834300000000001</v>
+      </c>
       <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
+      <c r="J153" s="4">
+        <v>5.5549999999999997</v>
+      </c>
       <c r="K153" s="4"/>
-      <c r="L153" s="4"/>
+      <c r="L153" s="4">
+        <v>5.2787199999999999</v>
+      </c>
       <c r="M153" s="4"/>
-      <c r="N153" s="4"/>
+      <c r="N153" s="4">
+        <v>5.1163699999999999</v>
+      </c>
       <c r="O153" s="4"/>
-      <c r="P153" s="4"/>
+      <c r="P153" s="4">
+        <f>AVERAGE(D153,F153,H153,J153,L153,N153)</f>
+        <v>5.545091666666667</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="171">

--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work Files\LLM\codes\LD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECA58BD-5009-4DC2-94C1-01DCBE4C2489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD020F5-3EF3-4B52-ACC4-54373B6645BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{19EAABD8-86DB-47E6-BFD1-E1050F603343}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="54">
   <si>
     <t>Data Num.</t>
   </si>
@@ -257,6 +257,14 @@
   </si>
   <si>
     <t>PRISM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sHASS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sPRISM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8809,7 +8817,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D606126C-3FE1-428A-BDA2-93CD7E4A00CB}">
-  <dimension ref="A2:T157"/>
+  <dimension ref="A2:T211"/>
   <sheetFormatPr defaultColWidth="7.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16" width="13.58203125" style="1" customWidth="1"/>
@@ -13650,7 +13658,7 @@
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>13</v>
@@ -14200,8 +14208,1582 @@
         <v>5.2813849999999993</v>
       </c>
     </row>
+    <row r="160" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="11"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="11"/>
+      <c r="H160" s="11"/>
+      <c r="I160" s="11"/>
+      <c r="J160" s="11"/>
+      <c r="K160" s="11"/>
+      <c r="L160" s="11"/>
+      <c r="M160" s="11"/>
+      <c r="N160" s="11"/>
+      <c r="O160" s="11"/>
+      <c r="P160" s="11"/>
+    </row>
+    <row r="161" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="10"/>
+      <c r="B161" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D161" s="12"/>
+      <c r="E161" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H161" s="12"/>
+      <c r="I161" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J161" s="12"/>
+      <c r="K161" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L161" s="12"/>
+      <c r="M161" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N161" s="12"/>
+      <c r="O161" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P161" s="12"/>
+    </row>
+    <row r="162" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="10"/>
+      <c r="B162" s="13"/>
+      <c r="C162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N162" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="10"/>
+      <c r="B163" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3">
+        <v>4.8345599999999997</v>
+      </c>
+      <c r="E163" s="3"/>
+      <c r="F163" s="3">
+        <v>5.78383</v>
+      </c>
+      <c r="G163" s="3"/>
+      <c r="H163" s="3">
+        <v>5.5440500000000004</v>
+      </c>
+      <c r="I163" s="3"/>
+      <c r="J163" s="3">
+        <v>5.0284899999999997</v>
+      </c>
+      <c r="K163" s="3"/>
+      <c r="L163" s="3">
+        <v>4.26187</v>
+      </c>
+      <c r="M163" s="3"/>
+      <c r="N163" s="3">
+        <v>3.9002300000000001</v>
+      </c>
+      <c r="O163" s="3"/>
+      <c r="P163" s="3">
+        <f>AVERAGE(D163,F163,H163,J163,L163,N163)</f>
+        <v>4.892171666666667</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="10"/>
+      <c r="B164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3">
+        <v>4.9534900000000004</v>
+      </c>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3">
+        <v>5.8631200000000003</v>
+      </c>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3">
+        <v>5.6006799999999997</v>
+      </c>
+      <c r="I164" s="3"/>
+      <c r="J164" s="3">
+        <v>5.2051499999999997</v>
+      </c>
+      <c r="K164" s="3"/>
+      <c r="L164" s="3">
+        <v>4.3748399999999998</v>
+      </c>
+      <c r="M164" s="3"/>
+      <c r="N164" s="3">
+        <v>3.99783</v>
+      </c>
+      <c r="O164" s="3"/>
+      <c r="P164" s="3">
+        <f>AVERAGE(D164,F164,H164,J164,L164,N164)</f>
+        <v>4.9991849999999998</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="10"/>
+      <c r="B165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="3"/>
+      <c r="M165" s="3"/>
+      <c r="N165" s="3"/>
+      <c r="O165" s="3"/>
+      <c r="P165" s="3" t="e">
+        <f>AVERAGE(D165,F165,H165,J165,L165,N165)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="10"/>
+      <c r="B166" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+      <c r="N166" s="3"/>
+      <c r="O166" s="3"/>
+      <c r="P166" s="3" t="e">
+        <f>AVERAGE(D166,F166,H166,J166,L166,N166)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="10"/>
+      <c r="B167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4">
+        <v>5.0605599999999997</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4">
+        <v>5.99892</v>
+      </c>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4">
+        <v>5.7626200000000001</v>
+      </c>
+      <c r="I167" s="4"/>
+      <c r="J167" s="4">
+        <v>5.2848899999999999</v>
+      </c>
+      <c r="K167" s="4"/>
+      <c r="L167" s="4">
+        <v>4.5831499999999998</v>
+      </c>
+      <c r="M167" s="4"/>
+      <c r="N167" s="4">
+        <v>4.1350300000000004</v>
+      </c>
+      <c r="O167" s="4"/>
+      <c r="P167" s="4">
+        <f>AVERAGE(D167,F167,H167,J167,L167,N167)</f>
+        <v>5.137528333333333</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="10"/>
+      <c r="B168" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="11"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11"/>
+      <c r="G168" s="11"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="11"/>
+      <c r="J168" s="11"/>
+      <c r="K168" s="11"/>
+      <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
+      <c r="N168" s="11"/>
+      <c r="O168" s="11"/>
+      <c r="P168" s="11"/>
+    </row>
+    <row r="169" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="10"/>
+      <c r="B169" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D169" s="12"/>
+      <c r="E169" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H169" s="12"/>
+      <c r="I169" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J169" s="12"/>
+      <c r="K169" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L169" s="12"/>
+      <c r="M169" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N169" s="12"/>
+      <c r="O169" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P169" s="12"/>
+    </row>
+    <row r="170" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="10"/>
+      <c r="B170" s="13"/>
+      <c r="C170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="10"/>
+      <c r="B171" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3">
+        <v>4.4094499999999996</v>
+      </c>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3">
+        <v>5.5106099999999998</v>
+      </c>
+      <c r="G171" s="3"/>
+      <c r="H171" s="3">
+        <v>5.2763</v>
+      </c>
+      <c r="I171" s="3"/>
+      <c r="J171" s="3">
+        <v>4.6450699999999996</v>
+      </c>
+      <c r="K171" s="3"/>
+      <c r="L171" s="3">
+        <v>3.9482300000000001</v>
+      </c>
+      <c r="M171" s="3"/>
+      <c r="N171" s="3">
+        <v>3.6365699999999999</v>
+      </c>
+      <c r="O171" s="3"/>
+      <c r="P171" s="3">
+        <f>AVERAGE(D171,F171,H171,J171,L171,N171)</f>
+        <v>4.5710383333333331</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="10"/>
+      <c r="B172" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3">
+        <v>4.4936100000000003</v>
+      </c>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3">
+        <v>5.6301399999999999</v>
+      </c>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3">
+        <v>5.4397799999999998</v>
+      </c>
+      <c r="I172" s="3"/>
+      <c r="J172" s="3">
+        <v>4.68405</v>
+      </c>
+      <c r="K172" s="3"/>
+      <c r="L172" s="3">
+        <v>4.0178700000000003</v>
+      </c>
+      <c r="M172" s="3"/>
+      <c r="N172" s="3">
+        <v>3.7398199999999999</v>
+      </c>
+      <c r="O172" s="3"/>
+      <c r="P172" s="3">
+        <f>AVERAGE(D172,F172,H172,J172,L172,N172)</f>
+        <v>4.6675450000000005</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="10"/>
+      <c r="B173" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+      <c r="N173" s="3"/>
+      <c r="O173" s="3"/>
+      <c r="P173" s="3" t="e">
+        <f>AVERAGE(D173,F173,H173,J173,L173,N173)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="10"/>
+      <c r="B174" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+      <c r="N174" s="3"/>
+      <c r="O174" s="3"/>
+      <c r="P174" s="3" t="e">
+        <f>AVERAGE(D174,F174,H174,J174,L174,N174)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="10"/>
+      <c r="B175" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4">
+        <v>4.6453499999999996</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4">
+        <v>5.6632300000000004</v>
+      </c>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4">
+        <v>5.4914199999999997</v>
+      </c>
+      <c r="I175" s="4"/>
+      <c r="J175" s="4">
+        <v>4.8323499999999999</v>
+      </c>
+      <c r="K175" s="4"/>
+      <c r="L175" s="4">
+        <v>4.1166</v>
+      </c>
+      <c r="M175" s="4"/>
+      <c r="N175" s="4">
+        <v>3.8397399999999999</v>
+      </c>
+      <c r="O175" s="4"/>
+      <c r="P175" s="4">
+        <f>AVERAGE(D175,F175,H175,J175,L175,N175)</f>
+        <v>4.7647816666666669</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="11"/>
+      <c r="J178" s="11"/>
+      <c r="K178" s="11"/>
+      <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
+      <c r="N178" s="11"/>
+      <c r="O178" s="11"/>
+      <c r="P178" s="11"/>
+    </row>
+    <row r="179" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="10"/>
+      <c r="B179" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D179" s="12"/>
+      <c r="E179" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H179" s="12"/>
+      <c r="I179" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J179" s="12"/>
+      <c r="K179" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L179" s="12"/>
+      <c r="M179" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N179" s="12"/>
+      <c r="O179" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P179" s="12"/>
+    </row>
+    <row r="180" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="10"/>
+      <c r="B180" s="13"/>
+      <c r="C180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P180" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="10"/>
+      <c r="B181" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3">
+        <v>4.8525200000000002</v>
+      </c>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3">
+        <v>5.8368399999999996</v>
+      </c>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3">
+        <v>5.5527899999999999</v>
+      </c>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3">
+        <v>5.1691900000000004</v>
+      </c>
+      <c r="K181" s="3"/>
+      <c r="L181" s="3">
+        <v>4.2882699999999998</v>
+      </c>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3">
+        <v>3.9023400000000001</v>
+      </c>
+      <c r="O181" s="3"/>
+      <c r="P181" s="3">
+        <f>AVERAGE(D181,F181,H181,J181,L181,N181)</f>
+        <v>4.9336583333333337</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="10"/>
+      <c r="B182" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3">
+        <v>5.06907</v>
+      </c>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3">
+        <v>5.9813799999999997</v>
+      </c>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3">
+        <v>5.7794100000000004</v>
+      </c>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3">
+        <v>5.3164999999999996</v>
+      </c>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3">
+        <v>4.5904400000000001</v>
+      </c>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3">
+        <v>4.1261000000000001</v>
+      </c>
+      <c r="O182" s="3"/>
+      <c r="P182" s="3">
+        <f>AVERAGE(D182,F182,H182,J182,L182,N182)</f>
+        <v>5.1438166666666669</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="10"/>
+      <c r="B183" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="3"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+      <c r="O183" s="3"/>
+      <c r="P183" s="3" t="e">
+        <f>AVERAGE(D183,F183,H183,J183,L183,N183)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="10"/>
+      <c r="B184" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+      <c r="O184" s="3"/>
+      <c r="P184" s="3" t="e">
+        <f>AVERAGE(D184,F184,H184,J184,L184,N184)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="10"/>
+      <c r="B185" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+      <c r="I185" s="4"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
+      <c r="L185" s="4"/>
+      <c r="M185" s="4"/>
+      <c r="N185" s="4"/>
+      <c r="O185" s="4"/>
+      <c r="P185" s="4" t="e">
+        <f>AVERAGE(D185,F185,H185,J185,L185,N185)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="10"/>
+      <c r="B186" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C186" s="11"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="11"/>
+      <c r="I186" s="11"/>
+      <c r="J186" s="11"/>
+      <c r="K186" s="11"/>
+      <c r="L186" s="11"/>
+      <c r="M186" s="11"/>
+      <c r="N186" s="11"/>
+      <c r="O186" s="11"/>
+      <c r="P186" s="11"/>
+    </row>
+    <row r="187" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="10"/>
+      <c r="B187" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D187" s="12"/>
+      <c r="E187" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H187" s="12"/>
+      <c r="I187" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J187" s="12"/>
+      <c r="K187" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L187" s="12"/>
+      <c r="M187" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N187" s="12"/>
+      <c r="O187" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P187" s="12"/>
+    </row>
+    <row r="188" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="10"/>
+      <c r="B188" s="13"/>
+      <c r="C188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O188" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P188" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="10"/>
+      <c r="B189" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3">
+        <v>4.4356799999999996</v>
+      </c>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3">
+        <v>5.5202</v>
+      </c>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3">
+        <v>5.3457699999999999</v>
+      </c>
+      <c r="I189" s="3"/>
+      <c r="J189" s="3">
+        <v>4.81379</v>
+      </c>
+      <c r="K189" s="3"/>
+      <c r="L189" s="3">
+        <v>3.9738099999999998</v>
+      </c>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3">
+        <v>3.5743100000000001</v>
+      </c>
+      <c r="O189" s="3"/>
+      <c r="P189" s="3">
+        <f>AVERAGE(D189,F189,H189,J189,L189,N189)</f>
+        <v>4.6105933333333331</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="10"/>
+      <c r="B190" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3">
+        <v>4.6087999999999996</v>
+      </c>
+      <c r="E190" s="3"/>
+      <c r="F190" s="3">
+        <v>5.7934700000000001</v>
+      </c>
+      <c r="G190" s="3"/>
+      <c r="H190" s="3">
+        <v>5.5641800000000003</v>
+      </c>
+      <c r="I190" s="3"/>
+      <c r="J190" s="3">
+        <v>4.9355399999999996</v>
+      </c>
+      <c r="K190" s="3"/>
+      <c r="L190" s="3">
+        <v>4.1799600000000003</v>
+      </c>
+      <c r="M190" s="3"/>
+      <c r="N190" s="3">
+        <v>3.76118</v>
+      </c>
+      <c r="O190" s="3"/>
+      <c r="P190" s="3">
+        <f>AVERAGE(D190,F190,H190,J190,L190,N190)</f>
+        <v>4.8071883333333334</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="10"/>
+      <c r="B191" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="3"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="3"/>
+      <c r="M191" s="3"/>
+      <c r="N191" s="3"/>
+      <c r="O191" s="3"/>
+      <c r="P191" s="3" t="e">
+        <f>AVERAGE(D191,F191,H191,J191,L191,N191)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="10"/>
+      <c r="B192" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+      <c r="O192" s="3"/>
+      <c r="P192" s="3" t="e">
+        <f>AVERAGE(D192,F192,H192,J192,L192,N192)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="10"/>
+      <c r="B193" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+      <c r="I193" s="4"/>
+      <c r="J193" s="4"/>
+      <c r="K193" s="4"/>
+      <c r="L193" s="4"/>
+      <c r="M193" s="4"/>
+      <c r="N193" s="4"/>
+      <c r="O193" s="4"/>
+      <c r="P193" s="4" t="e">
+        <f>AVERAGE(D193,F193,H193,J193,L193,N193)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B196" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="11"/>
+      <c r="I196" s="11"/>
+      <c r="J196" s="11"/>
+      <c r="K196" s="11"/>
+      <c r="L196" s="11"/>
+      <c r="M196" s="11"/>
+      <c r="N196" s="11"/>
+      <c r="O196" s="11"/>
+      <c r="P196" s="11"/>
+    </row>
+    <row r="197" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="10"/>
+      <c r="B197" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D197" s="12"/>
+      <c r="E197" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H197" s="12"/>
+      <c r="I197" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J197" s="12"/>
+      <c r="K197" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L197" s="12"/>
+      <c r="M197" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N197" s="12"/>
+      <c r="O197" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P197" s="12"/>
+    </row>
+    <row r="198" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="10"/>
+      <c r="B198" s="13"/>
+      <c r="C198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N198" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O198" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P198" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="10"/>
+      <c r="B199" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3">
+        <v>4.8350999999999997</v>
+      </c>
+      <c r="E199" s="3"/>
+      <c r="F199" s="3">
+        <v>5.8418599999999996</v>
+      </c>
+      <c r="G199" s="3"/>
+      <c r="H199" s="3">
+        <v>5.3804100000000004</v>
+      </c>
+      <c r="I199" s="3"/>
+      <c r="J199" s="3">
+        <v>5.1307099999999997</v>
+      </c>
+      <c r="K199" s="3"/>
+      <c r="L199" s="3">
+        <v>4.2869599999999997</v>
+      </c>
+      <c r="M199" s="3"/>
+      <c r="N199" s="3">
+        <v>3.9249200000000002</v>
+      </c>
+      <c r="O199" s="3"/>
+      <c r="P199" s="3">
+        <f>AVERAGE(D199,F199,H199,J199,L199,N199)</f>
+        <v>4.8999933333333336</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="10"/>
+      <c r="B200" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3">
+        <v>5.0928699999999996</v>
+      </c>
+      <c r="E200" s="3"/>
+      <c r="F200" s="3">
+        <v>5.9963899999999999</v>
+      </c>
+      <c r="G200" s="3"/>
+      <c r="H200" s="3">
+        <v>5.7409499999999998</v>
+      </c>
+      <c r="I200" s="3"/>
+      <c r="J200" s="3">
+        <v>5.3913000000000002</v>
+      </c>
+      <c r="K200" s="3"/>
+      <c r="L200" s="3">
+        <v>4.4194800000000001</v>
+      </c>
+      <c r="M200" s="3"/>
+      <c r="N200" s="3">
+        <v>4.1529199999999999</v>
+      </c>
+      <c r="O200" s="3"/>
+      <c r="P200" s="3">
+        <f>AVERAGE(D200,F200,H200,J200,L200,N200)</f>
+        <v>5.132318333333334</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="10"/>
+      <c r="B201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3">
+        <v>5.3201000000000001</v>
+      </c>
+      <c r="E201" s="3"/>
+      <c r="F201" s="3">
+        <v>6.1637899999999997</v>
+      </c>
+      <c r="G201" s="3"/>
+      <c r="H201" s="3">
+        <v>5.9080199999999996</v>
+      </c>
+      <c r="I201" s="3"/>
+      <c r="J201" s="3">
+        <v>5.5360100000000001</v>
+      </c>
+      <c r="K201" s="3"/>
+      <c r="L201" s="3">
+        <v>4.71347</v>
+      </c>
+      <c r="M201" s="3"/>
+      <c r="N201" s="3">
+        <v>4.3147200000000003</v>
+      </c>
+      <c r="O201" s="3"/>
+      <c r="P201" s="3">
+        <f>AVERAGE(D201,F201,H201,J201,L201,N201)</f>
+        <v>5.3260183333333337</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="10"/>
+      <c r="B202" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3">
+        <v>5.36137</v>
+      </c>
+      <c r="E202" s="3"/>
+      <c r="F202" s="3">
+        <v>6.2123900000000001</v>
+      </c>
+      <c r="G202" s="3"/>
+      <c r="H202" s="3">
+        <v>6.0613599999999996</v>
+      </c>
+      <c r="I202" s="3"/>
+      <c r="J202" s="3">
+        <v>5.5939699999999997</v>
+      </c>
+      <c r="K202" s="3"/>
+      <c r="L202" s="3">
+        <v>4.8575299999999997</v>
+      </c>
+      <c r="M202" s="3"/>
+      <c r="N202" s="3">
+        <v>4.4312899999999997</v>
+      </c>
+      <c r="O202" s="3"/>
+      <c r="P202" s="3">
+        <f>AVERAGE(D202,F202,H202,J202,L202,N202)</f>
+        <v>5.4196516666666668</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="10"/>
+      <c r="B203" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C203" s="4"/>
+      <c r="D203" s="4">
+        <v>5.4131900000000002</v>
+      </c>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4">
+        <v>6.2545000000000002</v>
+      </c>
+      <c r="G203" s="4"/>
+      <c r="H203" s="4">
+        <v>6.0812799999999996</v>
+      </c>
+      <c r="I203" s="4"/>
+      <c r="J203" s="4">
+        <v>5.6418999999999997</v>
+      </c>
+      <c r="K203" s="4"/>
+      <c r="L203" s="4">
+        <v>4.8334400000000004</v>
+      </c>
+      <c r="M203" s="4"/>
+      <c r="N203" s="4">
+        <v>4.4951999999999996</v>
+      </c>
+      <c r="O203" s="4"/>
+      <c r="P203" s="4">
+        <f>AVERAGE(D203,F203,H203,J203,L203,N203)</f>
+        <v>5.4532516666666666</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="10"/>
+      <c r="B204" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11"/>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="11"/>
+      <c r="I204" s="11"/>
+      <c r="J204" s="11"/>
+      <c r="K204" s="11"/>
+      <c r="L204" s="11"/>
+      <c r="M204" s="11"/>
+      <c r="N204" s="11"/>
+      <c r="O204" s="11"/>
+      <c r="P204" s="11"/>
+    </row>
+    <row r="205" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="10"/>
+      <c r="B205" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D205" s="12"/>
+      <c r="E205" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F205" s="12"/>
+      <c r="G205" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="H205" s="12"/>
+      <c r="I205" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J205" s="12"/>
+      <c r="K205" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L205" s="12"/>
+      <c r="M205" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N205" s="12"/>
+      <c r="O205" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="P205" s="12"/>
+    </row>
+    <row r="206" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="10"/>
+      <c r="B206" s="13"/>
+      <c r="C206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N206" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P206" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="10"/>
+      <c r="B207" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3">
+        <v>4.4249700000000001</v>
+      </c>
+      <c r="E207" s="3"/>
+      <c r="F207" s="3">
+        <v>5.5333399999999999</v>
+      </c>
+      <c r="G207" s="3"/>
+      <c r="H207" s="3">
+        <v>5.1902999999999997</v>
+      </c>
+      <c r="I207" s="3"/>
+      <c r="J207" s="3">
+        <v>4.8660300000000003</v>
+      </c>
+      <c r="K207" s="3"/>
+      <c r="L207" s="3">
+        <v>3.8866299999999998</v>
+      </c>
+      <c r="M207" s="3"/>
+      <c r="N207" s="3">
+        <v>3.6355400000000002</v>
+      </c>
+      <c r="O207" s="3"/>
+      <c r="P207" s="3">
+        <f>AVERAGE(D207,F207,H207,J207,L207,N207)</f>
+        <v>4.5894683333333335</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="10"/>
+      <c r="B208" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3">
+        <v>4.66181</v>
+      </c>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3">
+        <v>5.6358699999999997</v>
+      </c>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3">
+        <v>5.5303500000000003</v>
+      </c>
+      <c r="I208" s="3"/>
+      <c r="J208" s="3">
+        <v>4.9067100000000003</v>
+      </c>
+      <c r="K208" s="3"/>
+      <c r="L208" s="3">
+        <v>4.1264799999999999</v>
+      </c>
+      <c r="M208" s="3"/>
+      <c r="N208" s="3">
+        <v>3.8291499999999998</v>
+      </c>
+      <c r="O208" s="3"/>
+      <c r="P208" s="3">
+        <f>AVERAGE(D208,F208,H208,J208,L208,N208)</f>
+        <v>4.7817283333333336</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="10"/>
+      <c r="B209" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3">
+        <v>4.8665000000000003</v>
+      </c>
+      <c r="E209" s="3"/>
+      <c r="F209" s="3">
+        <v>5.8399900000000002</v>
+      </c>
+      <c r="G209" s="3"/>
+      <c r="H209" s="3">
+        <v>5.65158</v>
+      </c>
+      <c r="I209" s="3"/>
+      <c r="J209" s="3">
+        <v>5.07212</v>
+      </c>
+      <c r="K209" s="3"/>
+      <c r="L209" s="3">
+        <v>4.3304900000000002</v>
+      </c>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3">
+        <v>3.9704700000000002</v>
+      </c>
+      <c r="O209" s="3"/>
+      <c r="P209" s="3">
+        <f>AVERAGE(D209,F209,H209,J209,L209,N209)</f>
+        <v>4.9551916666666669</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="10"/>
+      <c r="B210" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3">
+        <v>4.9245000000000001</v>
+      </c>
+      <c r="E210" s="3"/>
+      <c r="F210" s="3">
+        <v>5.9912099999999997</v>
+      </c>
+      <c r="G210" s="3"/>
+      <c r="H210" s="3">
+        <v>5.8172800000000002</v>
+      </c>
+      <c r="I210" s="3"/>
+      <c r="J210" s="3">
+        <v>5.1707700000000001</v>
+      </c>
+      <c r="K210" s="3"/>
+      <c r="L210" s="3">
+        <v>4.4135600000000004</v>
+      </c>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3">
+        <v>4.1507300000000003</v>
+      </c>
+      <c r="O210" s="3"/>
+      <c r="P210" s="3">
+        <f>AVERAGE(D210,F210,H210,J210,L210,N210)</f>
+        <v>5.0780083333333339</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="10"/>
+      <c r="B211" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4">
+        <v>4.8952299999999997</v>
+      </c>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4">
+        <v>6.0022099999999998</v>
+      </c>
+      <c r="G211" s="4"/>
+      <c r="H211" s="4">
+        <v>5.8484299999999996</v>
+      </c>
+      <c r="I211" s="4"/>
+      <c r="J211" s="4">
+        <v>5.3302800000000001</v>
+      </c>
+      <c r="K211" s="4"/>
+      <c r="L211" s="4">
+        <v>4.4426100000000002</v>
+      </c>
+      <c r="M211" s="4"/>
+      <c r="N211" s="4">
+        <v>4.1807600000000003</v>
+      </c>
+      <c r="O211" s="4"/>
+      <c r="P211" s="4">
+        <f>AVERAGE(D211,F211,H211,J211,L211,N211)</f>
+        <v>5.1165866666666666</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="172">
+  <mergeCells count="229">
+    <mergeCell ref="A196:A211"/>
+    <mergeCell ref="B196:P196"/>
+    <mergeCell ref="B197:B198"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="G197:H197"/>
+    <mergeCell ref="I197:J197"/>
+    <mergeCell ref="K197:L197"/>
+    <mergeCell ref="M197:N197"/>
+    <mergeCell ref="O197:P197"/>
+    <mergeCell ref="B204:P204"/>
+    <mergeCell ref="B205:B206"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="E205:F205"/>
+    <mergeCell ref="G205:H205"/>
+    <mergeCell ref="I205:J205"/>
+    <mergeCell ref="K205:L205"/>
+    <mergeCell ref="M205:N205"/>
+    <mergeCell ref="O205:P205"/>
+    <mergeCell ref="A178:A193"/>
+    <mergeCell ref="B178:P178"/>
+    <mergeCell ref="B179:B180"/>
+    <mergeCell ref="C179:D179"/>
+    <mergeCell ref="E179:F179"/>
+    <mergeCell ref="G179:H179"/>
+    <mergeCell ref="I179:J179"/>
+    <mergeCell ref="K179:L179"/>
+    <mergeCell ref="M179:N179"/>
+    <mergeCell ref="O179:P179"/>
+    <mergeCell ref="B186:P186"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="E187:F187"/>
+    <mergeCell ref="G187:H187"/>
+    <mergeCell ref="I187:J187"/>
+    <mergeCell ref="K187:L187"/>
+    <mergeCell ref="M187:N187"/>
+    <mergeCell ref="O187:P187"/>
     <mergeCell ref="O133:P133"/>
     <mergeCell ref="B74:P74"/>
     <mergeCell ref="B75:B76"/>
@@ -14374,6 +15956,25 @@
     <mergeCell ref="K47:L47"/>
     <mergeCell ref="M47:N47"/>
     <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A160:A175"/>
+    <mergeCell ref="B160:P160"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="G161:H161"/>
+    <mergeCell ref="I161:J161"/>
+    <mergeCell ref="K161:L161"/>
+    <mergeCell ref="M161:N161"/>
+    <mergeCell ref="O161:P161"/>
+    <mergeCell ref="B168:P168"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="G169:H169"/>
+    <mergeCell ref="I169:J169"/>
+    <mergeCell ref="K169:L169"/>
+    <mergeCell ref="M169:N169"/>
+    <mergeCell ref="O169:P169"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14383,7 +15984,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368F3ECF-4C3C-4A6A-93FD-C9EEDD50477C}">
-  <dimension ref="A2:M63"/>
+  <dimension ref="A2:M79"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="15.58203125" style="1" customWidth="1"/>
@@ -16005,8 +17606,301 @@
         <v>3.9747900000000005</v>
       </c>
     </row>
+    <row r="66" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+    </row>
+    <row r="67" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="10"/>
+      <c r="B67" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="3">
+        <v>3.7833999999999999</v>
+      </c>
+      <c r="D68" s="3">
+        <v>4.3612599999999997</v>
+      </c>
+      <c r="E68" s="3">
+        <v>4.2225200000000003</v>
+      </c>
+      <c r="F68" s="3">
+        <v>3.9348399999999999</v>
+      </c>
+      <c r="G68" s="3">
+        <v>3.4268700000000001</v>
+      </c>
+      <c r="H68" s="3">
+        <v>3.1867399999999999</v>
+      </c>
+      <c r="I68" s="3">
+        <f>AVERAGE(C68:H68)</f>
+        <v>3.8192716666666673</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="10"/>
+      <c r="B69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3.8894700000000002</v>
+      </c>
+      <c r="D69" s="3">
+        <v>4.4556399999999998</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4.3234000000000004</v>
+      </c>
+      <c r="F69" s="3">
+        <v>4.0381799999999997</v>
+      </c>
+      <c r="G69" s="3">
+        <v>3.5754199999999998</v>
+      </c>
+      <c r="H69" s="3">
+        <v>3.2797800000000001</v>
+      </c>
+      <c r="I69" s="3">
+        <f t="shared" ref="I69:I72" si="6">AVERAGE(C69:H69)</f>
+        <v>3.9269816666666668</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="10"/>
+      <c r="B71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="10"/>
+      <c r="B72" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="3" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+    </row>
+    <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="10"/>
+      <c r="B74" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="10"/>
+      <c r="B75" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="3">
+        <v>3.5064199999999999</v>
+      </c>
+      <c r="D75" s="3">
+        <v>4.1836500000000001</v>
+      </c>
+      <c r="E75" s="3">
+        <v>4.0758000000000001</v>
+      </c>
+      <c r="F75" s="3">
+        <v>3.64452</v>
+      </c>
+      <c r="G75" s="3">
+        <v>3.2332399999999999</v>
+      </c>
+      <c r="H75" s="3">
+        <v>2.9424899999999998</v>
+      </c>
+      <c r="I75" s="3">
+        <f>AVERAGE(C75:H75)</f>
+        <v>3.5976866666666663</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="10"/>
+      <c r="B76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="3">
+        <v>3.60745</v>
+      </c>
+      <c r="D76" s="3">
+        <v>4.2968000000000002</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4.1498900000000001</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3.74688</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3.3121</v>
+      </c>
+      <c r="H76" s="3">
+        <v>3.0874100000000002</v>
+      </c>
+      <c r="I76" s="3">
+        <f t="shared" ref="I76:I79" si="7">AVERAGE(C76:H76)</f>
+        <v>3.7000883333333334</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="10"/>
+      <c r="B77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="10"/>
+      <c r="B78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="10"/>
+      <c r="B79" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
+    <mergeCell ref="A66:A79"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="B73:I73"/>
     <mergeCell ref="K2:M6"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="B2:I2"/>
